--- a/engine/adnocdist_study/ADNOCDIST_Valuation_Model_09082026.xlsx
+++ b/engine/adnocdist_study/ADNOCDIST_Valuation_Model_09082026.xlsx
@@ -211,6 +211,7 @@
     <xf numFmtId="10" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -224,7 +225,6 @@
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -782,24 +782,24 @@
       <c r="D2" s="20" t="n">
         <v>9478.001</v>
       </c>
-      <c r="E2" s="21">
-        <f>Assumptions!$C$58+Assumptions!C$44-Assumptions!C$43</f>
-        <v/>
-      </c>
-      <c r="F2" s="21">
-        <f>E2+Assumptions!D$44-Assumptions!D$43</f>
-        <v/>
-      </c>
-      <c r="G2" s="21">
-        <f>F2+Assumptions!E$44-Assumptions!E$43</f>
-        <v/>
-      </c>
-      <c r="H2" s="21">
-        <f>G2+Assumptions!F$44-Assumptions!F$43</f>
-        <v/>
-      </c>
-      <c r="I2" s="21">
-        <f>H2+Assumptions!G$44-Assumptions!G$43</f>
+      <c r="E2" s="22">
+        <f>Assumptions!$C$59+Assumptions!C$45-Assumptions!C$44</f>
+        <v/>
+      </c>
+      <c r="F2" s="22">
+        <f>E2+Assumptions!D$45-Assumptions!D$44</f>
+        <v/>
+      </c>
+      <c r="G2" s="22">
+        <f>F2+Assumptions!E$45-Assumptions!E$44</f>
+        <v/>
+      </c>
+      <c r="H2" s="22">
+        <f>G2+Assumptions!F$45-Assumptions!F$44</f>
+        <v/>
+      </c>
+      <c r="I2" s="22">
+        <f>H2+Assumptions!G$45-Assumptions!G$44</f>
         <v/>
       </c>
     </row>
@@ -818,24 +818,24 @@
       <c r="D3" s="20" t="n">
         <v>671.2729999999999</v>
       </c>
-      <c r="E3" s="21">
-        <f>Assumptions!$C$59</f>
-        <v/>
-      </c>
-      <c r="F3" s="21">
-        <f>Assumptions!$C$59</f>
-        <v/>
-      </c>
-      <c r="G3" s="21">
-        <f>Assumptions!$C$59</f>
-        <v/>
-      </c>
-      <c r="H3" s="21">
-        <f>Assumptions!$C$59</f>
-        <v/>
-      </c>
-      <c r="I3" s="21">
-        <f>Assumptions!$C$59</f>
+      <c r="E3" s="22">
+        <f>Assumptions!$C$60</f>
+        <v/>
+      </c>
+      <c r="F3" s="22">
+        <f>Assumptions!$C$60</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>Assumptions!$C$60</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>Assumptions!$C$60</f>
+        <v/>
+      </c>
+      <c r="I3" s="22">
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
     </row>
@@ -854,24 +854,24 @@
       <c r="D4" s="20" t="n">
         <v>1574.254</v>
       </c>
-      <c r="E4" s="21">
-        <f>Assumptions!$C$46/365*('Income Statement'!E2-'Income Statement'!E3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="21">
-        <f>Assumptions!$C$46/365*('Income Statement'!F2-'Income Statement'!F3)</f>
-        <v/>
-      </c>
-      <c r="G4" s="21">
-        <f>Assumptions!$C$46/365*('Income Statement'!G2-'Income Statement'!G3)</f>
-        <v/>
-      </c>
-      <c r="H4" s="21">
-        <f>Assumptions!$C$46/365*('Income Statement'!H2-'Income Statement'!H3)</f>
-        <v/>
-      </c>
-      <c r="I4" s="21">
-        <f>Assumptions!$C$46/365*('Income Statement'!I2-'Income Statement'!I3)</f>
+      <c r="E4" s="22">
+        <f>Assumptions!$C$47/365*('Income Statement'!E2-'Income Statement'!E3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="22">
+        <f>Assumptions!$C$47/365*('Income Statement'!F2-'Income Statement'!F3)</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>Assumptions!$C$47/365*('Income Statement'!G2-'Income Statement'!G3)</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>Assumptions!$C$47/365*('Income Statement'!H2-'Income Statement'!H3)</f>
+        <v/>
+      </c>
+      <c r="I4" s="22">
+        <f>Assumptions!$C$47/365*('Income Statement'!I2-'Income Statement'!I3)</f>
         <v/>
       </c>
     </row>
@@ -890,24 +890,24 @@
       <c r="D5" s="20" t="n">
         <v>3390.983</v>
       </c>
-      <c r="E5" s="21">
-        <f>Assumptions!$C$45/365*'Income Statement'!E2</f>
-        <v/>
-      </c>
-      <c r="F5" s="21">
-        <f>Assumptions!$C$45/365*'Income Statement'!F2</f>
-        <v/>
-      </c>
-      <c r="G5" s="21">
-        <f>Assumptions!$C$45/365*'Income Statement'!G2</f>
-        <v/>
-      </c>
-      <c r="H5" s="21">
-        <f>Assumptions!$C$45/365*'Income Statement'!H2</f>
-        <v/>
-      </c>
-      <c r="I5" s="21">
-        <f>Assumptions!$C$45/365*'Income Statement'!I2</f>
+      <c r="E5" s="22">
+        <f>Assumptions!$C$46/365*'Income Statement'!E2</f>
+        <v/>
+      </c>
+      <c r="F5" s="22">
+        <f>Assumptions!$C$46/365*'Income Statement'!F2</f>
+        <v/>
+      </c>
+      <c r="G5" s="22">
+        <f>Assumptions!$C$46/365*'Income Statement'!G2</f>
+        <v/>
+      </c>
+      <c r="H5" s="22">
+        <f>Assumptions!$C$46/365*'Income Statement'!H2</f>
+        <v/>
+      </c>
+      <c r="I5" s="22">
+        <f>Assumptions!$C$46/365*'Income Statement'!I2</f>
         <v/>
       </c>
     </row>
@@ -926,23 +926,23 @@
       <c r="D6" s="20" t="n">
         <v>2560.854</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="22">
         <f>E8+E9+E10+E11+E12+E13-E2-E3-E4-E5</f>
         <v/>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="22">
         <f>F8+F9+F10+F11+F12+F13-F2-F3-F4-F5</f>
         <v/>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="22">
         <f>G8+G9+G10+G11+G12+G13-G2-G3-G4-G5</f>
         <v/>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="22">
         <f>H8+H9+H10+H11+H12+H13-H2-H3-H4-H5</f>
         <v/>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="22">
         <f>I8+I9+I10+I11+I12+I13-I2-I3-I4-I5</f>
         <v/>
       </c>
@@ -953,32 +953,32 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B7" s="31" t="n">
+      <c r="B7" s="32" t="n">
         <v>18891.629</v>
       </c>
-      <c r="C7" s="31" t="n">
+      <c r="C7" s="32" t="n">
         <v>18180.794</v>
       </c>
-      <c r="D7" s="31" t="n">
+      <c r="D7" s="32" t="n">
         <v>17675.365</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="23">
         <f>E2+E3+E4+E5+E6</f>
         <v/>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="23">
         <f>F2+F3+F4+F5+F6</f>
         <v/>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="23">
         <f>G2+G3+G4+G5+G6</f>
         <v/>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="23">
         <f>H2+H3+H4+H5+H6</f>
         <v/>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="23">
         <f>I2+I3+I4+I5+I6</f>
         <v/>
       </c>
@@ -998,24 +998,24 @@
       <c r="D8" s="20" t="n">
         <v>3230.423</v>
       </c>
-      <c r="E8" s="21">
-        <f>Assumptions!$C$60+'Income Statement'!E18-Assumptions!$C$48*Assumptions!$C$4</f>
-        <v/>
-      </c>
-      <c r="F8" s="21">
-        <f>E8+'Income Statement'!F18-Assumptions!$C$48*Assumptions!$C$4</f>
-        <v/>
-      </c>
-      <c r="G8" s="21">
-        <f>F8+'Income Statement'!G18-Assumptions!$C$48*Assumptions!$C$4</f>
-        <v/>
-      </c>
-      <c r="H8" s="21">
-        <f>G8+'Income Statement'!H18-Assumptions!$C$48*Assumptions!$C$4</f>
-        <v/>
-      </c>
-      <c r="I8" s="21">
-        <f>H8+'Income Statement'!I18-Assumptions!$C$48*Assumptions!$C$4</f>
+      <c r="E8" s="22">
+        <f>Assumptions!$C$61+'Income Statement'!E18-Assumptions!$C$49*Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="F8" s="22">
+        <f>E8+'Income Statement'!F18-Assumptions!$C$49*Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="G8" s="22">
+        <f>F8+'Income Statement'!G18-Assumptions!$C$49*Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="H8" s="22">
+        <f>G8+'Income Statement'!H18-Assumptions!$C$49*Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="I8" s="22">
+        <f>H8+'Income Statement'!I18-Assumptions!$C$49*Assumptions!$C$4</f>
         <v/>
       </c>
     </row>
@@ -1034,24 +1034,24 @@
       <c r="D9" s="20" t="n">
         <v>230.374</v>
       </c>
-      <c r="E9" s="21">
-        <f>Assumptions!$C$61+Assumptions!$C$68</f>
-        <v/>
-      </c>
-      <c r="F9" s="21">
-        <f>E9+Assumptions!$C$68</f>
-        <v/>
-      </c>
-      <c r="G9" s="21">
-        <f>F9+Assumptions!$C$68</f>
-        <v/>
-      </c>
-      <c r="H9" s="21">
-        <f>G9+Assumptions!$C$68</f>
-        <v/>
-      </c>
-      <c r="I9" s="21">
-        <f>H9+Assumptions!$C$68</f>
+      <c r="E9" s="22">
+        <f>Assumptions!$C$62+Assumptions!$C$69</f>
+        <v/>
+      </c>
+      <c r="F9" s="22">
+        <f>E9+Assumptions!$C$69</f>
+        <v/>
+      </c>
+      <c r="G9" s="22">
+        <f>F9+Assumptions!$C$69</f>
+        <v/>
+      </c>
+      <c r="H9" s="22">
+        <f>G9+Assumptions!$C$69</f>
+        <v/>
+      </c>
+      <c r="I9" s="22">
+        <f>H9+Assumptions!$C$69</f>
         <v/>
       </c>
     </row>
@@ -1070,24 +1070,24 @@
       <c r="D10" s="20" t="n">
         <v>5545.975</v>
       </c>
-      <c r="E10" s="21">
-        <f>Assumptions!$C$62</f>
-        <v/>
-      </c>
-      <c r="F10" s="21">
-        <f>Assumptions!$C$62</f>
-        <v/>
-      </c>
-      <c r="G10" s="21">
-        <f>Assumptions!$C$62</f>
-        <v/>
-      </c>
-      <c r="H10" s="21">
-        <f>Assumptions!$C$62</f>
-        <v/>
-      </c>
-      <c r="I10" s="21">
-        <f>Assumptions!$C$62</f>
+      <c r="E10" s="22">
+        <f>Assumptions!$C$63</f>
+        <v/>
+      </c>
+      <c r="F10" s="22">
+        <f>Assumptions!$C$63</f>
+        <v/>
+      </c>
+      <c r="G10" s="22">
+        <f>Assumptions!$C$63</f>
+        <v/>
+      </c>
+      <c r="H10" s="22">
+        <f>Assumptions!$C$63</f>
+        <v/>
+      </c>
+      <c r="I10" s="22">
+        <f>Assumptions!$C$63</f>
         <v/>
       </c>
     </row>
@@ -1106,24 +1106,24 @@
       <c r="D11" s="20" t="n">
         <v>1446.327</v>
       </c>
-      <c r="E11" s="21">
-        <f>Assumptions!$C$63</f>
-        <v/>
-      </c>
-      <c r="F11" s="21">
-        <f>Assumptions!$C$63</f>
-        <v/>
-      </c>
-      <c r="G11" s="21">
-        <f>Assumptions!$C$63</f>
-        <v/>
-      </c>
-      <c r="H11" s="21">
-        <f>Assumptions!$C$63</f>
-        <v/>
-      </c>
-      <c r="I11" s="21">
-        <f>Assumptions!$C$63</f>
+      <c r="E11" s="22">
+        <f>Assumptions!$C$64</f>
+        <v/>
+      </c>
+      <c r="F11" s="22">
+        <f>Assumptions!$C$64</f>
+        <v/>
+      </c>
+      <c r="G11" s="22">
+        <f>Assumptions!$C$64</f>
+        <v/>
+      </c>
+      <c r="H11" s="22">
+        <f>Assumptions!$C$64</f>
+        <v/>
+      </c>
+      <c r="I11" s="22">
+        <f>Assumptions!$C$64</f>
         <v/>
       </c>
     </row>
@@ -1138,24 +1138,24 @@
       <c r="D12" s="20" t="n">
         <v>460.12</v>
       </c>
-      <c r="E12" s="21">
-        <f>Assumptions!$C$64</f>
-        <v/>
-      </c>
-      <c r="F12" s="21">
-        <f>Assumptions!$C$64</f>
-        <v/>
-      </c>
-      <c r="G12" s="21">
-        <f>Assumptions!$C$64</f>
-        <v/>
-      </c>
-      <c r="H12" s="21">
-        <f>Assumptions!$C$64</f>
-        <v/>
-      </c>
-      <c r="I12" s="21">
-        <f>Assumptions!$C$64</f>
+      <c r="E12" s="22">
+        <f>Assumptions!$C$65</f>
+        <v/>
+      </c>
+      <c r="F12" s="22">
+        <f>Assumptions!$C$65</f>
+        <v/>
+      </c>
+      <c r="G12" s="22">
+        <f>Assumptions!$C$65</f>
+        <v/>
+      </c>
+      <c r="H12" s="22">
+        <f>Assumptions!$C$65</f>
+        <v/>
+      </c>
+      <c r="I12" s="22">
+        <f>Assumptions!$C$65</f>
         <v/>
       </c>
     </row>
@@ -1174,24 +1174,24 @@
       <c r="D13" s="20" t="n">
         <v>6762.146000000001</v>
       </c>
-      <c r="E13" s="21">
-        <f>Assumptions!$C$47/365*('Income Statement'!E2-'Income Statement'!E3)</f>
-        <v/>
-      </c>
-      <c r="F13" s="21">
-        <f>Assumptions!$C$47/365*('Income Statement'!F2-'Income Statement'!F3)</f>
-        <v/>
-      </c>
-      <c r="G13" s="21">
-        <f>Assumptions!$C$47/365*('Income Statement'!G2-'Income Statement'!G3)</f>
-        <v/>
-      </c>
-      <c r="H13" s="21">
-        <f>Assumptions!$C$47/365*('Income Statement'!H2-'Income Statement'!H3)</f>
-        <v/>
-      </c>
-      <c r="I13" s="21">
-        <f>Assumptions!$C$47/365*('Income Statement'!I2-'Income Statement'!I3)</f>
+      <c r="E13" s="22">
+        <f>Assumptions!$C$48/365*('Income Statement'!E2-'Income Statement'!E3)</f>
+        <v/>
+      </c>
+      <c r="F13" s="22">
+        <f>Assumptions!$C$48/365*('Income Statement'!F2-'Income Statement'!F3)</f>
+        <v/>
+      </c>
+      <c r="G13" s="22">
+        <f>Assumptions!$C$48/365*('Income Statement'!G2-'Income Statement'!G3)</f>
+        <v/>
+      </c>
+      <c r="H13" s="22">
+        <f>Assumptions!$C$48/365*('Income Statement'!H2-'Income Statement'!H3)</f>
+        <v/>
+      </c>
+      <c r="I13" s="22">
+        <f>Assumptions!$C$48/365*('Income Statement'!I2-'Income Statement'!I3)</f>
         <v/>
       </c>
     </row>
@@ -1201,32 +1201,32 @@
           <t>TOTAL EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B14" s="31" t="n">
+      <c r="B14" s="32" t="n">
         <v>18891.629</v>
       </c>
-      <c r="C14" s="31" t="n">
+      <c r="C14" s="32" t="n">
         <v>18180.794</v>
       </c>
-      <c r="D14" s="31" t="n">
+      <c r="D14" s="32" t="n">
         <v>17675.365</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="23">
         <f>E8+E9+E10+E11+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="23">
         <f>F8+F9+F10+F11+F12+F13</f>
         <v/>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="23">
         <f>G8+G9+G10+G11+G12+G13</f>
         <v/>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="23">
         <f>H8+H9+H10+H11+H12+H13</f>
         <v/>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="23">
         <f>I8+I9+I10+I11+I12+I13</f>
         <v/>
       </c>
@@ -1237,32 +1237,32 @@
           <t>BALANCE CHECK (must be zero)</t>
         </is>
       </c>
-      <c r="B15" s="33" t="n">
+      <c r="B15" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="33" t="n">
+      <c r="C15" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="33" t="n">
+      <c r="D15" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="21">
         <f>E7-E14</f>
         <v/>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="21">
         <f>F7-F14</f>
         <v/>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="21">
         <f>G7-G14</f>
         <v/>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="21">
         <f>H7-H14</f>
         <v/>
       </c>
-      <c r="I15" s="34">
+      <c r="I15" s="21">
         <f>I7-I14</f>
         <v/>
       </c>
@@ -1282,23 +1282,23 @@
       <c r="D16" s="20" t="n">
         <v>2985.121000000001</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="22">
         <f>E10-E6</f>
         <v/>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="22">
         <f>F10-F6</f>
         <v/>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="22">
         <f>G10-G6</f>
         <v/>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="22">
         <f>H10-H6</f>
         <v/>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="22">
         <f>I10-I6</f>
         <v/>
       </c>
@@ -1318,23 +1318,23 @@
       <c r="D17" s="16" t="n">
         <v>0.25843384</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <f>E8/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <f>F8/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="26">
         <f>G8/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="26">
         <f>H8/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="26">
         <f>I8/Assumptions!$C$4</f>
         <v/>
       </c>
@@ -1426,23 +1426,23 @@
       <c r="D2" s="20" t="n">
         <v>3505.604</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="22">
         <f>'Income Statement'!E11</f>
         <v/>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="22">
         <f>'Income Statement'!F11</f>
         <v/>
       </c>
-      <c r="G2" s="21">
+      <c r="G2" s="22">
         <f>'Income Statement'!G11</f>
         <v/>
       </c>
-      <c r="H2" s="21">
+      <c r="H2" s="22">
         <f>'Income Statement'!H11</f>
         <v/>
       </c>
-      <c r="I2" s="21">
+      <c r="I2" s="22">
         <f>'Income Statement'!I11</f>
         <v/>
       </c>
@@ -1462,23 +1462,23 @@
       <c r="D3" s="18" t="n">
         <v>0.1017321411636604</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="30">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="30">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="G3" s="29">
+      <c r="G3" s="30">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="H3" s="29">
+      <c r="H3" s="30">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="I3" s="29">
+      <c r="I3" s="30">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
@@ -1489,13 +1489,13 @@
           <t>NOPAT = EBIT x (1 less the tax rate)</t>
         </is>
       </c>
-      <c r="B4" s="32" t="n">
+      <c r="B4" s="33" t="n">
         <v>2962.037770648459</v>
       </c>
-      <c r="C4" s="32" t="n">
+      <c r="C4" s="33" t="n">
         <v>2753.28964072531</v>
       </c>
-      <c r="D4" s="32" t="n">
+      <c r="D4" s="33" t="n">
         <v>3148.971399008107</v>
       </c>
       <c r="E4" s="17">
@@ -1534,24 +1534,24 @@
       <c r="D5" s="20" t="n">
         <v>775.946</v>
       </c>
-      <c r="E5" s="21">
-        <f>Assumptions!C$43</f>
-        <v/>
-      </c>
-      <c r="F5" s="21">
-        <f>Assumptions!D$43</f>
-        <v/>
-      </c>
-      <c r="G5" s="21">
-        <f>Assumptions!E$43</f>
-        <v/>
-      </c>
-      <c r="H5" s="21">
-        <f>Assumptions!F$43</f>
-        <v/>
-      </c>
-      <c r="I5" s="21">
-        <f>Assumptions!G$43</f>
+      <c r="E5" s="22">
+        <f>Assumptions!C$44</f>
+        <v/>
+      </c>
+      <c r="F5" s="22">
+        <f>Assumptions!D$44</f>
+        <v/>
+      </c>
+      <c r="G5" s="22">
+        <f>Assumptions!E$44</f>
+        <v/>
+      </c>
+      <c r="H5" s="22">
+        <f>Assumptions!F$44</f>
+        <v/>
+      </c>
+      <c r="I5" s="22">
+        <f>Assumptions!G$44</f>
         <v/>
       </c>
     </row>
@@ -1570,24 +1570,24 @@
       <c r="D6" s="20" t="n">
         <v>-1207.394</v>
       </c>
-      <c r="E6" s="21">
-        <f>-Assumptions!C$44</f>
-        <v/>
-      </c>
-      <c r="F6" s="21">
-        <f>-Assumptions!D$44</f>
-        <v/>
-      </c>
-      <c r="G6" s="21">
-        <f>-Assumptions!E$44</f>
-        <v/>
-      </c>
-      <c r="H6" s="21">
-        <f>-Assumptions!F$44</f>
-        <v/>
-      </c>
-      <c r="I6" s="21">
-        <f>-Assumptions!G$44</f>
+      <c r="E6" s="22">
+        <f>-Assumptions!C$45</f>
+        <v/>
+      </c>
+      <c r="F6" s="22">
+        <f>-Assumptions!D$45</f>
+        <v/>
+      </c>
+      <c r="G6" s="22">
+        <f>-Assumptions!E$45</f>
+        <v/>
+      </c>
+      <c r="H6" s="22">
+        <f>-Assumptions!F$45</f>
+        <v/>
+      </c>
+      <c r="I6" s="22">
+        <f>-Assumptions!G$45</f>
         <v/>
       </c>
     </row>
@@ -1600,23 +1600,23 @@
       <c r="B7" s="20" t="n"/>
       <c r="C7" s="20" t="n"/>
       <c r="D7" s="20" t="n"/>
-      <c r="E7" s="21">
+      <c r="E7" s="22">
         <f>-('Balance Sheet'!E5+'Balance Sheet'!E4-'Balance Sheet'!E13-'Balance Sheet'!D5-'Balance Sheet'!D4+'Balance Sheet'!D13)</f>
         <v/>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="22">
         <f>-('Balance Sheet'!F5+'Balance Sheet'!F4-'Balance Sheet'!F13-'Balance Sheet'!E5-'Balance Sheet'!E4+'Balance Sheet'!E13)</f>
         <v/>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="22">
         <f>-('Balance Sheet'!G5+'Balance Sheet'!G4-'Balance Sheet'!G13-'Balance Sheet'!F5-'Balance Sheet'!F4+'Balance Sheet'!F13)</f>
         <v/>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="22">
         <f>-('Balance Sheet'!H5+'Balance Sheet'!H4-'Balance Sheet'!H13-'Balance Sheet'!G5-'Balance Sheet'!G4+'Balance Sheet'!G13)</f>
         <v/>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="22">
         <f>-('Balance Sheet'!I5+'Balance Sheet'!I4-'Balance Sheet'!I13-'Balance Sheet'!H5-'Balance Sheet'!H4+'Balance Sheet'!H13)</f>
         <v/>
       </c>
@@ -1627,26 +1627,26 @@
           <t>FREE CASH FLOW TO THE FIRM</t>
         </is>
       </c>
-      <c r="B8" s="31" t="n"/>
-      <c r="C8" s="31" t="n"/>
-      <c r="D8" s="31" t="n"/>
-      <c r="E8" s="22">
+      <c r="B8" s="32" t="n"/>
+      <c r="C8" s="32" t="n"/>
+      <c r="D8" s="32" t="n"/>
+      <c r="E8" s="23">
         <f>E4+E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="23">
         <f>F4+F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="23">
         <f>G4+G5+G6+G7</f>
         <v/>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="23">
         <f>H4+H5+H6+H7</f>
         <v/>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="23">
         <f>I4+I5+I6+I7</f>
         <v/>
       </c>
@@ -1666,24 +1666,24 @@
       <c r="D9" s="20" t="n">
         <v>-2599.146</v>
       </c>
-      <c r="E9" s="21">
-        <f>-Assumptions!$C$48*Assumptions!$C$4</f>
-        <v/>
-      </c>
-      <c r="F9" s="21">
-        <f>-Assumptions!$C$48*Assumptions!$C$4</f>
-        <v/>
-      </c>
-      <c r="G9" s="21">
-        <f>-Assumptions!$C$48*Assumptions!$C$4</f>
-        <v/>
-      </c>
-      <c r="H9" s="21">
-        <f>-Assumptions!$C$48*Assumptions!$C$4</f>
-        <v/>
-      </c>
-      <c r="I9" s="21">
-        <f>-Assumptions!$C$48*Assumptions!$C$4</f>
+      <c r="E9" s="22">
+        <f>-Assumptions!$C$49*Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="F9" s="22">
+        <f>-Assumptions!$C$49*Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="G9" s="22">
+        <f>-Assumptions!$C$49*Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="H9" s="22">
+        <f>-Assumptions!$C$49*Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="I9" s="22">
+        <f>-Assumptions!$C$49*Assumptions!$C$4</f>
         <v/>
       </c>
     </row>
@@ -1774,23 +1774,23 @@
       <c r="D2" s="20" t="n">
         <v>35896.617</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="22">
         <f>'Income Statement'!E2</f>
         <v/>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="22">
         <f>'Income Statement'!F2</f>
         <v/>
       </c>
-      <c r="G2" s="21">
+      <c r="G2" s="22">
         <f>'Income Statement'!G2</f>
         <v/>
       </c>
-      <c r="H2" s="21">
+      <c r="H2" s="22">
         <f>'Income Statement'!H2</f>
         <v/>
       </c>
-      <c r="I2" s="21">
+      <c r="I2" s="22">
         <f>'Income Statement'!I2</f>
         <v/>
       </c>
@@ -1810,23 +1810,23 @@
       <c r="D3" s="20" t="n">
         <v>6945.79</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="22">
         <f>'Income Statement'!E3</f>
         <v/>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="22">
         <f>'Income Statement'!F3</f>
         <v/>
       </c>
-      <c r="G3" s="21">
+      <c r="G3" s="22">
         <f>'Income Statement'!G3</f>
         <v/>
       </c>
-      <c r="H3" s="21">
+      <c r="H3" s="22">
         <f>'Income Statement'!H3</f>
         <v/>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="22">
         <f>'Income Statement'!I3</f>
         <v/>
       </c>
@@ -1846,23 +1846,23 @@
       <c r="D4" s="20" t="n">
         <v>4281.55</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="22">
         <f>'Income Statement'!E8</f>
         <v/>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="22">
         <f>'Income Statement'!F8</f>
         <v/>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="22">
         <f>'Income Statement'!G8</f>
         <v/>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="22">
         <f>'Income Statement'!H8</f>
         <v/>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="22">
         <f>'Income Statement'!I8</f>
         <v/>
       </c>
@@ -1882,23 +1882,23 @@
       <c r="D5" s="20" t="n">
         <v>3505.604</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="22">
         <f>'Income Statement'!E11</f>
         <v/>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="22">
         <f>'Income Statement'!F11</f>
         <v/>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="22">
         <f>'Income Statement'!G11</f>
         <v/>
       </c>
-      <c r="H5" s="21">
+      <c r="H5" s="22">
         <f>'Income Statement'!H11</f>
         <v/>
       </c>
-      <c r="I5" s="21">
+      <c r="I5" s="22">
         <f>'Income Statement'!I11</f>
         <v/>
       </c>
@@ -1918,23 +1918,23 @@
       <c r="D6" s="20" t="n">
         <v>2794</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="22">
         <f>'Income Statement'!E18</f>
         <v/>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="22">
         <f>'Income Statement'!F18</f>
         <v/>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="22">
         <f>'Income Statement'!G18</f>
         <v/>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="22">
         <f>'Income Statement'!H18</f>
         <v/>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="22">
         <f>'Income Statement'!I18</f>
         <v/>
       </c>
@@ -1948,23 +1948,23 @@
       <c r="B7" s="4" t="inlineStr"/>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="21">
+      <c r="E7" s="22">
         <f>'Cash Flow'!E8</f>
         <v/>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="22">
         <f>'Cash Flow'!F8</f>
         <v/>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="22">
         <f>'Cash Flow'!G8</f>
         <v/>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="22">
         <f>'Cash Flow'!H8</f>
         <v/>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="22">
         <f>'Cash Flow'!I8</f>
         <v/>
       </c>
@@ -2017,9 +2017,9 @@
           <t>THESE CELLS ARE A WHOLE-MODEL RE-RUN — 50,000 simulated price paths each. They do NOT redraw when a driver on the Assumptions sheet changes.</t>
         </is>
       </c>
-      <c r="B2" s="23" t="n"/>
-      <c r="C2" s="23" t="n"/>
-      <c r="D2" s="24" t="n"/>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="25" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2214,120 +2214,120 @@
           <t>EACH CELL IS A COMPLETE REVALUATION of the whole model. These grids do NOT redraw when a driver changes.</t>
         </is>
       </c>
-      <c r="B2" s="23" t="n"/>
-      <c r="C2" s="23" t="n"/>
-      <c r="D2" s="23" t="n"/>
-      <c r="E2" s="23" t="n"/>
-      <c r="F2" s="24" t="n"/>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="25" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of capital 6.18%</t>
+          <t>Terminal cost of capital 6.56%</t>
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>5.051165332704169</v>
+        <v>4.686743038033034</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>5.382835166134885</v>
+        <v>4.966264082174509</v>
       </c>
       <c r="D3" s="15" t="n">
-        <v>5.784279167720555</v>
+        <v>5.30009108812957</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>6.280509705418305</v>
+        <v>5.706086415087039</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>6.910116665224723</v>
+        <v>6.210910815072849</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of capital 6.68%</t>
+          <t>Terminal cost of capital 7.06%</t>
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>4.652099800516405</v>
+        <v>4.338081945134413</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>4.921076137491585</v>
+        <v>4.567222912130541</v>
       </c>
       <c r="D4" s="15" t="n">
-        <v>5.241017621715765</v>
+        <v>4.83673778287524</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>5.628243962707286</v>
+        <v>5.158594234015194</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>6.106875169918197</v>
+        <v>5.550008498875564</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of capital 7.18%</t>
+          <t>Terminal cost of capital 7.56%</t>
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>4.312547046101024</v>
+        <v>4.038627665035003</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>4.533756598006698</v>
+        <v>4.228797998615474</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>4.793056883267031</v>
+        <v>4.449591502167147</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>5.101468718263538</v>
+        <v>4.70926927453304</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>5.474718266246048</v>
+        <v>5.019357433145563</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of capital 7.68%</t>
+          <t>Terminal cost of capital 8.06%</t>
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>4.020083198427797</v>
+        <v>3.778618892760917</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>4.204174150057215</v>
+        <v>3.938113156082837</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>4.417284785785445</v>
+        <v>4.12123033903702</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>4.667072849491019</v>
+        <v>4.333817343279192</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>4.964150245001583</v>
+        <v>4.58382413306109</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of capital 8.18%</t>
+          <t>Terminal cost of capital 8.56%</t>
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>3.765517908046157</v>
+        <v>3.550716356365404</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>3.920276010560161</v>
+        <v>3.685698405723232</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>4.097504399549541</v>
+        <v>3.839167477166377</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>4.302653165356912</v>
+        <v>4.015350548573732</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>4.543089965532787</v>
+        <v>4.219869555170337</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>0.06184379999999998</v>
+        <v>0.06560368642200001</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>5.784279167720555</v>
+        <v>5.30009108812957</v>
       </c>
     </row>
     <row r="11">
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>0.06684379999999998</v>
+        <v>0.070603686422</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>5.241017621715765</v>
+        <v>4.83673778287524</v>
       </c>
     </row>
     <row r="12">
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>0.07184379999999999</v>
+        <v>0.07560368642200001</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>4.793056883267031</v>
+        <v>4.449591502167147</v>
       </c>
     </row>
     <row r="13">
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>0.07684379999999999</v>
+        <v>0.08060368642200001</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>4.417284785785445</v>
+        <v>4.12123033903702</v>
       </c>
     </row>
     <row r="14">
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>0.08184379999999998</v>
+        <v>0.085603686422</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>4.097504399549541</v>
+        <v>3.839167477166377</v>
       </c>
     </row>
     <row r="15">
@@ -2425,7 +2425,7 @@
         <v>0.005</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>4.312547046101024</v>
+        <v>4.038627665035003</v>
       </c>
     </row>
     <row r="16">
@@ -2438,7 +2438,7 @@
         <v>0.01</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>4.533756598006698</v>
+        <v>4.228797998615474</v>
       </c>
     </row>
     <row r="17">
@@ -2451,7 +2451,7 @@
         <v>0.015</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>4.793056883267031</v>
+        <v>4.449591502167147</v>
       </c>
     </row>
     <row r="18">
@@ -2464,7 +2464,7 @@
         <v>0.02</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>5.101468718263538</v>
+        <v>4.70926927453304</v>
       </c>
     </row>
     <row r="19">
@@ -2477,7 +2477,7 @@
         <v>0.025</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>5.474718266246048</v>
+        <v>5.019357433145563</v>
       </c>
     </row>
     <row r="20">
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>5.518689485679632</v>
+        <v>5.266283774855093</v>
       </c>
     </row>
     <row r="21">
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="C21" s="15" t="n">
-        <v>5.040544547396718</v>
+        <v>4.824952324894785</v>
       </c>
     </row>
     <row r="22">
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="B22" s="16" t="n">
-        <v>0.509</v>
+        <v>0.6494</v>
       </c>
       <c r="C22" s="15" t="n">
-        <v>4.793056883267031</v>
+        <v>4.449591502167147</v>
       </c>
     </row>
     <row r="23">
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C23" s="15" t="n">
-        <v>4.126622322776198</v>
+        <v>3.973711096776246</v>
       </c>
     </row>
     <row r="24">
@@ -2542,7 +2542,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="15" t="n">
-        <v>3.3676672091461</v>
+        <v>3.469721946561251</v>
       </c>
     </row>
     <row r="25">
@@ -2555,7 +2555,7 @@
         <v>-0.01</v>
       </c>
       <c r="C25" s="15" t="n">
-        <v>4.561727547794757</v>
+        <v>4.235040245802537</v>
       </c>
     </row>
     <row r="26">
@@ -2568,7 +2568,7 @@
         <v>-0.005</v>
       </c>
       <c r="C26" s="15" t="n">
-        <v>4.676310776836733</v>
+        <v>4.341316677248776</v>
       </c>
     </row>
     <row r="27">
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="15" t="n">
-        <v>4.793056883267031</v>
+        <v>4.449591502167147</v>
       </c>
     </row>
     <row r="28">
@@ -2594,7 +2594,7 @@
         <v>0.005</v>
       </c>
       <c r="C28" s="15" t="n">
-        <v>4.911997212993007</v>
+        <v>4.559893626872848</v>
       </c>
     </row>
     <row r="29">
@@ -2607,7 +2607,7 @@
         <v>0.01</v>
       </c>
       <c r="C29" s="15" t="n">
-        <v>5.033163416799837</v>
+        <v>4.672252238508341</v>
       </c>
     </row>
     <row r="30">
@@ -2620,7 +2620,7 @@
         <v>-0.1</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>4.26141994796077</v>
+        <v>3.953235423567004</v>
       </c>
     </row>
     <row r="31">
@@ -2633,7 +2633,7 @@
         <v>-0.05</v>
       </c>
       <c r="C31" s="15" t="n">
-        <v>4.527238415613899</v>
+        <v>4.201413462867075</v>
       </c>
     </row>
     <row r="32">
@@ -2646,7 +2646,7 @@
         <v>0</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>4.793056883267031</v>
+        <v>4.449591502167147</v>
       </c>
     </row>
     <row r="33">
@@ -2659,7 +2659,7 @@
         <v>0.05</v>
       </c>
       <c r="C33" s="15" t="n">
-        <v>5.058875350920161</v>
+        <v>4.69776954146722</v>
       </c>
     </row>
     <row r="34">
@@ -2672,7 +2672,7 @@
         <v>0.1</v>
       </c>
       <c r="C34" s="15" t="n">
-        <v>5.324693818573292</v>
+        <v>4.945947580767291</v>
       </c>
     </row>
     <row r="35">
@@ -2685,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="C35" s="15" t="n">
-        <v>4.793056883267031</v>
+        <v>4.449591502167147</v>
       </c>
     </row>
     <row r="36">
@@ -2698,7 +2698,7 @@
         <v>150</v>
       </c>
       <c r="C36" s="15" t="n">
-        <v>4.957114918543484</v>
+        <v>4.602323091084383</v>
       </c>
     </row>
     <row r="37">
@@ -2711,7 +2711,7 @@
         <v>295</v>
       </c>
       <c r="C37" s="15" t="n">
-        <v>5.115704352644054</v>
+        <v>4.749963627037711</v>
       </c>
     </row>
     <row r="38">
@@ -2724,7 +2724,7 @@
         <v>450</v>
       </c>
       <c r="C38" s="15" t="n">
-        <v>5.285230989096386</v>
+        <v>4.907786268918853</v>
       </c>
     </row>
     <row r="39">
@@ -2737,7 +2737,7 @@
         <v>600</v>
       </c>
       <c r="C39" s="15" t="n">
-        <v>5.449289024372837</v>
+        <v>5.060517857836088</v>
       </c>
     </row>
     <row r="40">
@@ -2750,7 +2750,7 @@
         <v>0.09</v>
       </c>
       <c r="C40" s="15" t="n">
-        <v>4.860726443075919</v>
+        <v>4.512778315092071</v>
       </c>
     </row>
     <row r="41">
@@ -2763,7 +2763,7 @@
         <v>0.1017</v>
       </c>
       <c r="C41" s="15" t="n">
-        <v>4.793056883267031</v>
+        <v>4.449591502167147</v>
       </c>
     </row>
     <row r="42">
@@ -2776,7 +2776,7 @@
         <v>0.12</v>
       </c>
       <c r="C42" s="15" t="n">
-        <v>4.687214751258258</v>
+        <v>4.350760846053808</v>
       </c>
     </row>
     <row r="43">
@@ -2789,7 +2789,7 @@
         <v>0.15</v>
       </c>
       <c r="C43" s="15" t="n">
-        <v>4.513703059440599</v>
+        <v>4.188743377015546</v>
       </c>
     </row>
     <row r="44">
@@ -2802,7 +2802,7 @@
         <v>0.18</v>
       </c>
       <c r="C44" s="15" t="n">
-        <v>4.34019136762294</v>
+        <v>4.026725907977284</v>
       </c>
     </row>
     <row r="45">
@@ -2815,7 +2815,7 @@
         <v>-0.2</v>
       </c>
       <c r="C45" s="15" t="n">
-        <v>4.865152294844356</v>
+        <v>4.520662427533516</v>
       </c>
     </row>
     <row r="46">
@@ -2828,7 +2828,7 @@
         <v>-0.1</v>
       </c>
       <c r="C46" s="15" t="n">
-        <v>4.829104589055693</v>
+        <v>4.485126964850331</v>
       </c>
     </row>
     <row r="47">
@@ -2841,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="C47" s="15" t="n">
-        <v>4.793056883267031</v>
+        <v>4.449591502167147</v>
       </c>
     </row>
     <row r="48">
@@ -2854,7 +2854,7 @@
         <v>0.1</v>
       </c>
       <c r="C48" s="15" t="n">
-        <v>4.757009177478368</v>
+        <v>4.414056039483962</v>
       </c>
     </row>
     <row r="49">
@@ -2867,7 +2867,7 @@
         <v>0.2</v>
       </c>
       <c r="C49" s="15" t="n">
-        <v>4.720961471689706</v>
+        <v>4.378520576800778</v>
       </c>
     </row>
   </sheetData>
@@ -2960,23 +2960,23 @@
       <c r="D2" s="16" t="n">
         <v>0.224</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="26">
         <f>'Income Statement'!E19</f>
         <v/>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="26">
         <f>'Income Statement'!F19</f>
         <v/>
       </c>
-      <c r="G2" s="25">
+      <c r="G2" s="26">
         <f>'Income Statement'!G19</f>
         <v/>
       </c>
-      <c r="H2" s="25">
+      <c r="H2" s="26">
         <f>'Income Statement'!H19</f>
         <v/>
       </c>
-      <c r="I2" s="25">
+      <c r="I2" s="26">
         <f>'Income Statement'!I19</f>
         <v/>
       </c>
@@ -2996,23 +2996,23 @@
       <c r="D3" s="16" t="n">
         <v>0.25843384</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E3" s="26">
         <f>'Balance Sheet'!E17</f>
         <v/>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="26">
         <f>'Balance Sheet'!F17</f>
         <v/>
       </c>
-      <c r="G3" s="25">
+      <c r="G3" s="26">
         <f>'Balance Sheet'!G17</f>
         <v/>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="26">
         <f>'Balance Sheet'!H17</f>
         <v/>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="26">
         <f>'Balance Sheet'!I17</f>
         <v/>
       </c>
@@ -3032,24 +3032,24 @@
       <c r="D4" s="16" t="n">
         <v>0.20793168</v>
       </c>
-      <c r="E4" s="25">
-        <f>Assumptions!$C$48</f>
-        <v/>
-      </c>
-      <c r="F4" s="25">
-        <f>Assumptions!$C$48</f>
-        <v/>
-      </c>
-      <c r="G4" s="25">
-        <f>Assumptions!$C$48</f>
-        <v/>
-      </c>
-      <c r="H4" s="25">
-        <f>Assumptions!$C$48</f>
-        <v/>
-      </c>
-      <c r="I4" s="25">
-        <f>Assumptions!$C$48</f>
+      <c r="E4" s="26">
+        <f>Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="F4" s="26">
+        <f>Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="G4" s="26">
+        <f>Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="H4" s="26">
+        <f>Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="I4" s="26">
+        <f>Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
@@ -3068,23 +3068,23 @@
       <c r="D5" s="13" t="n">
         <v>0.1192744709062695</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="29">
         <f>'Income Statement'!E9</f>
         <v/>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="29">
         <f>'Income Statement'!F9</f>
         <v/>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="29">
         <f>'Income Statement'!G9</f>
         <v/>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="29">
         <f>'Income Statement'!H9</f>
         <v/>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="29">
         <f>'Income Statement'!I9</f>
         <v/>
       </c>
@@ -3104,23 +3104,23 @@
       <c r="D6" s="13" t="n">
         <v>0.8649022124966298</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="29">
         <f>'Income Statement'!E18/'Balance Sheet'!E8</f>
         <v/>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="29">
         <f>'Income Statement'!F18/'Balance Sheet'!F8</f>
         <v/>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="29">
         <f>'Income Statement'!G18/'Balance Sheet'!G8</f>
         <v/>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="29">
         <f>'Income Statement'!H18/'Balance Sheet'!H8</f>
         <v/>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="29">
         <f>'Income Statement'!I18/'Balance Sheet'!I8</f>
         <v/>
       </c>
@@ -3140,23 +3140,23 @@
       <c r="D7" s="35" t="n">
         <v>0.6972056848571196</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>'Balance Sheet'!E16/'Income Statement'!E8</f>
         <v/>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>'Balance Sheet'!F16/'Income Statement'!F8</f>
         <v/>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="27">
         <f>'Balance Sheet'!G16/'Income Statement'!G8</f>
         <v/>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="27">
         <f>'Balance Sheet'!H16/'Income Statement'!H8</f>
         <v/>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="27">
         <f>'Balance Sheet'!I16/'Income Statement'!I8</f>
         <v/>
       </c>
@@ -3176,23 +3176,23 @@
       <c r="D8" s="13" t="n">
         <v>0.5438486806689132</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <f>'Income Statement'!E11/('Balance Sheet'!E8+'Balance Sheet'!E9+'Balance Sheet'!E16)</f>
         <v/>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <f>'Income Statement'!F11/('Balance Sheet'!F8+'Balance Sheet'!F9+'Balance Sheet'!F16)</f>
         <v/>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="29">
         <f>'Income Statement'!G11/('Balance Sheet'!G8+'Balance Sheet'!G9+'Balance Sheet'!G16)</f>
         <v/>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="29">
         <f>'Income Statement'!H11/('Balance Sheet'!H8+'Balance Sheet'!H9+'Balance Sheet'!H16)</f>
         <v/>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="29">
         <f>'Income Statement'!I11/('Balance Sheet'!I8+'Balance Sheet'!I9+'Balance Sheet'!I16)</f>
         <v/>
       </c>
@@ -3245,9 +3245,9 @@
           <t>Peer observations are a CROSS-CHECK. They are not the source of any number in this valuation: the reference multiple is triangulated from the company’s own history on the Relative &amp; Normalized sheet.</t>
         </is>
       </c>
-      <c r="B2" s="23" t="n"/>
-      <c r="C2" s="23" t="n"/>
-      <c r="D2" s="24" t="n"/>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="25" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -3375,7 +3375,7 @@
           <t>PEER AVERAGE (context only)</t>
         </is>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="28">
         <f>AVERAGE(B3:B10)</f>
         <v/>
       </c>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="B12" s="36">
-        <f>(Assumptions!$C$5+Assumptions!$C$18+Assumptions!$C$63)/'Income Statement'!D8</f>
+        <f>(Assumptions!$C$5+Assumptions!$C$18+Assumptions!$C$64)/'Income Statement'!D8</f>
         <v/>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -3801,7 +3801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3991,11 +3991,11 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>own five-year weekly regression vs its exchange</t>
+          <t>own five-year weekly regression against the published index of its own exchange</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>0.509</v>
+        <v>0.6494</v>
       </c>
     </row>
     <row r="12">
@@ -4157,193 +4157,182 @@
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Terminal beta</t>
+          <t>Terminal beta drift, as a fraction of the distance to a market beta of one</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>drift toward the market as transition risk rises</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="n">
-        <v>0.7</v>
+          <t>so the terminal beta is DERIVED from the measured one, not asserted beside it</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>0.389</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t>Terminal beta = measured beta + drift x (1 less measured beta)</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="C23" s="21">
+        <f>Assumptions!$C$11+Assumptions!$C$22*(1-Assumptions!$C$11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t>Terminal cost of equity = normalised risk-free + terminal beta x premium</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>calculated</t>
         </is>
       </c>
-      <c r="C23" s="19">
-        <f>Assumptions!$C$9+Assumptions!$C$22*Assumptions!$C$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="C24" s="19">
+        <f>Assumptions!$C$9+Assumptions!$C$23*Assumptions!$C$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Terminal debt weight</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>normalised capital structure</t>
         </is>
       </c>
-      <c r="C24" s="13" t="n">
+      <c r="C25" s="13" t="n">
         <v>0.1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Terminal cost of capital = terminal equity and debt weights on their costs</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>calculated</t>
         </is>
       </c>
-      <c r="C25" s="19">
-        <f>(1-Assumptions!$C$24)*Assumptions!$C$23+Assumptions!$C$24*Assumptions!$C$17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Long-run growth after the forecast period</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>below domestic inflation</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>0.015</v>
+      <c r="C26" s="19">
+        <f>(1-Assumptions!$C$25)*Assumptions!$C$24+Assumptions!$C$25*Assumptions!$C$17</f>
+        <v/>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>Long-run growth after the forecast period</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>below domestic inflation</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>Terminal return on invested capital</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>fade from the realised return</t>
         </is>
       </c>
-      <c r="C27" s="13" t="n">
+      <c r="C28" s="13" t="n">
         <v>0.25</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>Volume and price drivers</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr"/>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Retail fuel volume growth</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>network and mobility, less transition drag</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E29" s="18" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="F29" s="18" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G29" s="18" t="n">
-        <v>0.012</v>
-      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Commercial fuel volume growth</t>
+          <t>Retail fuel volume growth</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>aviation growth, corporate rationalisation</t>
+          <t>network and mobility, less transition drag</t>
         </is>
       </c>
       <c r="C30" s="18" t="n">
-        <v>0.03</v>
+        <v>0.012</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="F30" s="18" t="n">
-        <v>0.018</v>
+        <v>0.015</v>
       </c>
       <c r="G30" s="18" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Realised retail price per litre (AED)</t>
+          <t>Commercial fuel volume growth</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>crude-linked price path</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>2.363</v>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>2.387</v>
-      </c>
-      <c r="G31" s="16" t="n">
-        <v>2.411</v>
+          <t>aviation growth, corporate rationalisation</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G31" s="18" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Realised commercial price per litre (AED)</t>
+          <t>Realised retail price per litre (AED)</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -4352,61 +4341,61 @@
         </is>
       </c>
       <c r="C32" s="16" t="n">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="D32" s="16" t="n">
-        <v>2.95</v>
+        <v>2.34</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>2.98</v>
+        <v>2.363</v>
       </c>
       <c r="F32" s="16" t="n">
-        <v>3.01</v>
+        <v>2.387</v>
       </c>
       <c r="G32" s="16" t="n">
-        <v>3.04</v>
+        <v>2.411</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Retail margin per litre, escalation</t>
+          <t>Realised commercial price per litre (AED)</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>domestic escalator</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G33" s="18" t="n">
-        <v>0.02</v>
+          <t>crude-linked price path</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="F33" s="16" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="G33" s="16" t="n">
+        <v>3.04</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Commercial margin per litre, escalation</t>
+          <t>Retail margin per litre, escalation</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>realised step then domestic escalator</t>
+          <t>domestic escalator</t>
         </is>
       </c>
       <c r="C34" s="18" t="n">
-        <v>0.17</v>
+        <v>0.02</v>
       </c>
       <c r="D34" s="18" t="n">
         <v>0.02</v>
@@ -4424,278 +4413,290 @@
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Non-fuel retail revenue growth</t>
+          <t>Commercial margin per litre, escalation</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>company's own doubling target to 2030</t>
+          <t>realised step then domestic escalator</t>
         </is>
       </c>
       <c r="C35" s="18" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="D35" s="18" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="F35" s="18" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G35" s="18" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Non-fuel retail gross margin</t>
+          <t>Non-fuel retail revenue growth</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>realised first half 2026</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="D36" s="13" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E36" s="13" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F36" s="13" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="G36" s="13" t="n">
-        <v>0.5600000000000001</v>
+          <t>company's own doubling target to 2030</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G36" s="18" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Inventory movement, normalised frame (AED m)</t>
+          <t>Non-fuel retail gross margin</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>realised first half only, nil thereafter</t>
-        </is>
-      </c>
-      <c r="C37" s="20" t="n">
-        <v>762</v>
-      </c>
-      <c r="D37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="20" t="n">
-        <v>0</v>
+          <t>realised first half 2026</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
+          <t>Inventory movement, normalised frame (AED m)</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>realised first half only, nil thereafter</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="n">
+        <v>762</v>
+      </c>
+      <c r="D38" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
           <t>Inventory movement, through-cycle frame (AED m)</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>FY2024-FY2025 average carried forward</t>
         </is>
       </c>
-      <c r="C38" s="20" t="n">
+      <c r="C39" s="20" t="n">
         <v>950</v>
       </c>
-      <c r="D38" s="20" t="n">
+      <c r="D39" s="20" t="n">
         <v>295</v>
       </c>
-      <c r="E38" s="20" t="n">
+      <c r="E39" s="20" t="n">
         <v>295</v>
       </c>
-      <c r="F38" s="20" t="n">
+      <c r="F39" s="20" t="n">
         <v>295</v>
       </c>
-      <c r="G38" s="20" t="n">
+      <c r="G39" s="20" t="n">
         <v>295</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>Cost, capital spending and working capital</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr"/>
-      <c r="C39" s="2" t="inlineStr"/>
-      <c r="D39" s="2" t="inlineStr"/>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Cash operating cost growth</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>domestic escalator plus network, less efficiency</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D40" s="18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E40" s="18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F40" s="18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G40" s="18" t="n">
-        <v>0.04</v>
-      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Other income growth</t>
+          <t>Cash operating cost growth</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>domestic escalator</t>
+          <t>domestic escalator plus network, less efficiency</t>
         </is>
       </c>
       <c r="C41" s="18" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="E41" s="18" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Impairments and other operating expenses (AED m)</t>
+          <t>Other income growth</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>realised then normalised</t>
-        </is>
-      </c>
-      <c r="C42" s="20" t="n">
-        <v>360</v>
-      </c>
-      <c r="D42" s="20" t="n">
-        <v>220</v>
-      </c>
-      <c r="E42" s="20" t="n">
-        <v>225</v>
-      </c>
-      <c r="F42" s="20" t="n">
-        <v>230</v>
-      </c>
-      <c r="G42" s="20" t="n">
-        <v>235</v>
+          <t>domestic escalator</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F42" s="18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G42" s="18" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Depreciation and amortisation (AED m)</t>
+          <t>Impairments and other operating expenses (AED m)</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>grown on the asset base</t>
+          <t>realised then normalised</t>
         </is>
       </c>
       <c r="C43" s="20" t="n">
-        <v>800</v>
+        <v>360</v>
       </c>
       <c r="D43" s="20" t="n">
-        <v>830</v>
+        <v>220</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>862</v>
+        <v>225</v>
       </c>
       <c r="F43" s="20" t="n">
-        <v>894</v>
+        <v>230</v>
       </c>
       <c r="G43" s="20" t="n">
-        <v>926</v>
+        <v>235</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Capital expenditure (AED m)</t>
+          <t>Depreciation and amortisation (AED m)</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>company's own FY2026 guidance, then network</t>
+          <t>grown on the asset base</t>
         </is>
       </c>
       <c r="C44" s="20" t="n">
-        <v>1010</v>
+        <v>800</v>
       </c>
       <c r="D44" s="20" t="n">
-        <v>1060</v>
+        <v>830</v>
       </c>
       <c r="E44" s="20" t="n">
-        <v>1100</v>
+        <v>862</v>
       </c>
       <c r="F44" s="20" t="n">
-        <v>1140</v>
+        <v>894</v>
       </c>
       <c r="G44" s="20" t="n">
-        <v>1180</v>
+        <v>926</v>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Receivable days including parent balances</t>
+          <t>Capital expenditure (AED m)</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>FY2025 statements</t>
-        </is>
-      </c>
-      <c r="C45" s="15" t="n">
-        <v>34.47981727637454</v>
+          <t>company's own FY2026 guidance, then network</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D45" s="20" t="n">
+        <v>1060</v>
+      </c>
+      <c r="E45" s="20" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F45" s="20" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G45" s="20" t="n">
+        <v>1180</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Inventory days</t>
+          <t>Receivable days including parent balances</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -4704,13 +4705,13 @@
         </is>
       </c>
       <c r="C46" s="15" t="n">
-        <v>19.84754045195324</v>
+        <v>34.47981727637454</v>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Payable days including parent balances</t>
+          <t>Inventory days</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -4719,71 +4720,71 @@
         </is>
       </c>
       <c r="C47" s="15" t="n">
-        <v>85.25432762248899</v>
+        <v>19.84754045195324</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Dividend per share (AED)</t>
+          <t>Payable days including parent balances</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>stated policy</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="n">
-        <v>0.2057</v>
+          <t>FY2025 statements</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="n">
+        <v>85.25432762248899</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
+          <t>Dividend per share (AED)</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>stated policy</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="n">
+        <v>0.2057</v>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
           <t>Dividend payout ratio</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>paid against earnings since listing</t>
         </is>
       </c>
-      <c r="C49" s="13" t="n">
+      <c r="C50" s="13" t="n">
         <v>0.92</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
         <is>
           <t>Opening position, from the audited FY2025 balance sheet</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr"/>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>Retail fuel volume, FY2025 (million litres)</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>disclosure</t>
-        </is>
-      </c>
-      <c r="C51" s="20" t="n">
-        <v>11042</v>
-      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Commercial fuel volume, FY2025 (million litres)</t>
+          <t>Retail fuel volume, FY2025 (million litres)</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
@@ -4792,28 +4793,28 @@
         </is>
       </c>
       <c r="C52" s="20" t="n">
-        <v>4668</v>
+        <v>11042</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Retail margin per litre, FY2025 (AED)</t>
+          <t>Commercial fuel volume, FY2025 (million litres)</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>unit build: segment gross profit less inventory movement, over volume</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="n">
-        <v>0.3542836442673429</v>
+          <t>disclosure</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="n">
+        <v>4668</v>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Commercial margin per litre, FY2025 (AED)</t>
+          <t>Retail margin per litre, FY2025 (AED)</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
@@ -4822,28 +4823,28 @@
         </is>
       </c>
       <c r="C54" s="16" t="n">
-        <v>0.367395029991431</v>
+        <v>0.3542836442673429</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Non-fuel retail revenue, FY2025 (AED m)</t>
+          <t>Commercial margin per litre, FY2025 (AED)</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>disclosure</t>
-        </is>
-      </c>
-      <c r="C55" s="20" t="n">
-        <v>1783.747</v>
+          <t>unit build: segment gross profit less inventory movement, over volume</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="n">
+        <v>0.367395029991431</v>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Cash operating costs, FY2025 (AED m)</t>
+          <t>Non-fuel retail revenue, FY2025 (AED m)</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
@@ -4852,13 +4853,13 @@
         </is>
       </c>
       <c r="C56" s="20" t="n">
-        <v>2547.6</v>
+        <v>1783.747</v>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Other income, FY2025 (AED m)</t>
+          <t>Cash operating costs, FY2025 (AED m)</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
@@ -4867,13 +4868,13 @@
         </is>
       </c>
       <c r="C57" s="20" t="n">
-        <v>167.665</v>
+        <v>2547.6</v>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Fixed and right-of-use assets, FY2025 (AED m)</t>
+          <t>Other income, FY2025 (AED m)</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
@@ -4882,13 +4883,13 @@
         </is>
       </c>
       <c r="C58" s="20" t="n">
-        <v>9478.001</v>
+        <v>167.665</v>
       </c>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Goodwill, intangibles and other non-current, FY2025 (AED m)</t>
+          <t>Fixed and right-of-use assets, FY2025 (AED m)</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -4897,13 +4898,13 @@
         </is>
       </c>
       <c r="C59" s="20" t="n">
-        <v>671.2729999999999</v>
+        <v>9478.001</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Equity attributable to owners, FY2025 (AED m)</t>
+          <t>Goodwill, intangibles and other non-current, FY2025 (AED m)</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
@@ -4912,13 +4913,13 @@
         </is>
       </c>
       <c r="C60" s="20" t="n">
-        <v>3230.423</v>
+        <v>671.2729999999999</v>
       </c>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Non-controlling interests, FY2025 (AED m)</t>
+          <t>Equity attributable to owners, FY2025 (AED m)</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -4927,13 +4928,13 @@
         </is>
       </c>
       <c r="C61" s="20" t="n">
-        <v>230.374</v>
+        <v>3230.423</v>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Borrowings, FY2025 (AED m)</t>
+          <t>Non-controlling interests, FY2025 (AED m)</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
@@ -4942,13 +4943,13 @@
         </is>
       </c>
       <c r="C62" s="20" t="n">
-        <v>5545.975</v>
+        <v>230.374</v>
       </c>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Lease liabilities, FY2025 (AED m)</t>
+          <t>Borrowings, FY2025 (AED m)</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -4957,13 +4958,13 @@
         </is>
       </c>
       <c r="C63" s="20" t="n">
-        <v>1446.327</v>
+        <v>5545.975</v>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Provisions and deferred tax, FY2025 (AED m)</t>
+          <t>Lease liabilities, FY2025 (AED m)</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
@@ -4972,13 +4973,13 @@
         </is>
       </c>
       <c r="C64" s="20" t="n">
-        <v>460.12</v>
+        <v>1446.327</v>
       </c>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Term deposits, FY2025 (AED m)</t>
+          <t>Provisions and deferred tax, FY2025 (AED m)</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -4987,28 +4988,28 @@
         </is>
       </c>
       <c r="C65" s="20" t="n">
-        <v>200</v>
+        <v>460.12</v>
       </c>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Finance costs, held at the FY2025 level (AED m)</t>
+          <t>Term deposits, FY2025 (AED m)</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>disclosure, held flat</t>
+          <t>disclosure</t>
         </is>
       </c>
       <c r="C66" s="20" t="n">
-        <v>402.945</v>
+        <v>200</v>
       </c>
     </row>
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Interest income, held at the FY2025 level (AED m)</t>
+          <t>Finance costs, held at the FY2025 level (AED m)</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
@@ -5017,21 +5018,36 @@
         </is>
       </c>
       <c r="C67" s="20" t="n">
-        <v>71.274</v>
+        <v>402.945</v>
       </c>
     </row>
     <row r="68" ht="24" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
+          <t>Interest income, held at the FY2025 level (AED m)</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>disclosure, held flat</t>
+        </is>
+      </c>
+      <c r="C68" s="20" t="n">
+        <v>71.274</v>
+      </c>
+    </row>
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
           <t>Non-controlling share of profit (AED m)</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>disclosure, held flat</t>
         </is>
       </c>
-      <c r="C68" s="20" t="n">
+      <c r="C69" s="20" t="n">
         <v>57.042</v>
       </c>
     </row>
@@ -5077,11 +5093,11 @@
           <t>Present value of five years of free cash flow</t>
         </is>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="22">
         <f>DCF!G14</f>
         <v/>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="22">
         <f>DCF!G24</f>
         <v/>
       </c>
@@ -5092,11 +5108,11 @@
           <t>Present value of the terminal value</t>
         </is>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="22">
         <f>DCF!B30</f>
         <v/>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="22">
         <f>DCF!B38</f>
         <v/>
       </c>
@@ -5107,11 +5123,11 @@
           <t>ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B4" s="22">
+      <c r="B4" s="23">
         <f>B2+B3</f>
         <v/>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="23">
         <f>C2+C3</f>
         <v/>
       </c>
@@ -5137,11 +5153,11 @@
           <t>Less net debt excluding leases</t>
         </is>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="22">
         <f>-Assumptions!$C$18</f>
         <v/>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="22">
         <f>-Assumptions!$C$18</f>
         <v/>
       </c>
@@ -5152,12 +5168,12 @@
           <t>Less lease liabilities</t>
         </is>
       </c>
-      <c r="B7" s="21">
-        <f>-Assumptions!$C$63</f>
-        <v/>
-      </c>
-      <c r="C7" s="21">
-        <f>-Assumptions!$C$63</f>
+      <c r="B7" s="22">
+        <f>-Assumptions!$C$64</f>
+        <v/>
+      </c>
+      <c r="C7" s="22">
+        <f>-Assumptions!$C$64</f>
         <v/>
       </c>
     </row>
@@ -5167,12 +5183,12 @@
           <t>Less non-controlling interests</t>
         </is>
       </c>
-      <c r="B8" s="21">
-        <f>-Assumptions!$C$61</f>
-        <v/>
-      </c>
-      <c r="C8" s="21">
-        <f>-Assumptions!$C$61</f>
+      <c r="B8" s="22">
+        <f>-Assumptions!$C$62</f>
+        <v/>
+      </c>
+      <c r="C8" s="22">
+        <f>-Assumptions!$C$62</f>
         <v/>
       </c>
     </row>
@@ -5182,11 +5198,11 @@
           <t>EQUITY VALUE</t>
         </is>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="23">
         <f>B4+B6+B7+B8</f>
         <v/>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="23">
         <f>C4+C6+C7+C8</f>
         <v/>
       </c>
@@ -5267,12 +5283,12 @@
           <t>Revenue is volume times realised price. Gross profit is volume times margin per litre. They are different questions: the price is a pass-through of crude and moves revenue and cost together, while the margin per litre is what the business earns.</t>
         </is>
       </c>
-      <c r="B2" s="23" t="n"/>
-      <c r="C2" s="23" t="n"/>
-      <c r="D2" s="23" t="n"/>
-      <c r="E2" s="23" t="n"/>
-      <c r="F2" s="23" t="n"/>
-      <c r="G2" s="24" t="n"/>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="24" t="n"/>
+      <c r="G2" s="25" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -5283,24 +5299,24 @@
       <c r="B3" s="20" t="n">
         <v>11042</v>
       </c>
-      <c r="C3" s="21">
-        <f>Assumptions!$C$51*(1+Assumptions!C$29)</f>
-        <v/>
-      </c>
-      <c r="D3" s="21">
-        <f>C3*(1+Assumptions!D$29)</f>
-        <v/>
-      </c>
-      <c r="E3" s="21">
-        <f>D3*(1+Assumptions!E$29)</f>
-        <v/>
-      </c>
-      <c r="F3" s="21">
-        <f>E3*(1+Assumptions!F$29)</f>
-        <v/>
-      </c>
-      <c r="G3" s="21">
-        <f>F3*(1+Assumptions!G$29)</f>
+      <c r="C3" s="22">
+        <f>Assumptions!$C$52*(1+Assumptions!C$30)</f>
+        <v/>
+      </c>
+      <c r="D3" s="22">
+        <f>C3*(1+Assumptions!D$30)</f>
+        <v/>
+      </c>
+      <c r="E3" s="22">
+        <f>D3*(1+Assumptions!E$30)</f>
+        <v/>
+      </c>
+      <c r="F3" s="22">
+        <f>E3*(1+Assumptions!F$30)</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>F3*(1+Assumptions!G$30)</f>
         <v/>
       </c>
     </row>
@@ -5313,24 +5329,24 @@
       <c r="B4" s="20" t="n">
         <v>4668</v>
       </c>
-      <c r="C4" s="21">
-        <f>Assumptions!$C$52*(1+Assumptions!C$30)</f>
-        <v/>
-      </c>
-      <c r="D4" s="21">
-        <f>C4*(1+Assumptions!D$30)</f>
-        <v/>
-      </c>
-      <c r="E4" s="21">
-        <f>D4*(1+Assumptions!E$30)</f>
-        <v/>
-      </c>
-      <c r="F4" s="21">
-        <f>E4*(1+Assumptions!F$30)</f>
-        <v/>
-      </c>
-      <c r="G4" s="21">
-        <f>F4*(1+Assumptions!G$30)</f>
+      <c r="C4" s="22">
+        <f>Assumptions!$C$53*(1+Assumptions!C$31)</f>
+        <v/>
+      </c>
+      <c r="D4" s="22">
+        <f>C4*(1+Assumptions!D$31)</f>
+        <v/>
+      </c>
+      <c r="E4" s="22">
+        <f>D4*(1+Assumptions!E$31)</f>
+        <v/>
+      </c>
+      <c r="F4" s="22">
+        <f>E4*(1+Assumptions!F$31)</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>F4*(1+Assumptions!G$31)</f>
         <v/>
       </c>
     </row>
@@ -5373,24 +5389,24 @@
       <c r="B6" s="16" t="n">
         <v>2.064570458250317</v>
       </c>
-      <c r="C6" s="25">
-        <f>Assumptions!C$31</f>
-        <v/>
-      </c>
-      <c r="D6" s="25">
-        <f>Assumptions!D$31</f>
-        <v/>
-      </c>
-      <c r="E6" s="25">
-        <f>Assumptions!E$31</f>
-        <v/>
-      </c>
-      <c r="F6" s="25">
-        <f>Assumptions!F$31</f>
-        <v/>
-      </c>
-      <c r="G6" s="25">
-        <f>Assumptions!G$31</f>
+      <c r="C6" s="26">
+        <f>Assumptions!C$32</f>
+        <v/>
+      </c>
+      <c r="D6" s="26">
+        <f>Assumptions!D$32</f>
+        <v/>
+      </c>
+      <c r="E6" s="26">
+        <f>Assumptions!E$32</f>
+        <v/>
+      </c>
+      <c r="F6" s="26">
+        <f>Assumptions!F$32</f>
+        <v/>
+      </c>
+      <c r="G6" s="26">
+        <f>Assumptions!G$32</f>
         <v/>
       </c>
     </row>
@@ -5403,24 +5419,24 @@
       <c r="B7" s="16" t="n">
         <v>2.424139460154242</v>
       </c>
-      <c r="C7" s="25">
-        <f>Assumptions!C$32</f>
-        <v/>
-      </c>
-      <c r="D7" s="25">
-        <f>Assumptions!D$32</f>
-        <v/>
-      </c>
-      <c r="E7" s="25">
-        <f>Assumptions!E$32</f>
-        <v/>
-      </c>
-      <c r="F7" s="25">
-        <f>Assumptions!F$32</f>
-        <v/>
-      </c>
-      <c r="G7" s="25">
-        <f>Assumptions!G$32</f>
+      <c r="C7" s="26">
+        <f>Assumptions!C$33</f>
+        <v/>
+      </c>
+      <c r="D7" s="26">
+        <f>Assumptions!D$33</f>
+        <v/>
+      </c>
+      <c r="E7" s="26">
+        <f>Assumptions!E$33</f>
+        <v/>
+      </c>
+      <c r="F7" s="26">
+        <f>Assumptions!F$33</f>
+        <v/>
+      </c>
+      <c r="G7" s="26">
+        <f>Assumptions!G$33</f>
         <v/>
       </c>
     </row>
@@ -5433,23 +5449,23 @@
       <c r="B8" s="20" t="n">
         <v>22796.987</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="22">
         <f>C3*C6</f>
         <v/>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="22">
         <f>D3*D6</f>
         <v/>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="22">
         <f>E3*E6</f>
         <v/>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="22">
         <f>F3*F6</f>
         <v/>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="22">
         <f>G3*G6</f>
         <v/>
       </c>
@@ -5463,23 +5479,23 @@
       <c r="B9" s="20" t="n">
         <v>11315.883</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="22">
         <f>C4*C7</f>
         <v/>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="22">
         <f>D4*D7</f>
         <v/>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="22">
         <f>E4*E7</f>
         <v/>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="22">
         <f>F4*F7</f>
         <v/>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="22">
         <f>G4*G7</f>
         <v/>
       </c>
@@ -5493,24 +5509,24 @@
       <c r="B10" s="20" t="n">
         <v>1783.747</v>
       </c>
-      <c r="C10" s="21">
-        <f>Assumptions!$C$55*(1+Assumptions!C$35)</f>
-        <v/>
-      </c>
-      <c r="D10" s="21">
-        <f>C10*(1+Assumptions!D$35)</f>
-        <v/>
-      </c>
-      <c r="E10" s="21">
-        <f>D10*(1+Assumptions!E$35)</f>
-        <v/>
-      </c>
-      <c r="F10" s="21">
-        <f>E10*(1+Assumptions!F$35)</f>
-        <v/>
-      </c>
-      <c r="G10" s="21">
-        <f>F10*(1+Assumptions!G$35)</f>
+      <c r="C10" s="22">
+        <f>Assumptions!$C$56*(1+Assumptions!C$36)</f>
+        <v/>
+      </c>
+      <c r="D10" s="22">
+        <f>C10*(1+Assumptions!D$36)</f>
+        <v/>
+      </c>
+      <c r="E10" s="22">
+        <f>D10*(1+Assumptions!E$36)</f>
+        <v/>
+      </c>
+      <c r="F10" s="22">
+        <f>E10*(1+Assumptions!F$36)</f>
+        <v/>
+      </c>
+      <c r="G10" s="22">
+        <f>F10*(1+Assumptions!G$36)</f>
         <v/>
       </c>
     </row>
@@ -5523,23 +5539,23 @@
       <c r="B11" s="20" t="n">
         <v>35896.617</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="23">
         <f>C8+C9+C10</f>
         <v/>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="23">
         <f>D8+D9+D10</f>
         <v/>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="23">
         <f>E8+E9+E10</f>
         <v/>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="23">
         <f>F8+F9+F10</f>
         <v/>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="23">
         <f>G8+G9+G10</f>
         <v/>
       </c>
@@ -5553,24 +5569,24 @@
       <c r="B12" s="16" t="n">
         <v>0.3542836442673429</v>
       </c>
-      <c r="C12" s="25">
-        <f>Assumptions!$C$53*(1+Assumptions!C$33)</f>
-        <v/>
-      </c>
-      <c r="D12" s="25">
-        <f>C12*(1+Assumptions!D$33)</f>
-        <v/>
-      </c>
-      <c r="E12" s="25">
-        <f>D12*(1+Assumptions!E$33)</f>
-        <v/>
-      </c>
-      <c r="F12" s="25">
-        <f>E12*(1+Assumptions!F$33)</f>
-        <v/>
-      </c>
-      <c r="G12" s="25">
-        <f>F12*(1+Assumptions!G$33)</f>
+      <c r="C12" s="26">
+        <f>Assumptions!$C$54*(1+Assumptions!C$34)</f>
+        <v/>
+      </c>
+      <c r="D12" s="26">
+        <f>C12*(1+Assumptions!D$34)</f>
+        <v/>
+      </c>
+      <c r="E12" s="26">
+        <f>D12*(1+Assumptions!E$34)</f>
+        <v/>
+      </c>
+      <c r="F12" s="26">
+        <f>E12*(1+Assumptions!F$34)</f>
+        <v/>
+      </c>
+      <c r="G12" s="26">
+        <f>F12*(1+Assumptions!G$34)</f>
         <v/>
       </c>
     </row>
@@ -5583,24 +5599,24 @@
       <c r="B13" s="16" t="n">
         <v>0.367395029991431</v>
       </c>
-      <c r="C13" s="25">
-        <f>Assumptions!$C$54*(1+Assumptions!C$34)</f>
-        <v/>
-      </c>
-      <c r="D13" s="25">
-        <f>C13*(1+Assumptions!D$34)</f>
-        <v/>
-      </c>
-      <c r="E13" s="25">
-        <f>D13*(1+Assumptions!E$34)</f>
-        <v/>
-      </c>
-      <c r="F13" s="25">
-        <f>E13*(1+Assumptions!F$34)</f>
-        <v/>
-      </c>
-      <c r="G13" s="25">
-        <f>F13*(1+Assumptions!G$34)</f>
+      <c r="C13" s="26">
+        <f>Assumptions!$C$55*(1+Assumptions!C$35)</f>
+        <v/>
+      </c>
+      <c r="D13" s="26">
+        <f>C13*(1+Assumptions!D$35)</f>
+        <v/>
+      </c>
+      <c r="E13" s="26">
+        <f>D13*(1+Assumptions!E$35)</f>
+        <v/>
+      </c>
+      <c r="F13" s="26">
+        <f>E13*(1+Assumptions!F$35)</f>
+        <v/>
+      </c>
+      <c r="G13" s="26">
+        <f>F13*(1+Assumptions!G$35)</f>
         <v/>
       </c>
     </row>
@@ -5613,23 +5629,23 @@
       <c r="B14" s="20" t="n">
         <v>3912</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="22">
         <f>C3*C12</f>
         <v/>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="22">
         <f>D3*D12</f>
         <v/>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="22">
         <f>E3*E12</f>
         <v/>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="22">
         <f>F3*F12</f>
         <v/>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="22">
         <f>G3*G12</f>
         <v/>
       </c>
@@ -5643,23 +5659,23 @@
       <c r="B15" s="20" t="n">
         <v>1715</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="22">
         <f>C4*C13</f>
         <v/>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="22">
         <f>D4*D13</f>
         <v/>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="22">
         <f>E4*E13</f>
         <v/>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="22">
         <f>F4*F13</f>
         <v/>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="22">
         <f>G4*G13</f>
         <v/>
       </c>
@@ -5673,24 +5689,24 @@
       <c r="B16" s="20" t="n">
         <v>984</v>
       </c>
-      <c r="C16" s="21">
-        <f>C10*Assumptions!C$36</f>
-        <v/>
-      </c>
-      <c r="D16" s="21">
-        <f>D10*Assumptions!D$36</f>
-        <v/>
-      </c>
-      <c r="E16" s="21">
-        <f>E10*Assumptions!E$36</f>
-        <v/>
-      </c>
-      <c r="F16" s="21">
-        <f>F10*Assumptions!F$36</f>
-        <v/>
-      </c>
-      <c r="G16" s="21">
-        <f>G10*Assumptions!G$36</f>
+      <c r="C16" s="22">
+        <f>C10*Assumptions!C$37</f>
+        <v/>
+      </c>
+      <c r="D16" s="22">
+        <f>D10*Assumptions!D$37</f>
+        <v/>
+      </c>
+      <c r="E16" s="22">
+        <f>E10*Assumptions!E$37</f>
+        <v/>
+      </c>
+      <c r="F16" s="22">
+        <f>F10*Assumptions!F$37</f>
+        <v/>
+      </c>
+      <c r="G16" s="22">
+        <f>G10*Assumptions!G$37</f>
         <v/>
       </c>
     </row>
@@ -5703,23 +5719,23 @@
       <c r="B17" s="20" t="n">
         <v>6610.79</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="23">
         <f>C14+C15+C16</f>
         <v/>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="23">
         <f>D14+D15+D16</f>
         <v/>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="23">
         <f>E14+E15+E16</f>
         <v/>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="23">
         <f>F14+F15+F16</f>
         <v/>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="23">
         <f>G14+G15+G16</f>
         <v/>
       </c>
@@ -5733,24 +5749,24 @@
       <c r="B18" s="20" t="n">
         <v>335</v>
       </c>
-      <c r="C18" s="21">
-        <f>Assumptions!C$37</f>
-        <v/>
-      </c>
-      <c r="D18" s="21">
-        <f>Assumptions!D$37</f>
-        <v/>
-      </c>
-      <c r="E18" s="21">
-        <f>Assumptions!E$37</f>
-        <v/>
-      </c>
-      <c r="F18" s="21">
-        <f>Assumptions!F$37</f>
-        <v/>
-      </c>
-      <c r="G18" s="21">
-        <f>Assumptions!G$37</f>
+      <c r="C18" s="22">
+        <f>Assumptions!C$38</f>
+        <v/>
+      </c>
+      <c r="D18" s="22">
+        <f>Assumptions!D$38</f>
+        <v/>
+      </c>
+      <c r="E18" s="22">
+        <f>Assumptions!E$38</f>
+        <v/>
+      </c>
+      <c r="F18" s="22">
+        <f>Assumptions!F$38</f>
+        <v/>
+      </c>
+      <c r="G18" s="22">
+        <f>Assumptions!G$38</f>
         <v/>
       </c>
     </row>
@@ -5763,24 +5779,24 @@
       <c r="B19" s="20" t="n">
         <v>335</v>
       </c>
-      <c r="C19" s="21">
-        <f>Assumptions!C$38</f>
-        <v/>
-      </c>
-      <c r="D19" s="21">
-        <f>Assumptions!D$38</f>
-        <v/>
-      </c>
-      <c r="E19" s="21">
-        <f>Assumptions!E$38</f>
-        <v/>
-      </c>
-      <c r="F19" s="21">
-        <f>Assumptions!F$38</f>
-        <v/>
-      </c>
-      <c r="G19" s="21">
-        <f>Assumptions!G$38</f>
+      <c r="C19" s="22">
+        <f>Assumptions!C$39</f>
+        <v/>
+      </c>
+      <c r="D19" s="22">
+        <f>Assumptions!D$39</f>
+        <v/>
+      </c>
+      <c r="E19" s="22">
+        <f>Assumptions!E$39</f>
+        <v/>
+      </c>
+      <c r="F19" s="22">
+        <f>Assumptions!F$39</f>
+        <v/>
+      </c>
+      <c r="G19" s="22">
+        <f>Assumptions!G$39</f>
         <v/>
       </c>
     </row>
@@ -5793,23 +5809,23 @@
       <c r="B20" s="20" t="n">
         <v>6945.79</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="23">
         <f>C17+C18</f>
         <v/>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="23">
         <f>D17+D18</f>
         <v/>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="23">
         <f>E17+E18</f>
         <v/>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="23">
         <f>F17+F18</f>
         <v/>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="23">
         <f>G17+G18</f>
         <v/>
       </c>
@@ -5823,23 +5839,23 @@
       <c r="B21" s="20" t="n">
         <v>6945.79</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="23">
         <f>C17+C19</f>
         <v/>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="23">
         <f>D17+D19</f>
         <v/>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="23">
         <f>E17+E19</f>
         <v/>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="23">
         <f>F17+F19</f>
         <v/>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="23">
         <f>G17+G19</f>
         <v/>
       </c>
@@ -5895,9 +5911,9 @@
           <t>Triangulation: the reference multiple is the AVERAGE of three independently-derived readings, taken on the sheet rather than asserted.</t>
         </is>
       </c>
-      <c r="B2" s="23" t="n"/>
-      <c r="C2" s="23" t="n"/>
-      <c r="D2" s="24" t="n"/>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="25" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -5905,7 +5921,7 @@
           <t>Own trailing multiple today</t>
         </is>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="27">
         <f>Assumptions!$C$3/'Income Statement'!D19</f>
         <v/>
       </c>
@@ -5921,7 +5937,7 @@
           <t>Own three-year average multiple</t>
         </is>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <f>(Assumptions!$C$3/'Income Statement'!B19+Assumptions!$C$3/'Income Statement'!C19+Assumptions!$C$3/'Income Statement'!D19)/3</f>
         <v/>
       </c>
@@ -5937,8 +5953,8 @@
           <t>Multiple the company’s own economics justify</t>
         </is>
       </c>
-      <c r="B5" s="26">
-        <f>Assumptions!$C$49*(1+Assumptions!$C$26)/(Assumptions!$C$12-Assumptions!$C$26)</f>
+      <c r="B5" s="27">
+        <f>Assumptions!$C$50*(1+Assumptions!$C$27)/(Assumptions!$C$12-Assumptions!$C$27)</f>
         <v/>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -5953,7 +5969,7 @@
           <t>REFERENCE MULTIPLE — the average of the three</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="28">
         <f>(B3+B4+B5)/3</f>
         <v/>
       </c>
@@ -5985,8 +6001,8 @@
           <t>First forecast year earnings per share — Frame B (AED)</t>
         </is>
       </c>
-      <c r="B8" s="25">
-        <f>(DCF!B18+Assumptions!$C$67-Assumptions!$C$66)*(1-Assumptions!$C$16)/Assumptions!$C$4-Assumptions!$C$68/Assumptions!$C$4</f>
+      <c r="B8" s="26">
+        <f>(DCF!B18+Assumptions!$C$68-Assumptions!$C$67)*(1-Assumptions!$C$16)/Assumptions!$C$4-Assumptions!$C$69/Assumptions!$C$4</f>
         <v/>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -6017,7 +6033,7 @@
           <t>Normalised EBITDA — structural gross profit only, no inventory movement</t>
         </is>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="22">
         <f>Segments!C17+'Income Statement'!E5+'Income Statement'!E6+'Income Statement'!E7</f>
         <v/>
       </c>
@@ -6029,8 +6045,8 @@
           <t>Normalised EBIT</t>
         </is>
       </c>
-      <c r="B11" s="21">
-        <f>B10-Assumptions!C$43</f>
+      <c r="B11" s="22">
+        <f>B10-Assumptions!C$44</f>
         <v/>
       </c>
       <c r="D11" s="8" t="inlineStr"/>
@@ -6041,7 +6057,7 @@
           <t>Normalised NOPAT</t>
         </is>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="22">
         <f>B11*(1-Assumptions!$C$16)</f>
         <v/>
       </c>
@@ -6053,8 +6069,8 @@
           <t>Normalised enterprise value = NOPAT / (cost of capital less growth)</t>
         </is>
       </c>
-      <c r="B13" s="21">
-        <f>B12/(Assumptions!$C$21-Assumptions!$C$26)</f>
+      <c r="B13" s="22">
+        <f>B12/(Assumptions!$C$21-Assumptions!$C$27)</f>
         <v/>
       </c>
       <c r="D13" s="8" t="inlineStr"/>
@@ -6065,8 +6081,8 @@
           <t>Normalised equity value</t>
         </is>
       </c>
-      <c r="B14" s="21">
-        <f>B13-Assumptions!$C$18-Assumptions!$C$63-Assumptions!$C$61</f>
+      <c r="B14" s="22">
+        <f>B13-Assumptions!$C$18-Assumptions!$C$64-Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="D14" s="8" t="inlineStr"/>
@@ -6089,8 +6105,8 @@
           <t>Book value per share (AED)</t>
         </is>
       </c>
-      <c r="B16" s="25">
-        <f>Assumptions!$C$60/Assumptions!$C$4</f>
+      <c r="B16" s="26">
+        <f>Assumptions!$C$61/Assumptions!$C$4</f>
         <v/>
       </c>
       <c r="D16" s="8" t="inlineStr"/>
@@ -6101,7 +6117,7 @@
           <t>Sustainable return on equity — the three-year mean</t>
         </is>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="29">
         <f>('Income Statement'!B18/3472.066+'Income Statement'!C18/2991.839+'Income Statement'!D18/3230.423)/3</f>
         <v/>
       </c>
@@ -6113,8 +6129,8 @@
           <t>Justified multiple of book = (return less growth) / (cost of equity less growth)</t>
         </is>
       </c>
-      <c r="B18" s="26">
-        <f>(B17-Assumptions!$C$26)/(Assumptions!$C$12-Assumptions!$C$26)</f>
+      <c r="B18" s="27">
+        <f>(B17-Assumptions!$C$27)/(Assumptions!$C$12-Assumptions!$C$27)</f>
         <v/>
       </c>
       <c r="D18" s="8" t="inlineStr"/>
@@ -6138,7 +6154,7 @@
         </is>
       </c>
       <c r="B20" s="12">
-        <f>Assumptions!$C$48*(1+Assumptions!$C$26)/(Assumptions!$C$12-Assumptions!$C$26)</f>
+        <f>Assumptions!$C$49*(1+Assumptions!$C$27)/(Assumptions!$C$12-Assumptions!$C$27)</f>
         <v/>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -6216,23 +6232,23 @@
           <t>Glide fraction toward the terminal cost of capital</t>
         </is>
       </c>
-      <c r="B2" s="28">
+      <c r="B2" s="29">
         <f>(1)/5</f>
         <v/>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="29">
         <f>(2)/5</f>
         <v/>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="29">
         <f>(3)/5</f>
         <v/>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="29">
         <f>(4)/5</f>
         <v/>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="29">
         <f>(5)/5</f>
         <v/>
       </c>
@@ -6243,24 +6259,24 @@
           <t>Discount rate = first-year rate + glide x (terminal less first-year)</t>
         </is>
       </c>
-      <c r="B3" s="29">
-        <f>Assumptions!$C$21+B2*(Assumptions!$C$25-Assumptions!$C$21)</f>
-        <v/>
-      </c>
-      <c r="C3" s="29">
-        <f>Assumptions!$C$21+C2*(Assumptions!$C$25-Assumptions!$C$21)</f>
-        <v/>
-      </c>
-      <c r="D3" s="29">
-        <f>Assumptions!$C$21+D2*(Assumptions!$C$25-Assumptions!$C$21)</f>
-        <v/>
-      </c>
-      <c r="E3" s="29">
-        <f>Assumptions!$C$21+E2*(Assumptions!$C$25-Assumptions!$C$21)</f>
-        <v/>
-      </c>
-      <c r="F3" s="29">
-        <f>Assumptions!$C$21+F2*(Assumptions!$C$25-Assumptions!$C$21)</f>
+      <c r="B3" s="30">
+        <f>Assumptions!$C$21+B2*(Assumptions!$C$26-Assumptions!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C3" s="30">
+        <f>Assumptions!$C$21+C2*(Assumptions!$C$26-Assumptions!$C$21)</f>
+        <v/>
+      </c>
+      <c r="D3" s="30">
+        <f>Assumptions!$C$21+D2*(Assumptions!$C$26-Assumptions!$C$21)</f>
+        <v/>
+      </c>
+      <c r="E3" s="30">
+        <f>Assumptions!$C$21+E2*(Assumptions!$C$26-Assumptions!$C$21)</f>
+        <v/>
+      </c>
+      <c r="F3" s="30">
+        <f>Assumptions!$C$21+F2*(Assumptions!$C$26-Assumptions!$C$21)</f>
         <v/>
       </c>
     </row>
@@ -6270,23 +6286,23 @@
           <t>Discount factor (compounding)</t>
         </is>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="31">
         <f>1/(1+B3)</f>
         <v/>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="31">
         <f>B4/(1+C3)</f>
         <v/>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="31">
         <f>C4/(1+D3)</f>
         <v/>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <f>D4/(1+E3)</f>
         <v/>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="31">
         <f>E4/(1+F3)</f>
         <v/>
       </c>
@@ -6310,24 +6326,24 @@
           <t>EBITDA — Frame A</t>
         </is>
       </c>
-      <c r="B6" s="21">
-        <f>Segments!C20-Assumptions!$C$56*0+'Income Statement'!E5+'Income Statement'!E6+'Income Statement'!E7</f>
-        <v/>
-      </c>
-      <c r="C6" s="21">
-        <f>Segments!D20-Assumptions!$C$56*0+'Income Statement'!F5+'Income Statement'!F6+'Income Statement'!F7</f>
-        <v/>
-      </c>
-      <c r="D6" s="21">
-        <f>Segments!E20-Assumptions!$C$56*0+'Income Statement'!G5+'Income Statement'!G6+'Income Statement'!G7</f>
-        <v/>
-      </c>
-      <c r="E6" s="21">
-        <f>Segments!F20-Assumptions!$C$56*0+'Income Statement'!H5+'Income Statement'!H6+'Income Statement'!H7</f>
-        <v/>
-      </c>
-      <c r="F6" s="21">
-        <f>Segments!G20-Assumptions!$C$56*0+'Income Statement'!I5+'Income Statement'!I6+'Income Statement'!I7</f>
+      <c r="B6" s="22">
+        <f>Segments!C20-Assumptions!$C$57*0+'Income Statement'!E5+'Income Statement'!E6+'Income Statement'!E7</f>
+        <v/>
+      </c>
+      <c r="C6" s="22">
+        <f>Segments!D20-Assumptions!$C$57*0+'Income Statement'!F5+'Income Statement'!F6+'Income Statement'!F7</f>
+        <v/>
+      </c>
+      <c r="D6" s="22">
+        <f>Segments!E20-Assumptions!$C$57*0+'Income Statement'!G5+'Income Statement'!G6+'Income Statement'!G7</f>
+        <v/>
+      </c>
+      <c r="E6" s="22">
+        <f>Segments!F20-Assumptions!$C$57*0+'Income Statement'!H5+'Income Statement'!H6+'Income Statement'!H7</f>
+        <v/>
+      </c>
+      <c r="F6" s="22">
+        <f>Segments!G20-Assumptions!$C$57*0+'Income Statement'!I5+'Income Statement'!I6+'Income Statement'!I7</f>
         <v/>
       </c>
     </row>
@@ -6337,24 +6353,24 @@
           <t>Less depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B7" s="21">
-        <f>-Assumptions!C$43</f>
-        <v/>
-      </c>
-      <c r="C7" s="21">
-        <f>-Assumptions!D$43</f>
-        <v/>
-      </c>
-      <c r="D7" s="21">
-        <f>-Assumptions!E$43</f>
-        <v/>
-      </c>
-      <c r="E7" s="21">
-        <f>-Assumptions!F$43</f>
-        <v/>
-      </c>
-      <c r="F7" s="21">
-        <f>-Assumptions!G$43</f>
+      <c r="B7" s="22">
+        <f>-Assumptions!C$44</f>
+        <v/>
+      </c>
+      <c r="C7" s="22">
+        <f>-Assumptions!D$44</f>
+        <v/>
+      </c>
+      <c r="D7" s="22">
+        <f>-Assumptions!E$44</f>
+        <v/>
+      </c>
+      <c r="E7" s="22">
+        <f>-Assumptions!F$44</f>
+        <v/>
+      </c>
+      <c r="F7" s="22">
+        <f>-Assumptions!G$44</f>
         <v/>
       </c>
     </row>
@@ -6418,24 +6434,24 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B10" s="21">
-        <f>Assumptions!C$43</f>
-        <v/>
-      </c>
-      <c r="C10" s="21">
-        <f>Assumptions!D$43</f>
-        <v/>
-      </c>
-      <c r="D10" s="21">
-        <f>Assumptions!E$43</f>
-        <v/>
-      </c>
-      <c r="E10" s="21">
-        <f>Assumptions!F$43</f>
-        <v/>
-      </c>
-      <c r="F10" s="21">
-        <f>Assumptions!G$43</f>
+      <c r="B10" s="22">
+        <f>Assumptions!C$44</f>
+        <v/>
+      </c>
+      <c r="C10" s="22">
+        <f>Assumptions!D$44</f>
+        <v/>
+      </c>
+      <c r="D10" s="22">
+        <f>Assumptions!E$44</f>
+        <v/>
+      </c>
+      <c r="E10" s="22">
+        <f>Assumptions!F$44</f>
+        <v/>
+      </c>
+      <c r="F10" s="22">
+        <f>Assumptions!G$44</f>
         <v/>
       </c>
     </row>
@@ -6445,24 +6461,24 @@
           <t>Less capital expenditure</t>
         </is>
       </c>
-      <c r="B11" s="21">
-        <f>-Assumptions!C$44</f>
-        <v/>
-      </c>
-      <c r="C11" s="21">
-        <f>-Assumptions!D$44</f>
-        <v/>
-      </c>
-      <c r="D11" s="21">
-        <f>-Assumptions!E$44</f>
-        <v/>
-      </c>
-      <c r="E11" s="21">
-        <f>-Assumptions!F$44</f>
-        <v/>
-      </c>
-      <c r="F11" s="21">
-        <f>-Assumptions!G$44</f>
+      <c r="B11" s="22">
+        <f>-Assumptions!C$45</f>
+        <v/>
+      </c>
+      <c r="C11" s="22">
+        <f>-Assumptions!D$45</f>
+        <v/>
+      </c>
+      <c r="D11" s="22">
+        <f>-Assumptions!E$45</f>
+        <v/>
+      </c>
+      <c r="E11" s="22">
+        <f>-Assumptions!F$45</f>
+        <v/>
+      </c>
+      <c r="F11" s="22">
+        <f>-Assumptions!G$45</f>
         <v/>
       </c>
     </row>
@@ -6472,23 +6488,23 @@
           <t>Less increase in working capital</t>
         </is>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="22">
         <f>'Cash Flow'!E7</f>
         <v/>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="22">
         <f>'Cash Flow'!F7</f>
         <v/>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="22">
         <f>'Cash Flow'!G7</f>
         <v/>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="22">
         <f>'Cash Flow'!H7</f>
         <v/>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="22">
         <f>'Cash Flow'!I7</f>
         <v/>
       </c>
@@ -6499,23 +6515,23 @@
           <t>FREE CASH FLOW TO THE FIRM — Frame A</t>
         </is>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="23">
         <f>B9+B10+B11+B12</f>
         <v/>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="23">
         <f>C9+C10+C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="23">
         <f>D9+D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="23">
         <f>E9+E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="23">
         <f>F9+F10+F11+F12</f>
         <v/>
       </c>
@@ -6526,27 +6542,27 @@
           <t>PRESENT VALUE of free cash flow</t>
         </is>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="23">
         <f>B13*B4</f>
         <v/>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="23">
         <f>C13*C4</f>
         <v/>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="23">
         <f>D13*D4</f>
         <v/>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="23">
         <f>E13*E4</f>
         <v/>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="23">
         <f>F13*F4</f>
         <v/>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="23">
         <f>SUM(B14:F14)</f>
         <v/>
       </c>
@@ -6570,24 +6586,24 @@
           <t>EBITDA — Frame B</t>
         </is>
       </c>
-      <c r="B16" s="21">
-        <f>Segments!C21-Assumptions!$C$56*0+'Income Statement'!E5+'Income Statement'!E6+'Income Statement'!E7</f>
-        <v/>
-      </c>
-      <c r="C16" s="21">
-        <f>Segments!D21-Assumptions!$C$56*0+'Income Statement'!F5+'Income Statement'!F6+'Income Statement'!F7</f>
-        <v/>
-      </c>
-      <c r="D16" s="21">
-        <f>Segments!E21-Assumptions!$C$56*0+'Income Statement'!G5+'Income Statement'!G6+'Income Statement'!G7</f>
-        <v/>
-      </c>
-      <c r="E16" s="21">
-        <f>Segments!F21-Assumptions!$C$56*0+'Income Statement'!H5+'Income Statement'!H6+'Income Statement'!H7</f>
-        <v/>
-      </c>
-      <c r="F16" s="21">
-        <f>Segments!G21-Assumptions!$C$56*0+'Income Statement'!I5+'Income Statement'!I6+'Income Statement'!I7</f>
+      <c r="B16" s="22">
+        <f>Segments!C21-Assumptions!$C$57*0+'Income Statement'!E5+'Income Statement'!E6+'Income Statement'!E7</f>
+        <v/>
+      </c>
+      <c r="C16" s="22">
+        <f>Segments!D21-Assumptions!$C$57*0+'Income Statement'!F5+'Income Statement'!F6+'Income Statement'!F7</f>
+        <v/>
+      </c>
+      <c r="D16" s="22">
+        <f>Segments!E21-Assumptions!$C$57*0+'Income Statement'!G5+'Income Statement'!G6+'Income Statement'!G7</f>
+        <v/>
+      </c>
+      <c r="E16" s="22">
+        <f>Segments!F21-Assumptions!$C$57*0+'Income Statement'!H5+'Income Statement'!H6+'Income Statement'!H7</f>
+        <v/>
+      </c>
+      <c r="F16" s="22">
+        <f>Segments!G21-Assumptions!$C$57*0+'Income Statement'!I5+'Income Statement'!I6+'Income Statement'!I7</f>
         <v/>
       </c>
     </row>
@@ -6597,24 +6613,24 @@
           <t>Less depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B17" s="21">
-        <f>-Assumptions!C$43</f>
-        <v/>
-      </c>
-      <c r="C17" s="21">
-        <f>-Assumptions!D$43</f>
-        <v/>
-      </c>
-      <c r="D17" s="21">
-        <f>-Assumptions!E$43</f>
-        <v/>
-      </c>
-      <c r="E17" s="21">
-        <f>-Assumptions!F$43</f>
-        <v/>
-      </c>
-      <c r="F17" s="21">
-        <f>-Assumptions!G$43</f>
+      <c r="B17" s="22">
+        <f>-Assumptions!C$44</f>
+        <v/>
+      </c>
+      <c r="C17" s="22">
+        <f>-Assumptions!D$44</f>
+        <v/>
+      </c>
+      <c r="D17" s="22">
+        <f>-Assumptions!E$44</f>
+        <v/>
+      </c>
+      <c r="E17" s="22">
+        <f>-Assumptions!F$44</f>
+        <v/>
+      </c>
+      <c r="F17" s="22">
+        <f>-Assumptions!G$44</f>
         <v/>
       </c>
     </row>
@@ -6678,24 +6694,24 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B20" s="21">
-        <f>Assumptions!C$43</f>
-        <v/>
-      </c>
-      <c r="C20" s="21">
-        <f>Assumptions!D$43</f>
-        <v/>
-      </c>
-      <c r="D20" s="21">
-        <f>Assumptions!E$43</f>
-        <v/>
-      </c>
-      <c r="E20" s="21">
-        <f>Assumptions!F$43</f>
-        <v/>
-      </c>
-      <c r="F20" s="21">
-        <f>Assumptions!G$43</f>
+      <c r="B20" s="22">
+        <f>Assumptions!C$44</f>
+        <v/>
+      </c>
+      <c r="C20" s="22">
+        <f>Assumptions!D$44</f>
+        <v/>
+      </c>
+      <c r="D20" s="22">
+        <f>Assumptions!E$44</f>
+        <v/>
+      </c>
+      <c r="E20" s="22">
+        <f>Assumptions!F$44</f>
+        <v/>
+      </c>
+      <c r="F20" s="22">
+        <f>Assumptions!G$44</f>
         <v/>
       </c>
     </row>
@@ -6705,24 +6721,24 @@
           <t>Less capital expenditure</t>
         </is>
       </c>
-      <c r="B21" s="21">
-        <f>-Assumptions!C$44</f>
-        <v/>
-      </c>
-      <c r="C21" s="21">
-        <f>-Assumptions!D$44</f>
-        <v/>
-      </c>
-      <c r="D21" s="21">
-        <f>-Assumptions!E$44</f>
-        <v/>
-      </c>
-      <c r="E21" s="21">
-        <f>-Assumptions!F$44</f>
-        <v/>
-      </c>
-      <c r="F21" s="21">
-        <f>-Assumptions!G$44</f>
+      <c r="B21" s="22">
+        <f>-Assumptions!C$45</f>
+        <v/>
+      </c>
+      <c r="C21" s="22">
+        <f>-Assumptions!D$45</f>
+        <v/>
+      </c>
+      <c r="D21" s="22">
+        <f>-Assumptions!E$45</f>
+        <v/>
+      </c>
+      <c r="E21" s="22">
+        <f>-Assumptions!F$45</f>
+        <v/>
+      </c>
+      <c r="F21" s="22">
+        <f>-Assumptions!G$45</f>
         <v/>
       </c>
     </row>
@@ -6732,23 +6748,23 @@
           <t>Less increase in working capital</t>
         </is>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="22">
         <f>'Cash Flow'!E7</f>
         <v/>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="22">
         <f>'Cash Flow'!F7</f>
         <v/>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="22">
         <f>'Cash Flow'!G7</f>
         <v/>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="22">
         <f>'Cash Flow'!H7</f>
         <v/>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="22">
         <f>'Cash Flow'!I7</f>
         <v/>
       </c>
@@ -6759,23 +6775,23 @@
           <t>FREE CASH FLOW TO THE FIRM — Frame B</t>
         </is>
       </c>
-      <c r="B23" s="22">
+      <c r="B23" s="23">
         <f>B19+B20+B21+B22</f>
         <v/>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="23">
         <f>C19+C20+C21+C22</f>
         <v/>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="23">
         <f>D19+D20+D21+D22</f>
         <v/>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="23">
         <f>E19+E20+E21+E22</f>
         <v/>
       </c>
-      <c r="F23" s="22">
+      <c r="F23" s="23">
         <f>F19+F20+F21+F22</f>
         <v/>
       </c>
@@ -6786,27 +6802,27 @@
           <t>PRESENT VALUE of free cash flow</t>
         </is>
       </c>
-      <c r="B24" s="22">
+      <c r="B24" s="23">
         <f>B23*B4</f>
         <v/>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="23">
         <f>C23*C4</f>
         <v/>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="23">
         <f>D23*D4</f>
         <v/>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="23">
         <f>E23*E4</f>
         <v/>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="23">
         <f>F23*F4</f>
         <v/>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="23">
         <f>SUM(B24:F24)</f>
         <v/>
       </c>
@@ -6830,8 +6846,8 @@
           <t>Reinvestment rate = long-run growth / terminal return on capital</t>
         </is>
       </c>
-      <c r="B26" s="28">
-        <f>Assumptions!$C$26/Assumptions!$C$27</f>
+      <c r="B26" s="29">
+        <f>Assumptions!$C$27/Assumptions!$C$28</f>
         <v/>
       </c>
     </row>
@@ -6841,8 +6857,8 @@
           <t>Terminal NOPAT = final-year NOPAT x (1 + growth)</t>
         </is>
       </c>
-      <c r="B27" s="21">
-        <f>F9*(1+Assumptions!$C$26)</f>
+      <c r="B27" s="22">
+        <f>F9*(1+Assumptions!$C$27)</f>
         <v/>
       </c>
     </row>
@@ -6852,7 +6868,7 @@
           <t>Terminal free cash flow = terminal NOPAT x (1 less reinvestment)</t>
         </is>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="22">
         <f>B27*(1-B26)</f>
         <v/>
       </c>
@@ -6864,7 +6880,7 @@
         </is>
       </c>
       <c r="B29" s="17">
-        <f>B28/(Assumptions!$C$25-Assumptions!$C$26)</f>
+        <f>B28/(Assumptions!$C$26-Assumptions!$C$27)</f>
         <v/>
       </c>
     </row>
@@ -6874,7 +6890,7 @@
           <t>Present value of the terminal value</t>
         </is>
       </c>
-      <c r="B30" s="22">
+      <c r="B30" s="23">
         <f>B29*F4</f>
         <v/>
       </c>
@@ -6885,7 +6901,7 @@
           <t>ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B31" s="22">
+      <c r="B31" s="23">
         <f>G14+B30</f>
         <v/>
       </c>
@@ -6920,8 +6936,8 @@
           <t>Reinvestment rate = long-run growth / terminal return on capital</t>
         </is>
       </c>
-      <c r="B34" s="28">
-        <f>Assumptions!$C$26/Assumptions!$C$27</f>
+      <c r="B34" s="29">
+        <f>Assumptions!$C$27/Assumptions!$C$28</f>
         <v/>
       </c>
     </row>
@@ -6931,8 +6947,8 @@
           <t>Terminal NOPAT = final-year NOPAT x (1 + growth)</t>
         </is>
       </c>
-      <c r="B35" s="21">
-        <f>F19*(1+Assumptions!$C$26)</f>
+      <c r="B35" s="22">
+        <f>F19*(1+Assumptions!$C$27)</f>
         <v/>
       </c>
     </row>
@@ -6942,7 +6958,7 @@
           <t>Terminal free cash flow = terminal NOPAT x (1 less reinvestment)</t>
         </is>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="22">
         <f>B35*(1-B34)</f>
         <v/>
       </c>
@@ -6954,7 +6970,7 @@
         </is>
       </c>
       <c r="B37" s="17">
-        <f>B36/(Assumptions!$C$25-Assumptions!$C$26)</f>
+        <f>B36/(Assumptions!$C$26-Assumptions!$C$27)</f>
         <v/>
       </c>
     </row>
@@ -6964,7 +6980,7 @@
           <t>Present value of the terminal value</t>
         </is>
       </c>
-      <c r="B38" s="22">
+      <c r="B38" s="23">
         <f>B37*F4</f>
         <v/>
       </c>
@@ -6975,7 +6991,7 @@
           <t>ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B39" s="22">
+      <c r="B39" s="23">
         <f>G24+B38</f>
         <v/>
       </c>
@@ -7078,23 +7094,23 @@
       <c r="D2" s="20" t="n">
         <v>35896.617</v>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="22">
         <f>Segments!C11</f>
         <v/>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="22">
         <f>Segments!D11</f>
         <v/>
       </c>
-      <c r="G2" s="21">
+      <c r="G2" s="22">
         <f>Segments!E11</f>
         <v/>
       </c>
-      <c r="H2" s="21">
+      <c r="H2" s="22">
         <f>Segments!F11</f>
         <v/>
       </c>
-      <c r="I2" s="21">
+      <c r="I2" s="22">
         <f>Segments!G11</f>
         <v/>
       </c>
@@ -7114,23 +7130,23 @@
       <c r="D3" s="20" t="n">
         <v>6945.79</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="22">
         <f>Segments!C20</f>
         <v/>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="22">
         <f>Segments!D20</f>
         <v/>
       </c>
-      <c r="G3" s="21">
+      <c r="G3" s="22">
         <f>Segments!E20</f>
         <v/>
       </c>
-      <c r="H3" s="21">
+      <c r="H3" s="22">
         <f>Segments!F20</f>
         <v/>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="22">
         <f>Segments!G20</f>
         <v/>
       </c>
@@ -7150,23 +7166,23 @@
       <c r="D4" s="13" t="n">
         <v>0.193494278304833</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="29">
         <f>E3/E2</f>
         <v/>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="29">
         <f>F3/F2</f>
         <v/>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="29">
         <f>G3/G2</f>
         <v/>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="29">
         <f>H3/H2</f>
         <v/>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="29">
         <f>I3/I2</f>
         <v/>
       </c>
@@ -7186,24 +7202,24 @@
       <c r="D5" s="20" t="n">
         <v>-2547.6</v>
       </c>
-      <c r="E5" s="21">
-        <f>-Assumptions!$C$56*(1+Assumptions!C$40)</f>
-        <v/>
-      </c>
-      <c r="F5" s="21">
-        <f>E5*(1+Assumptions!D$40)</f>
-        <v/>
-      </c>
-      <c r="G5" s="21">
-        <f>F5*(1+Assumptions!E$40)</f>
-        <v/>
-      </c>
-      <c r="H5" s="21">
-        <f>G5*(1+Assumptions!F$40)</f>
-        <v/>
-      </c>
-      <c r="I5" s="21">
-        <f>H5*(1+Assumptions!G$40)</f>
+      <c r="E5" s="22">
+        <f>-Assumptions!$C$57*(1+Assumptions!C$41)</f>
+        <v/>
+      </c>
+      <c r="F5" s="22">
+        <f>E5*(1+Assumptions!D$41)</f>
+        <v/>
+      </c>
+      <c r="G5" s="22">
+        <f>F5*(1+Assumptions!E$41)</f>
+        <v/>
+      </c>
+      <c r="H5" s="22">
+        <f>G5*(1+Assumptions!F$41)</f>
+        <v/>
+      </c>
+      <c r="I5" s="22">
+        <f>H5*(1+Assumptions!G$41)</f>
         <v/>
       </c>
     </row>
@@ -7222,24 +7238,24 @@
       <c r="D6" s="20" t="n">
         <v>167.665</v>
       </c>
-      <c r="E6" s="21">
-        <f>Assumptions!$C$57*(1+Assumptions!C$41)</f>
-        <v/>
-      </c>
-      <c r="F6" s="21">
-        <f>E6*(1+Assumptions!D$41)</f>
-        <v/>
-      </c>
-      <c r="G6" s="21">
-        <f>F6*(1+Assumptions!E$41)</f>
-        <v/>
-      </c>
-      <c r="H6" s="21">
-        <f>G6*(1+Assumptions!F$41)</f>
-        <v/>
-      </c>
-      <c r="I6" s="21">
-        <f>H6*(1+Assumptions!G$41)</f>
+      <c r="E6" s="22">
+        <f>Assumptions!$C$58*(1+Assumptions!C$42)</f>
+        <v/>
+      </c>
+      <c r="F6" s="22">
+        <f>E6*(1+Assumptions!D$42)</f>
+        <v/>
+      </c>
+      <c r="G6" s="22">
+        <f>F6*(1+Assumptions!E$42)</f>
+        <v/>
+      </c>
+      <c r="H6" s="22">
+        <f>G6*(1+Assumptions!F$42)</f>
+        <v/>
+      </c>
+      <c r="I6" s="22">
+        <f>H6*(1+Assumptions!G$42)</f>
         <v/>
       </c>
     </row>
@@ -7258,24 +7274,24 @@
       <c r="D7" s="20" t="n">
         <v>-284.305</v>
       </c>
-      <c r="E7" s="21">
-        <f>-Assumptions!C$42</f>
-        <v/>
-      </c>
-      <c r="F7" s="21">
-        <f>-Assumptions!D$42</f>
-        <v/>
-      </c>
-      <c r="G7" s="21">
-        <f>-Assumptions!E$42</f>
-        <v/>
-      </c>
-      <c r="H7" s="21">
-        <f>-Assumptions!F$42</f>
-        <v/>
-      </c>
-      <c r="I7" s="21">
-        <f>-Assumptions!G$42</f>
+      <c r="E7" s="22">
+        <f>-Assumptions!C$43</f>
+        <v/>
+      </c>
+      <c r="F7" s="22">
+        <f>-Assumptions!D$43</f>
+        <v/>
+      </c>
+      <c r="G7" s="22">
+        <f>-Assumptions!E$43</f>
+        <v/>
+      </c>
+      <c r="H7" s="22">
+        <f>-Assumptions!F$43</f>
+        <v/>
+      </c>
+      <c r="I7" s="22">
+        <f>-Assumptions!G$43</f>
         <v/>
       </c>
     </row>
@@ -7285,32 +7301,32 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="32" t="n">
         <v>3679.814</v>
       </c>
-      <c r="C8" s="31" t="n">
+      <c r="C8" s="32" t="n">
         <v>3854.702</v>
       </c>
-      <c r="D8" s="31" t="n">
+      <c r="D8" s="32" t="n">
         <v>4281.55</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="23">
         <f>E3+E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="23">
         <f>F3+F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="23">
         <f>G3+G5+G6+G7</f>
         <v/>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="23">
         <f>H3+H5+H6+H7</f>
         <v/>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="23">
         <f>I3+I5+I6+I7</f>
         <v/>
       </c>
@@ -7330,23 +7346,23 @@
       <c r="D9" s="13" t="n">
         <v>0.1192744709062695</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <f>E8/E2</f>
         <v/>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="29">
         <f>F8/F2</f>
         <v/>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="29">
         <f>G8/G2</f>
         <v/>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="29">
         <f>H8/H2</f>
         <v/>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="29">
         <f>I8/I2</f>
         <v/>
       </c>
@@ -7366,24 +7382,24 @@
       <c r="D10" s="20" t="n">
         <v>-775.946</v>
       </c>
-      <c r="E10" s="21">
-        <f>-Assumptions!C$43</f>
-        <v/>
-      </c>
-      <c r="F10" s="21">
-        <f>-Assumptions!D$43</f>
-        <v/>
-      </c>
-      <c r="G10" s="21">
-        <f>-Assumptions!E$43</f>
-        <v/>
-      </c>
-      <c r="H10" s="21">
-        <f>-Assumptions!F$43</f>
-        <v/>
-      </c>
-      <c r="I10" s="21">
-        <f>-Assumptions!G$43</f>
+      <c r="E10" s="22">
+        <f>-Assumptions!C$44</f>
+        <v/>
+      </c>
+      <c r="F10" s="22">
+        <f>-Assumptions!D$44</f>
+        <v/>
+      </c>
+      <c r="G10" s="22">
+        <f>-Assumptions!E$44</f>
+        <v/>
+      </c>
+      <c r="H10" s="22">
+        <f>-Assumptions!F$44</f>
+        <v/>
+      </c>
+      <c r="I10" s="22">
+        <f>-Assumptions!G$44</f>
         <v/>
       </c>
     </row>
@@ -7393,32 +7409,32 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B11" s="31" t="n">
+      <c r="B11" s="32" t="n">
         <v>2983.249</v>
       </c>
-      <c r="C11" s="31" t="n">
+      <c r="C11" s="32" t="n">
         <v>3068.895</v>
       </c>
-      <c r="D11" s="31" t="n">
+      <c r="D11" s="32" t="n">
         <v>3505.604</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="23">
         <f>E8+E10</f>
         <v/>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="23">
         <f>F8+F10</f>
         <v/>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="23">
         <f>G8+G10</f>
         <v/>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="23">
         <f>H8+H10</f>
         <v/>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="23">
         <f>I8+I10</f>
         <v/>
       </c>
@@ -7438,24 +7454,24 @@
       <c r="D12" s="20" t="n">
         <v>71.274</v>
       </c>
-      <c r="E12" s="21">
-        <f>Assumptions!$C$67</f>
-        <v/>
-      </c>
-      <c r="F12" s="21">
-        <f>Assumptions!$C$67</f>
-        <v/>
-      </c>
-      <c r="G12" s="21">
-        <f>Assumptions!$C$67</f>
-        <v/>
-      </c>
-      <c r="H12" s="21">
-        <f>Assumptions!$C$67</f>
-        <v/>
-      </c>
-      <c r="I12" s="21">
-        <f>Assumptions!$C$67</f>
+      <c r="E12" s="22">
+        <f>Assumptions!$C$68</f>
+        <v/>
+      </c>
+      <c r="F12" s="22">
+        <f>Assumptions!$C$68</f>
+        <v/>
+      </c>
+      <c r="G12" s="22">
+        <f>Assumptions!$C$68</f>
+        <v/>
+      </c>
+      <c r="H12" s="22">
+        <f>Assumptions!$C$68</f>
+        <v/>
+      </c>
+      <c r="I12" s="22">
+        <f>Assumptions!$C$68</f>
         <v/>
       </c>
     </row>
@@ -7474,24 +7490,24 @@
       <c r="D13" s="20" t="n">
         <v>-402.945</v>
       </c>
-      <c r="E13" s="21">
-        <f>-Assumptions!$C$66</f>
-        <v/>
-      </c>
-      <c r="F13" s="21">
-        <f>-Assumptions!$C$66</f>
-        <v/>
-      </c>
-      <c r="G13" s="21">
-        <f>-Assumptions!$C$66</f>
-        <v/>
-      </c>
-      <c r="H13" s="21">
-        <f>-Assumptions!$C$66</f>
-        <v/>
-      </c>
-      <c r="I13" s="21">
-        <f>-Assumptions!$C$66</f>
+      <c r="E13" s="22">
+        <f>-Assumptions!$C$67</f>
+        <v/>
+      </c>
+      <c r="F13" s="22">
+        <f>-Assumptions!$C$67</f>
+        <v/>
+      </c>
+      <c r="G13" s="22">
+        <f>-Assumptions!$C$67</f>
+        <v/>
+      </c>
+      <c r="H13" s="22">
+        <f>-Assumptions!$C$67</f>
+        <v/>
+      </c>
+      <c r="I13" s="22">
+        <f>-Assumptions!$C$67</f>
         <v/>
       </c>
     </row>
@@ -7510,23 +7526,23 @@
       <c r="D14" s="20" t="n">
         <v>3173.933</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="22">
         <f>E11+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="22">
         <f>F11+F12+F13</f>
         <v/>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="22">
         <f>G11+G12+G13</f>
         <v/>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="22">
         <f>H11+H12+H13</f>
         <v/>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="22">
         <f>I11+I12+I13</f>
         <v/>
       </c>
@@ -7546,23 +7562,23 @@
       <c r="D15" s="20" t="n">
         <v>-322.891</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="22">
         <f>-E14*Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="22">
         <f>-F14*Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="22">
         <f>-G14*Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="H15" s="21">
+      <c r="H15" s="22">
         <f>-H14*Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="22">
         <f>-I14*Assumptions!$C$16</f>
         <v/>
       </c>
@@ -7573,13 +7589,13 @@
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B16" s="32" t="n">
+      <c r="B16" s="33" t="n">
         <v>2630.489</v>
       </c>
-      <c r="C16" s="32" t="n">
+      <c r="C16" s="33" t="n">
         <v>2472.283</v>
       </c>
-      <c r="D16" s="32" t="n">
+      <c r="D16" s="33" t="n">
         <v>2851.042</v>
       </c>
       <c r="E16" s="17">
@@ -7618,24 +7634,24 @@
       <c r="D17" s="20" t="n">
         <v>-57.042</v>
       </c>
-      <c r="E17" s="21">
-        <f>-Assumptions!$C$68</f>
-        <v/>
-      </c>
-      <c r="F17" s="21">
-        <f>-Assumptions!$C$68</f>
-        <v/>
-      </c>
-      <c r="G17" s="21">
-        <f>-Assumptions!$C$68</f>
-        <v/>
-      </c>
-      <c r="H17" s="21">
-        <f>-Assumptions!$C$68</f>
-        <v/>
-      </c>
-      <c r="I17" s="21">
-        <f>-Assumptions!$C$68</f>
+      <c r="E17" s="22">
+        <f>-Assumptions!$C$69</f>
+        <v/>
+      </c>
+      <c r="F17" s="22">
+        <f>-Assumptions!$C$69</f>
+        <v/>
+      </c>
+      <c r="G17" s="22">
+        <f>-Assumptions!$C$69</f>
+        <v/>
+      </c>
+      <c r="H17" s="22">
+        <f>-Assumptions!$C$69</f>
+        <v/>
+      </c>
+      <c r="I17" s="22">
+        <f>-Assumptions!$C$69</f>
         <v/>
       </c>
     </row>
@@ -7645,32 +7661,32 @@
           <t>Profit attributable to owners</t>
         </is>
       </c>
-      <c r="B18" s="31" t="n">
+      <c r="B18" s="32" t="n">
         <v>2601.421</v>
       </c>
-      <c r="C18" s="31" t="n">
+      <c r="C18" s="32" t="n">
         <v>2420.275</v>
       </c>
-      <c r="D18" s="31" t="n">
+      <c r="D18" s="32" t="n">
         <v>2794</v>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="23">
         <f>E16+E17</f>
         <v/>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="23">
         <f>F16+F17</f>
         <v/>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="23">
         <f>G16+G17</f>
         <v/>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="23">
         <f>H16+H17</f>
         <v/>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="23">
         <f>I16+I17</f>
         <v/>
       </c>
@@ -7690,23 +7706,23 @@
       <c r="D19" s="16" t="n">
         <v>0.224</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="26">
         <f>E18/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="26">
         <f>F18/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="26">
         <f>G18/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="H19" s="25">
+      <c r="H19" s="26">
         <f>H18/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="I19" s="25">
+      <c r="I19" s="26">
         <f>I18/Assumptions!$C$4</f>
         <v/>
       </c>

--- a/engine/adnocdist_study/ADNOCDIST_Valuation_Model_09082026.xlsx
+++ b/engine/adnocdist_study/ADNOCDIST_Valuation_Model_09082026.xlsx
@@ -2223,111 +2223,111 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of capital 6.56%</t>
+          <t>Terminal cost of capital 6.44%</t>
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>4.686743038033034</v>
+        <v>4.472057106292805</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.966264082174509</v>
+        <v>4.746931359768977</v>
       </c>
       <c r="D3" s="15" t="n">
-        <v>5.30009108812957</v>
+        <v>5.076582096917631</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>5.706086415087039</v>
+        <v>5.47952561256779</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>6.210910815072849</v>
+        <v>5.983683475617217</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of capital 7.06%</t>
+          <t>Terminal cost of capital 6.94%</t>
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>4.338081945134413</v>
+        <v>4.133065423237127</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>4.567222912130541</v>
+        <v>4.357643870613312</v>
       </c>
       <c r="D4" s="15" t="n">
-        <v>4.83673778287524</v>
+        <v>4.622723217256807</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>5.158594234015194</v>
+        <v>4.940607713204206</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>5.550008498875564</v>
+        <v>5.32914727592826</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of capital 7.56%</t>
+          <t>Terminal cost of capital 7.44%</t>
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>4.038627665035003</v>
+        <v>3.842746999092251</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>4.228797998615474</v>
+        <v>4.028603553261314</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>4.449591502167147</v>
+        <v>4.245038895322488</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>4.70926927453304</v>
+        <v>4.500488664637969</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>5.019357433145563</v>
+        <v>4.806805518226626</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of capital 8.06%</t>
+          <t>Terminal cost of capital 7.94%</t>
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>3.778618892760917</v>
+        <v>3.59128714076265</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>3.938113156082837</v>
+        <v>3.746786204909884</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>4.12123033903702</v>
+        <v>3.925782439022962</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>4.333817343279192</v>
+        <v>4.134212042214958</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>4.58382413306109</v>
+        <v>4.38019467206157</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of capital 8.56%</t>
+          <t>Terminal cost of capital 8.44%</t>
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>3.550716356365404</v>
+        <v>3.371344144996052</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>3.685698405723232</v>
+        <v>3.502669927571309</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>3.839167477166377</v>
+        <v>3.652323326060763</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>4.015350548573732</v>
+        <v>3.824574900660831</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>4.219869555170337</v>
+        <v>4.025133733494157</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>0.06560368642200001</v>
+        <v>0.06437428020423498</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>5.30009108812957</v>
+        <v>5.076582096917631</v>
       </c>
     </row>
     <row r="11">
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>0.070603686422</v>
+        <v>0.06937428020423497</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>4.83673778287524</v>
+        <v>4.622723217256807</v>
       </c>
     </row>
     <row r="12">
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>0.07560368642200001</v>
+        <v>0.07437428020423498</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>4.449591502167147</v>
+        <v>4.245038895322488</v>
       </c>
     </row>
     <row r="13">
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>0.08060368642200001</v>
+        <v>0.07937428020423498</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>4.12123033903702</v>
+        <v>3.925782439022962</v>
       </c>
     </row>
     <row r="14">
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>0.085603686422</v>
+        <v>0.08437428020423497</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>3.839167477166377</v>
+        <v>3.652323326060763</v>
       </c>
     </row>
     <row r="15">
@@ -2425,7 +2425,7 @@
         <v>0.005</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>4.038627665035003</v>
+        <v>3.842746999092251</v>
       </c>
     </row>
     <row r="16">
@@ -2438,7 +2438,7 @@
         <v>0.01</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>4.228797998615474</v>
+        <v>4.028603553261314</v>
       </c>
     </row>
     <row r="17">
@@ -2451,7 +2451,7 @@
         <v>0.015</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>4.449591502167147</v>
+        <v>4.245038895322488</v>
       </c>
     </row>
     <row r="18">
@@ -2464,7 +2464,7 @@
         <v>0.02</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>4.70926927453304</v>
+        <v>4.500488664637969</v>
       </c>
     </row>
     <row r="19">
@@ -2477,7 +2477,7 @@
         <v>0.025</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>5.019357433145563</v>
+        <v>4.806805518226626</v>
       </c>
     </row>
     <row r="20">
@@ -2490,7 +2490,7 @@
         <v>0.45</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>5.266283774855093</v>
+        <v>5.083566069029051</v>
       </c>
     </row>
     <row r="21">
@@ -2503,7 +2503,7 @@
         <v>0.55</v>
       </c>
       <c r="C21" s="15" t="n">
-        <v>4.824952324894785</v>
+        <v>4.627963827527954</v>
       </c>
     </row>
     <row r="22">
@@ -2516,7 +2516,7 @@
         <v>0.6494</v>
       </c>
       <c r="C22" s="15" t="n">
-        <v>4.449591502167147</v>
+        <v>4.245038895322488</v>
       </c>
     </row>
     <row r="23">
@@ -2529,7 +2529,7 @@
         <v>0.8</v>
       </c>
       <c r="C23" s="15" t="n">
-        <v>3.973711096776246</v>
+        <v>3.765473170804389</v>
       </c>
     </row>
     <row r="24">
@@ -2542,7 +2542,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="15" t="n">
-        <v>3.469721946561251</v>
+        <v>3.264593336664223</v>
       </c>
     </row>
     <row r="25">
@@ -2555,7 +2555,7 @@
         <v>-0.01</v>
       </c>
       <c r="C25" s="15" t="n">
-        <v>4.235040245802537</v>
+        <v>3.995245141207556</v>
       </c>
     </row>
     <row r="26">
@@ -2568,7 +2568,7 @@
         <v>-0.005</v>
       </c>
       <c r="C26" s="15" t="n">
-        <v>4.341316677248776</v>
+        <v>4.161499559846868</v>
       </c>
     </row>
     <row r="27">
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="15" t="n">
-        <v>4.449591502167147</v>
+        <v>4.330957230076974</v>
       </c>
     </row>
     <row r="28">
@@ -2594,7 +2594,7 @@
         <v>0.005</v>
       </c>
       <c r="C28" s="15" t="n">
-        <v>4.559893626872848</v>
+        <v>4.503665582326194</v>
       </c>
     </row>
     <row r="29">
@@ -2607,7 +2607,7 @@
         <v>0.01</v>
       </c>
       <c r="C29" s="15" t="n">
-        <v>4.672252238508341</v>
+        <v>4.679672518529684</v>
       </c>
     </row>
     <row r="30">
@@ -2620,7 +2620,7 @@
         <v>-0.1</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>3.953235423567004</v>
+        <v>3.495985504611076</v>
       </c>
     </row>
     <row r="31">
@@ -2633,7 +2633,7 @@
         <v>-0.05</v>
       </c>
       <c r="C31" s="15" t="n">
-        <v>4.201413462867075</v>
+        <v>3.870512199966782</v>
       </c>
     </row>
     <row r="32">
@@ -2646,7 +2646,7 @@
         <v>0</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>4.449591502167147</v>
+        <v>4.245038895322488</v>
       </c>
     </row>
     <row r="33">
@@ -2659,7 +2659,7 @@
         <v>0.05</v>
       </c>
       <c r="C33" s="15" t="n">
-        <v>4.69776954146722</v>
+        <v>4.619565590678196</v>
       </c>
     </row>
     <row r="34">
@@ -2672,7 +2672,7 @@
         <v>0.1</v>
       </c>
       <c r="C34" s="15" t="n">
-        <v>4.945947580767291</v>
+        <v>4.994092286033902</v>
       </c>
     </row>
     <row r="35">
@@ -2685,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="C35" s="15" t="n">
-        <v>4.449591502167147</v>
+        <v>4.245038895322488</v>
       </c>
     </row>
     <row r="36">
@@ -2698,7 +2698,7 @@
         <v>150</v>
       </c>
       <c r="C36" s="15" t="n">
-        <v>4.602323091084383</v>
+        <v>4.399700826320476</v>
       </c>
     </row>
     <row r="37">
@@ -2711,7 +2711,7 @@
         <v>295</v>
       </c>
       <c r="C37" s="15" t="n">
-        <v>4.749963627037711</v>
+        <v>4.549207359618531</v>
       </c>
     </row>
     <row r="38">
@@ -2724,7 +2724,7 @@
         <v>450</v>
       </c>
       <c r="C38" s="15" t="n">
-        <v>4.907786268918853</v>
+        <v>4.709024688316452</v>
       </c>
     </row>
     <row r="39">
@@ -2737,7 +2737,7 @@
         <v>600</v>
       </c>
       <c r="C39" s="15" t="n">
-        <v>5.060517857836088</v>
+        <v>4.863686619314439</v>
       </c>
     </row>
     <row r="40">
@@ -2750,7 +2750,7 @@
         <v>0.09</v>
       </c>
       <c r="C40" s="15" t="n">
-        <v>4.512778315092071</v>
+        <v>4.305226915811582</v>
       </c>
     </row>
     <row r="41">
@@ -2763,7 +2763,7 @@
         <v>0.1017</v>
       </c>
       <c r="C41" s="15" t="n">
-        <v>4.449591502167147</v>
+        <v>4.245038895322488</v>
       </c>
     </row>
     <row r="42">
@@ -2776,7 +2776,7 @@
         <v>0.12</v>
       </c>
       <c r="C42" s="15" t="n">
-        <v>4.350760846053808</v>
+        <v>4.15089865814724</v>
       </c>
     </row>
     <row r="43">
@@ -2789,7 +2789,7 @@
         <v>0.15</v>
       </c>
       <c r="C43" s="15" t="n">
-        <v>4.188743377015546</v>
+        <v>3.996570400482897</v>
       </c>
     </row>
     <row r="44">
@@ -2802,7 +2802,7 @@
         <v>0.18</v>
       </c>
       <c r="C44" s="15" t="n">
-        <v>4.026725907977284</v>
+        <v>3.842242142818554</v>
       </c>
     </row>
     <row r="45">
@@ -2815,7 +2815,7 @@
         <v>-0.2</v>
       </c>
       <c r="C45" s="15" t="n">
-        <v>4.520662427533516</v>
+        <v>4.309259537260891</v>
       </c>
     </row>
     <row r="46">
@@ -2828,7 +2828,7 @@
         <v>-0.1</v>
       </c>
       <c r="C46" s="15" t="n">
-        <v>4.485126964850331</v>
+        <v>4.27714921629169</v>
       </c>
     </row>
     <row r="47">
@@ -2841,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="C47" s="15" t="n">
-        <v>4.449591502167147</v>
+        <v>4.245038895322488</v>
       </c>
     </row>
     <row r="48">
@@ -2854,7 +2854,7 @@
         <v>0.1</v>
       </c>
       <c r="C48" s="15" t="n">
-        <v>4.414056039483962</v>
+        <v>4.212928574353287</v>
       </c>
     </row>
     <row r="49">
@@ -2867,7 +2867,7 @@
         <v>0.2</v>
       </c>
       <c r="C49" s="15" t="n">
-        <v>4.378520576800778</v>
+        <v>4.180818253384087</v>
       </c>
     </row>
   </sheetData>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="C8" s="18" t="n">
-        <v>0.0042</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="9">

--- a/engine/adnocdist_study/ADNOCDIST_Valuation_Model_09082026.xlsx
+++ b/engine/adnocdist_study/ADNOCDIST_Valuation_Model_09082026.xlsx
@@ -31,11 +31,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -173,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -213,20 +214,22 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -783,23 +786,23 @@
         <v>9478.001</v>
       </c>
       <c r="E2" s="22">
-        <f>Assumptions!$C$59+Assumptions!C$45-Assumptions!C$44</f>
+        <f>Assumptions!$C$75+Assumptions!C$49-Assumptions!C$48</f>
         <v/>
       </c>
       <c r="F2" s="22">
-        <f>E2+Assumptions!D$45-Assumptions!D$44</f>
+        <f>E2+Assumptions!D$49-Assumptions!D$48</f>
         <v/>
       </c>
       <c r="G2" s="22">
-        <f>F2+Assumptions!E$45-Assumptions!E$44</f>
+        <f>F2+Assumptions!E$49-Assumptions!E$48</f>
         <v/>
       </c>
       <c r="H2" s="22">
-        <f>G2+Assumptions!F$45-Assumptions!F$44</f>
+        <f>G2+Assumptions!F$49-Assumptions!F$48</f>
         <v/>
       </c>
       <c r="I2" s="22">
-        <f>H2+Assumptions!G$45-Assumptions!G$44</f>
+        <f>H2+Assumptions!G$49-Assumptions!G$48</f>
         <v/>
       </c>
     </row>
@@ -819,23 +822,23 @@
         <v>671.2729999999999</v>
       </c>
       <c r="E3" s="22">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="F3" s="22">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="G3" s="22">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="H3" s="22">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="I3" s="22">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
     </row>
@@ -855,23 +858,23 @@
         <v>1574.254</v>
       </c>
       <c r="E4" s="22">
-        <f>Assumptions!$C$47/365*('Income Statement'!E2-'Income Statement'!E3)</f>
+        <f>Assumptions!$C$54/365*('Income Statement'!E2-'Income Statement'!E3)</f>
         <v/>
       </c>
       <c r="F4" s="22">
-        <f>Assumptions!$C$47/365*('Income Statement'!F2-'Income Statement'!F3)</f>
+        <f>Assumptions!$C$54/365*('Income Statement'!F2-'Income Statement'!F3)</f>
         <v/>
       </c>
       <c r="G4" s="22">
-        <f>Assumptions!$C$47/365*('Income Statement'!G2-'Income Statement'!G3)</f>
+        <f>Assumptions!$C$54/365*('Income Statement'!G2-'Income Statement'!G3)</f>
         <v/>
       </c>
       <c r="H4" s="22">
-        <f>Assumptions!$C$47/365*('Income Statement'!H2-'Income Statement'!H3)</f>
+        <f>Assumptions!$C$54/365*('Income Statement'!H2-'Income Statement'!H3)</f>
         <v/>
       </c>
       <c r="I4" s="22">
-        <f>Assumptions!$C$47/365*('Income Statement'!I2-'Income Statement'!I3)</f>
+        <f>Assumptions!$C$54/365*('Income Statement'!I2-'Income Statement'!I3)</f>
         <v/>
       </c>
     </row>
@@ -891,23 +894,23 @@
         <v>3390.983</v>
       </c>
       <c r="E5" s="22">
-        <f>Assumptions!$C$46/365*'Income Statement'!E2</f>
+        <f>Assumptions!$C$53/365*'Income Statement'!E2</f>
         <v/>
       </c>
       <c r="F5" s="22">
-        <f>Assumptions!$C$46/365*'Income Statement'!F2</f>
+        <f>Assumptions!$C$53/365*'Income Statement'!F2</f>
         <v/>
       </c>
       <c r="G5" s="22">
-        <f>Assumptions!$C$46/365*'Income Statement'!G2</f>
+        <f>Assumptions!$C$53/365*'Income Statement'!G2</f>
         <v/>
       </c>
       <c r="H5" s="22">
-        <f>Assumptions!$C$46/365*'Income Statement'!H2</f>
+        <f>Assumptions!$C$53/365*'Income Statement'!H2</f>
         <v/>
       </c>
       <c r="I5" s="22">
-        <f>Assumptions!$C$46/365*'Income Statement'!I2</f>
+        <f>Assumptions!$C$53/365*'Income Statement'!I2</f>
         <v/>
       </c>
     </row>
@@ -953,32 +956,32 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
+      <c r="B7" s="34" t="n">
         <v>18891.629</v>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="34" t="n">
         <v>18180.794</v>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" s="34" t="n">
         <v>17675.365</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="24">
         <f>E2+E3+E4+E5+E6</f>
         <v/>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="24">
         <f>F2+F3+F4+F5+F6</f>
         <v/>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="24">
         <f>G2+G3+G4+G5+G6</f>
         <v/>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="24">
         <f>H2+H3+H4+H5+H6</f>
         <v/>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="24">
         <f>I2+I3+I4+I5+I6</f>
         <v/>
       </c>
@@ -999,23 +1002,23 @@
         <v>3230.423</v>
       </c>
       <c r="E8" s="22">
-        <f>Assumptions!$C$61+'Income Statement'!E18-Assumptions!$C$49*Assumptions!$C$4</f>
+        <f>Assumptions!$C$77+'Income Statement'!E18-'Income Statement'!E22</f>
         <v/>
       </c>
       <c r="F8" s="22">
-        <f>E8+'Income Statement'!F18-Assumptions!$C$49*Assumptions!$C$4</f>
+        <f>E8+'Income Statement'!F18-'Income Statement'!F22</f>
         <v/>
       </c>
       <c r="G8" s="22">
-        <f>F8+'Income Statement'!G18-Assumptions!$C$49*Assumptions!$C$4</f>
+        <f>F8+'Income Statement'!G18-'Income Statement'!G22</f>
         <v/>
       </c>
       <c r="H8" s="22">
-        <f>G8+'Income Statement'!H18-Assumptions!$C$49*Assumptions!$C$4</f>
+        <f>G8+'Income Statement'!H18-'Income Statement'!H22</f>
         <v/>
       </c>
       <c r="I8" s="22">
-        <f>H8+'Income Statement'!I18-Assumptions!$C$49*Assumptions!$C$4</f>
+        <f>H8+'Income Statement'!I18-'Income Statement'!I22</f>
         <v/>
       </c>
     </row>
@@ -1035,23 +1038,23 @@
         <v>230.374</v>
       </c>
       <c r="E9" s="22">
-        <f>Assumptions!$C$62+Assumptions!$C$69</f>
+        <f>Assumptions!$C$78+Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="F9" s="22">
-        <f>E9+Assumptions!$C$69</f>
+        <f>E9+Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="G9" s="22">
-        <f>F9+Assumptions!$C$69</f>
+        <f>F9+Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="H9" s="22">
-        <f>G9+Assumptions!$C$69</f>
+        <f>G9+Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="I9" s="22">
-        <f>H9+Assumptions!$C$69</f>
+        <f>H9+Assumptions!$C$85</f>
         <v/>
       </c>
     </row>
@@ -1071,23 +1074,23 @@
         <v>5545.975</v>
       </c>
       <c r="E10" s="22">
-        <f>Assumptions!$C$63</f>
+        <f>Assumptions!$C$79</f>
         <v/>
       </c>
       <c r="F10" s="22">
-        <f>Assumptions!$C$63</f>
+        <f>Assumptions!$C$79</f>
         <v/>
       </c>
       <c r="G10" s="22">
-        <f>Assumptions!$C$63</f>
+        <f>Assumptions!$C$79</f>
         <v/>
       </c>
       <c r="H10" s="22">
-        <f>Assumptions!$C$63</f>
+        <f>Assumptions!$C$79</f>
         <v/>
       </c>
       <c r="I10" s="22">
-        <f>Assumptions!$C$63</f>
+        <f>Assumptions!$C$79</f>
         <v/>
       </c>
     </row>
@@ -1107,23 +1110,23 @@
         <v>1446.327</v>
       </c>
       <c r="E11" s="22">
-        <f>Assumptions!$C$64</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="F11" s="22">
-        <f>Assumptions!$C$64</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="G11" s="22">
-        <f>Assumptions!$C$64</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="H11" s="22">
-        <f>Assumptions!$C$64</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="I11" s="22">
-        <f>Assumptions!$C$64</f>
+        <f>Assumptions!$C$80</f>
         <v/>
       </c>
     </row>
@@ -1139,23 +1142,23 @@
         <v>460.12</v>
       </c>
       <c r="E12" s="22">
-        <f>Assumptions!$C$65</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
       <c r="F12" s="22">
-        <f>Assumptions!$C$65</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
       <c r="G12" s="22">
-        <f>Assumptions!$C$65</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
       <c r="H12" s="22">
-        <f>Assumptions!$C$65</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
       <c r="I12" s="22">
-        <f>Assumptions!$C$65</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
     </row>
@@ -1175,23 +1178,23 @@
         <v>6762.146000000001</v>
       </c>
       <c r="E13" s="22">
-        <f>Assumptions!$C$48/365*('Income Statement'!E2-'Income Statement'!E3)</f>
+        <f>Assumptions!$C$55/365*('Income Statement'!E2-'Income Statement'!E3)</f>
         <v/>
       </c>
       <c r="F13" s="22">
-        <f>Assumptions!$C$48/365*('Income Statement'!F2-'Income Statement'!F3)</f>
+        <f>Assumptions!$C$55/365*('Income Statement'!F2-'Income Statement'!F3)</f>
         <v/>
       </c>
       <c r="G13" s="22">
-        <f>Assumptions!$C$48/365*('Income Statement'!G2-'Income Statement'!G3)</f>
+        <f>Assumptions!$C$55/365*('Income Statement'!G2-'Income Statement'!G3)</f>
         <v/>
       </c>
       <c r="H13" s="22">
-        <f>Assumptions!$C$48/365*('Income Statement'!H2-'Income Statement'!H3)</f>
+        <f>Assumptions!$C$55/365*('Income Statement'!H2-'Income Statement'!H3)</f>
         <v/>
       </c>
       <c r="I13" s="22">
-        <f>Assumptions!$C$48/365*('Income Statement'!I2-'Income Statement'!I3)</f>
+        <f>Assumptions!$C$55/365*('Income Statement'!I2-'Income Statement'!I3)</f>
         <v/>
       </c>
     </row>
@@ -1201,32 +1204,32 @@
           <t>TOTAL EQUITY AND LIABILITIES</t>
         </is>
       </c>
-      <c r="B14" s="32" t="n">
+      <c r="B14" s="34" t="n">
         <v>18891.629</v>
       </c>
-      <c r="C14" s="32" t="n">
+      <c r="C14" s="34" t="n">
         <v>18180.794</v>
       </c>
-      <c r="D14" s="32" t="n">
+      <c r="D14" s="34" t="n">
         <v>17675.365</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="24">
         <f>E8+E9+E10+E11+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="24">
         <f>F8+F9+F10+F11+F12+F13</f>
         <v/>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="24">
         <f>G8+G9+G10+G11+G12+G13</f>
         <v/>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="24">
         <f>H8+H9+H10+H11+H12+H13</f>
         <v/>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="24">
         <f>I8+I9+I10+I11+I12+I13</f>
         <v/>
       </c>
@@ -1237,13 +1240,13 @@
           <t>BALANCE CHECK (must be zero)</t>
         </is>
       </c>
-      <c r="B15" s="34" t="n">
+      <c r="B15" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="34" t="n">
+      <c r="C15" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="34" t="n">
+      <c r="D15" s="36" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="21">
@@ -1318,23 +1321,23 @@
       <c r="D17" s="16" t="n">
         <v>0.25843384</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="28">
         <f>E8/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="28">
         <f>F8/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="28">
         <f>G8/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="28">
         <f>H8/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="28">
         <f>I8/Assumptions!$C$4</f>
         <v/>
       </c>
@@ -1462,23 +1465,23 @@
       <c r="D3" s="18" t="n">
         <v>0.1017321411636604</v>
       </c>
-      <c r="E3" s="30">
+      <c r="E3" s="31">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="F3" s="30">
+      <c r="F3" s="31">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="G3" s="30">
+      <c r="G3" s="31">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="H3" s="30">
+      <c r="H3" s="31">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="I3" s="30">
+      <c r="I3" s="31">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
@@ -1489,13 +1492,13 @@
           <t>NOPAT = EBIT x (1 less the tax rate)</t>
         </is>
       </c>
-      <c r="B4" s="33" t="n">
+      <c r="B4" s="35" t="n">
         <v>2962.037770648459</v>
       </c>
-      <c r="C4" s="33" t="n">
+      <c r="C4" s="35" t="n">
         <v>2753.28964072531</v>
       </c>
-      <c r="D4" s="33" t="n">
+      <c r="D4" s="35" t="n">
         <v>3148.971399008107</v>
       </c>
       <c r="E4" s="17">
@@ -1535,23 +1538,23 @@
         <v>775.946</v>
       </c>
       <c r="E5" s="22">
-        <f>Assumptions!C$44</f>
+        <f>Assumptions!C$48</f>
         <v/>
       </c>
       <c r="F5" s="22">
-        <f>Assumptions!D$44</f>
+        <f>Assumptions!D$48</f>
         <v/>
       </c>
       <c r="G5" s="22">
-        <f>Assumptions!E$44</f>
+        <f>Assumptions!E$48</f>
         <v/>
       </c>
       <c r="H5" s="22">
-        <f>Assumptions!F$44</f>
+        <f>Assumptions!F$48</f>
         <v/>
       </c>
       <c r="I5" s="22">
-        <f>Assumptions!G$44</f>
+        <f>Assumptions!G$48</f>
         <v/>
       </c>
     </row>
@@ -1571,23 +1574,23 @@
         <v>-1207.394</v>
       </c>
       <c r="E6" s="22">
-        <f>-Assumptions!C$45</f>
+        <f>-Assumptions!C$49</f>
         <v/>
       </c>
       <c r="F6" s="22">
-        <f>-Assumptions!D$45</f>
+        <f>-Assumptions!D$49</f>
         <v/>
       </c>
       <c r="G6" s="22">
-        <f>-Assumptions!E$45</f>
+        <f>-Assumptions!E$49</f>
         <v/>
       </c>
       <c r="H6" s="22">
-        <f>-Assumptions!F$45</f>
+        <f>-Assumptions!F$49</f>
         <v/>
       </c>
       <c r="I6" s="22">
-        <f>-Assumptions!G$45</f>
+        <f>-Assumptions!G$49</f>
         <v/>
       </c>
     </row>
@@ -1627,26 +1630,26 @@
           <t>FREE CASH FLOW TO THE FIRM</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n"/>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="32" t="n"/>
-      <c r="E8" s="23">
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="24">
         <f>E4+E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="24">
         <f>F4+F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="24">
         <f>G4+G5+G6+G7</f>
         <v/>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="24">
         <f>H4+H5+H6+H7</f>
         <v/>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="24">
         <f>I4+I5+I6+I7</f>
         <v/>
       </c>
@@ -1667,23 +1670,23 @@
         <v>-2599.146</v>
       </c>
       <c r="E9" s="22">
-        <f>-Assumptions!$C$49*Assumptions!$C$4</f>
+        <f>-'Income Statement'!E22</f>
         <v/>
       </c>
       <c r="F9" s="22">
-        <f>-Assumptions!$C$49*Assumptions!$C$4</f>
+        <f>-'Income Statement'!F22</f>
         <v/>
       </c>
       <c r="G9" s="22">
-        <f>-Assumptions!$C$49*Assumptions!$C$4</f>
+        <f>-'Income Statement'!G22</f>
         <v/>
       </c>
       <c r="H9" s="22">
-        <f>-Assumptions!$C$49*Assumptions!$C$4</f>
+        <f>-'Income Statement'!H22</f>
         <v/>
       </c>
       <c r="I9" s="22">
-        <f>-Assumptions!$C$49*Assumptions!$C$4</f>
+        <f>-'Income Statement'!I22</f>
         <v/>
       </c>
     </row>
@@ -2017,9 +2020,9 @@
           <t>THESE CELLS ARE A WHOLE-MODEL RE-RUN — 50,000 simulated price paths each. They do NOT redraw when a driver on the Assumptions sheet changes.</t>
         </is>
       </c>
-      <c r="B2" s="24" t="n"/>
-      <c r="C2" s="24" t="n"/>
-      <c r="D2" s="25" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="26" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2214,11 +2217,11 @@
           <t>EACH CELL IS A COMPLETE REVALUATION of the whole model. These grids do NOT redraw when a driver changes.</t>
         </is>
       </c>
-      <c r="B2" s="24" t="n"/>
-      <c r="C2" s="24" t="n"/>
-      <c r="D2" s="24" t="n"/>
-      <c r="E2" s="24" t="n"/>
-      <c r="F2" s="25" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="26" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2227,19 +2230,19 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>4.472057106292805</v>
+        <v>5.037845630037896</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.746931359768977</v>
+        <v>5.345214853859902</v>
       </c>
       <c r="D3" s="15" t="n">
-        <v>5.076582096917631</v>
+        <v>5.713836104953238</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>5.47952561256779</v>
+        <v>6.16441462979946</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>5.983683475617217</v>
+        <v>6.728172817732825</v>
       </c>
     </row>
     <row r="4">
@@ -2249,19 +2252,19 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>4.133065423237127</v>
+        <v>4.658763041404357</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>4.357643870613312</v>
+        <v>4.909890610408024</v>
       </c>
       <c r="D4" s="15" t="n">
-        <v>4.622723217256807</v>
+        <v>5.206306997169102</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>4.940607713204206</v>
+        <v>5.561771030445217</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>5.32914727592826</v>
+        <v>5.996242801840086</v>
       </c>
     </row>
     <row r="5">
@@ -2271,19 +2274,19 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>3.842746999092251</v>
+        <v>4.334107990736483</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>4.028603553261314</v>
+        <v>4.541936057842556</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>4.245038895322488</v>
+        <v>4.783957863288807</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>4.500488664637969</v>
+        <v>5.069606287348343</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>4.806805518226626</v>
+        <v>5.412135179525237</v>
       </c>
     </row>
     <row r="6">
@@ -2293,19 +2296,19 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>3.59128714076265</v>
+        <v>4.052905511891289</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>3.746786204909884</v>
+        <v>4.226787299827193</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>3.925782439022962</v>
+        <v>4.426944036409902</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>4.134212042214958</v>
+        <v>4.660013683874013</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>4.38019467206157</v>
+        <v>4.935075786102526</v>
       </c>
     </row>
     <row r="7">
@@ -2315,19 +2318,19 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>3.371344144996052</v>
+        <v>3.806945979527142</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>3.502669927571309</v>
+        <v>3.953796778929035</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>3.652323326060763</v>
+        <v>4.121141840732053</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>3.824574900660831</v>
+        <v>4.31375658044441</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>4.025133733494157</v>
+        <v>4.538024994088219</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
@@ -2360,7 +2363,7 @@
         <v>0.06437428020423498</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>5.076582096917631</v>
+        <v>5.713836104953238</v>
       </c>
     </row>
     <row r="11">
@@ -2373,7 +2376,7 @@
         <v>0.06937428020423497</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>4.622723217256807</v>
+        <v>5.206306997169102</v>
       </c>
     </row>
     <row r="12">
@@ -2386,7 +2389,7 @@
         <v>0.07437428020423498</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>4.245038895322488</v>
+        <v>4.783957863288807</v>
       </c>
     </row>
     <row r="13">
@@ -2399,7 +2402,7 @@
         <v>0.07937428020423498</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>3.925782439022962</v>
+        <v>4.426944036409902</v>
       </c>
     </row>
     <row r="14">
@@ -2412,7 +2415,7 @@
         <v>0.08437428020423497</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>3.652323326060763</v>
+        <v>4.121141840732053</v>
       </c>
     </row>
     <row r="15">
@@ -2425,7 +2428,7 @@
         <v>0.005</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>3.842746999092251</v>
+        <v>4.334107990736483</v>
       </c>
     </row>
     <row r="16">
@@ -2438,7 +2441,7 @@
         <v>0.01</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>4.028603553261314</v>
+        <v>4.541936057842556</v>
       </c>
     </row>
     <row r="17">
@@ -2451,7 +2454,7 @@
         <v>0.015</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>4.245038895322488</v>
+        <v>4.783957863288807</v>
       </c>
     </row>
     <row r="18">
@@ -2464,7 +2467,7 @@
         <v>0.02</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>4.500488664637969</v>
+        <v>5.069606287348343</v>
       </c>
     </row>
     <row r="19">
@@ -2477,7 +2480,7 @@
         <v>0.025</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>4.806805518226626</v>
+        <v>5.412135179525237</v>
       </c>
     </row>
     <row r="20">
@@ -2490,7 +2493,7 @@
         <v>0.45</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>5.083566069029051</v>
+        <v>5.721632266901376</v>
       </c>
     </row>
     <row r="21">
@@ -2503,7 +2506,7 @@
         <v>0.55</v>
       </c>
       <c r="C21" s="15" t="n">
-        <v>4.627963827527954</v>
+        <v>5.212160196485639</v>
       </c>
     </row>
     <row r="22">
@@ -2516,7 +2519,7 @@
         <v>0.6494</v>
       </c>
       <c r="C22" s="15" t="n">
-        <v>4.245038895322488</v>
+        <v>4.783957863288807</v>
       </c>
     </row>
     <row r="23">
@@ -2529,7 +2532,7 @@
         <v>0.8</v>
       </c>
       <c r="C23" s="15" t="n">
-        <v>3.765473170804389</v>
+        <v>4.247686654673135</v>
       </c>
     </row>
     <row r="24">
@@ -2542,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="15" t="n">
-        <v>3.264593336664223</v>
+        <v>3.687579642884075</v>
       </c>
     </row>
     <row r="25">
@@ -2555,7 +2558,7 @@
         <v>-0.01</v>
       </c>
       <c r="C25" s="15" t="n">
-        <v>3.995245141207556</v>
+        <v>4.503551144301958</v>
       </c>
     </row>
     <row r="26">
@@ -2568,7 +2571,7 @@
         <v>-0.005</v>
       </c>
       <c r="C26" s="15" t="n">
-        <v>4.161499559846868</v>
+        <v>4.681463152860606</v>
       </c>
     </row>
     <row r="27">
@@ -2581,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="15" t="n">
-        <v>4.330957230076974</v>
+        <v>4.862800051117585</v>
       </c>
     </row>
     <row r="28">
@@ -2594,7 +2597,7 @@
         <v>0.005</v>
       </c>
       <c r="C28" s="15" t="n">
-        <v>4.503665582326194</v>
+        <v>5.047612510089233</v>
       </c>
     </row>
     <row r="29">
@@ -2607,7 +2610,7 @@
         <v>0.01</v>
       </c>
       <c r="C29" s="15" t="n">
-        <v>4.679672518529684</v>
+        <v>5.235951704116874</v>
       </c>
     </row>
     <row r="30">
@@ -2620,7 +2623,7 @@
         <v>-0.1</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>3.495985504611076</v>
+        <v>3.980351258054539</v>
       </c>
     </row>
     <row r="31">
@@ -2633,7 +2636,7 @@
         <v>-0.05</v>
       </c>
       <c r="C31" s="15" t="n">
-        <v>3.870512199966782</v>
+        <v>4.382154560671673</v>
       </c>
     </row>
     <row r="32">
@@ -2646,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>4.245038895322488</v>
+        <v>4.783957863288807</v>
       </c>
     </row>
     <row r="33">
@@ -2659,7 +2662,7 @@
         <v>0.05</v>
       </c>
       <c r="C33" s="15" t="n">
-        <v>4.619565590678196</v>
+        <v>5.185761165905943</v>
       </c>
     </row>
     <row r="34">
@@ -2672,7 +2675,7 @@
         <v>0.1</v>
       </c>
       <c r="C34" s="15" t="n">
-        <v>4.994092286033902</v>
+        <v>5.587564468523079</v>
       </c>
     </row>
     <row r="35">
@@ -2685,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="C35" s="15" t="n">
-        <v>4.245038895322488</v>
+        <v>4.783957863288807</v>
       </c>
     </row>
     <row r="36">
@@ -2698,7 +2701,7 @@
         <v>150</v>
       </c>
       <c r="C36" s="15" t="n">
-        <v>4.399700826320476</v>
+        <v>4.938619794286794</v>
       </c>
     </row>
     <row r="37">
@@ -2711,7 +2714,7 @@
         <v>295</v>
       </c>
       <c r="C37" s="15" t="n">
-        <v>4.549207359618531</v>
+        <v>5.088126327584848</v>
       </c>
     </row>
     <row r="38">
@@ -2724,7 +2727,7 @@
         <v>450</v>
       </c>
       <c r="C38" s="15" t="n">
-        <v>4.709024688316452</v>
+        <v>5.247943656282771</v>
       </c>
     </row>
     <row r="39">
@@ -2737,7 +2740,7 @@
         <v>600</v>
       </c>
       <c r="C39" s="15" t="n">
-        <v>4.863686619314439</v>
+        <v>5.402605587280759</v>
       </c>
     </row>
     <row r="40">
@@ -2750,7 +2753,7 @@
         <v>0.09</v>
       </c>
       <c r="C40" s="15" t="n">
-        <v>4.305226915811582</v>
+        <v>4.851251222861921</v>
       </c>
     </row>
     <row r="41">
@@ -2763,7 +2766,7 @@
         <v>0.1017</v>
       </c>
       <c r="C41" s="15" t="n">
-        <v>4.245038895322488</v>
+        <v>4.783957863288807</v>
       </c>
     </row>
     <row r="42">
@@ -2776,7 +2779,7 @@
         <v>0.12</v>
       </c>
       <c r="C42" s="15" t="n">
-        <v>4.15089865814724</v>
+        <v>4.678704147033425</v>
       </c>
     </row>
     <row r="43">
@@ -2789,7 +2792,7 @@
         <v>0.15</v>
       </c>
       <c r="C43" s="15" t="n">
-        <v>3.996570400482897</v>
+        <v>4.506157071204932</v>
       </c>
     </row>
     <row r="44">
@@ -2802,7 +2805,7 @@
         <v>0.18</v>
       </c>
       <c r="C44" s="15" t="n">
-        <v>3.842242142818554</v>
+        <v>4.333609995376437</v>
       </c>
     </row>
     <row r="45">
@@ -2815,7 +2818,7 @@
         <v>-0.2</v>
       </c>
       <c r="C45" s="15" t="n">
-        <v>4.309259537260891</v>
+        <v>4.848178505227209</v>
       </c>
     </row>
     <row r="46">
@@ -2828,7 +2831,7 @@
         <v>-0.1</v>
       </c>
       <c r="C46" s="15" t="n">
-        <v>4.27714921629169</v>
+        <v>4.816068184258008</v>
       </c>
     </row>
     <row r="47">
@@ -2841,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="C47" s="15" t="n">
-        <v>4.245038895322488</v>
+        <v>4.783957863288807</v>
       </c>
     </row>
     <row r="48">
@@ -2854,7 +2857,7 @@
         <v>0.1</v>
       </c>
       <c r="C48" s="15" t="n">
-        <v>4.212928574353287</v>
+        <v>4.751847542319606</v>
       </c>
     </row>
     <row r="49">
@@ -2867,7 +2870,7 @@
         <v>0.2</v>
       </c>
       <c r="C49" s="15" t="n">
-        <v>4.180818253384087</v>
+        <v>4.719737221350404</v>
       </c>
     </row>
   </sheetData>
@@ -2960,23 +2963,23 @@
       <c r="D2" s="16" t="n">
         <v>0.224</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="28">
         <f>'Income Statement'!E19</f>
         <v/>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="28">
         <f>'Income Statement'!F19</f>
         <v/>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="28">
         <f>'Income Statement'!G19</f>
         <v/>
       </c>
-      <c r="H2" s="26">
+      <c r="H2" s="28">
         <f>'Income Statement'!H19</f>
         <v/>
       </c>
-      <c r="I2" s="26">
+      <c r="I2" s="28">
         <f>'Income Statement'!I19</f>
         <v/>
       </c>
@@ -2996,23 +2999,23 @@
       <c r="D3" s="16" t="n">
         <v>0.25843384</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="28">
         <f>'Balance Sheet'!E17</f>
         <v/>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="28">
         <f>'Balance Sheet'!F17</f>
         <v/>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="28">
         <f>'Balance Sheet'!G17</f>
         <v/>
       </c>
-      <c r="H3" s="26">
+      <c r="H3" s="28">
         <f>'Balance Sheet'!H17</f>
         <v/>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="28">
         <f>'Balance Sheet'!I17</f>
         <v/>
       </c>
@@ -3032,24 +3035,24 @@
       <c r="D4" s="16" t="n">
         <v>0.20793168</v>
       </c>
-      <c r="E4" s="26">
-        <f>Assumptions!$C$49</f>
-        <v/>
-      </c>
-      <c r="F4" s="26">
-        <f>Assumptions!$C$49</f>
-        <v/>
-      </c>
-      <c r="G4" s="26">
-        <f>Assumptions!$C$49</f>
-        <v/>
-      </c>
-      <c r="H4" s="26">
-        <f>Assumptions!$C$49</f>
-        <v/>
-      </c>
-      <c r="I4" s="26">
-        <f>Assumptions!$C$49</f>
+      <c r="E4" s="28">
+        <f>Assumptions!$C$56</f>
+        <v/>
+      </c>
+      <c r="F4" s="28">
+        <f>Assumptions!$C$56</f>
+        <v/>
+      </c>
+      <c r="G4" s="28">
+        <f>Assumptions!$C$56</f>
+        <v/>
+      </c>
+      <c r="H4" s="28">
+        <f>Assumptions!$C$56</f>
+        <v/>
+      </c>
+      <c r="I4" s="28">
+        <f>Assumptions!$C$56</f>
         <v/>
       </c>
     </row>
@@ -3131,32 +3134,32 @@
           <t>Net debt to EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="37" t="n">
         <v>0.6245201523772669</v>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="37" t="n">
         <v>0.6891274604366304</v>
       </c>
-      <c r="D7" s="35" t="n">
+      <c r="D7" s="37" t="n">
         <v>0.6972056848571196</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="30">
         <f>'Balance Sheet'!E16/'Income Statement'!E8</f>
         <v/>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="30">
         <f>'Balance Sheet'!F16/'Income Statement'!F8</f>
         <v/>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="30">
         <f>'Balance Sheet'!G16/'Income Statement'!G8</f>
         <v/>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="30">
         <f>'Balance Sheet'!H16/'Income Statement'!H8</f>
         <v/>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="30">
         <f>'Balance Sheet'!I16/'Income Statement'!I8</f>
         <v/>
       </c>
@@ -3245,9 +3248,9 @@
           <t>Peer observations are a CROSS-CHECK. They are not the source of any number in this valuation: the reference multiple is triangulated from the company’s own history on the Relative &amp; Normalized sheet.</t>
         </is>
       </c>
-      <c r="B2" s="24" t="n"/>
-      <c r="C2" s="24" t="n"/>
-      <c r="D2" s="25" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="26" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -3255,7 +3258,7 @@
           <t>Aldrees Petroleum and Transport Services</t>
         </is>
       </c>
-      <c r="B3" s="35" t="n">
+      <c r="B3" s="37" t="n">
         <v>12.89</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -3270,7 +3273,7 @@
           <t>Saudi Automotive Services Company / SASCO</t>
         </is>
       </c>
-      <c r="B4" s="35" t="n">
+      <c r="B4" s="37" t="n">
         <v>12.28</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -3285,7 +3288,7 @@
           <t>Alimentation Couche-Tard</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="37" t="n">
         <v>10.66</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -3300,7 +3303,7 @@
           <t>Casey's General Stores</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="37" t="n">
         <v>22.41</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -3315,7 +3318,7 @@
           <t>Murphy USA</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="37" t="n">
         <v>10.03</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -3330,7 +3333,7 @@
           <t>OMV Petrom</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="37" t="n">
         <v>9.91</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -3345,7 +3348,7 @@
           <t>Vibra Energia</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="37" t="n">
         <v>7.7</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -3360,7 +3363,7 @@
           <t>Ultrapar Participacoes</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="37" t="n">
         <v>6.8</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -3375,7 +3378,7 @@
           <t>PEER AVERAGE (context only)</t>
         </is>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="32">
         <f>AVERAGE(B3:B10)</f>
         <v/>
       </c>
@@ -3396,8 +3399,8 @@
           <t>This company, on the traded price</t>
         </is>
       </c>
-      <c r="B12" s="36">
-        <f>(Assumptions!$C$5+Assumptions!$C$18+Assumptions!$C$64)/'Income Statement'!D8</f>
+      <c r="B12" s="38">
+        <f>(Assumptions!$C$5+Assumptions!$C$18+Assumptions!$C$80)/'Income Statement'!D8</f>
         <v/>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -3578,7 +3581,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>'Relative &amp; Normalized'!B20</f>
+        <f>'Relative &amp; Normalized'!B23</f>
         <v/>
       </c>
     </row>
@@ -3671,11 +3674,11 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <f>'Relative &amp; Normalized'!B15</f>
+        <f>'Relative &amp; Normalized'!B18</f>
         <v/>
       </c>
       <c r="C3" s="7">
-        <f>'Relative &amp; Normalized'!B15</f>
+        <f>'Relative &amp; Normalized'!B18</f>
         <v/>
       </c>
       <c r="D3" s="13" t="n">
@@ -3694,11 +3697,11 @@
         </is>
       </c>
       <c r="B4" s="7">
-        <f>'Relative &amp; Normalized'!B7</f>
+        <f>'Relative &amp; Normalized'!B9</f>
         <v/>
       </c>
       <c r="C4" s="7">
-        <f>'Relative &amp; Normalized'!B9</f>
+        <f>'Relative &amp; Normalized'!B11</f>
         <v/>
       </c>
       <c r="D4" s="13" t="n">
@@ -3717,11 +3720,11 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>'Relative &amp; Normalized'!B19</f>
+        <f>'Relative &amp; Normalized'!B22</f>
         <v/>
       </c>
       <c r="C5" s="7">
-        <f>'Relative &amp; Normalized'!B19</f>
+        <f>'Relative &amp; Normalized'!B22</f>
         <v/>
       </c>
       <c r="D5" s="13" t="n">
@@ -3801,7 +3804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4154,25 +4157,26 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1">
+    <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Terminal beta drift, as a fraction of the distance to a market beta of one</t>
+          <t>Terminal beta = the measured beta (flat, pegged market)</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>so the terminal beta is DERIVED from the measured one, not asserted beside it</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="n">
-        <v>0.389</v>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="C22" s="21">
+        <f>Assumptions!$C$11</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Terminal beta = measured beta + drift x (1 less measured beta)</t>
+          <t>Terminal cost of equity = normalised risk-free + terminal beta x premium</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -4180,15 +4184,15 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C23" s="21">
-        <f>Assumptions!$C$11+Assumptions!$C$22*(1-Assumptions!$C$11)</f>
+      <c r="C23" s="19">
+        <f>Assumptions!$C$9+Assumptions!$C$22*Assumptions!$C$10</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of equity = normalised risk-free + terminal beta x premium</t>
+          <t>Terminal debt weight = today's weight (flat, pegged market)</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -4196,170 +4200,182 @@
           <t>calculated</t>
         </is>
       </c>
-      <c r="C24" s="19">
-        <f>Assumptions!$C$9+Assumptions!$C$23*Assumptions!$C$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1">
+      <c r="C24" s="14">
+        <f>Assumptions!$C$20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Terminal debt weight</t>
+          <t>Terminal cost of capital = terminal equity and debt weights on their costs</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>normalised capital structure</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="26">
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="C25" s="19">
+        <f>(1-Assumptions!$C$24)*Assumptions!$C$23+Assumptions!$C$24*Assumptions!$C$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Terminal cost of capital = terminal equity and debt weights on their costs</t>
+          <t>Long-run growth after the forecast period</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>calculated</t>
-        </is>
-      </c>
-      <c r="C26" s="19">
-        <f>(1-Assumptions!$C$25)*Assumptions!$C$24+Assumptions!$C$25*Assumptions!$C$17</f>
-        <v/>
+          <t>below domestic inflation</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Long-run growth after the forecast period</t>
+          <t>Terminal return on invested capital</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>below domestic inflation</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Terminal return on invested capital</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
           <t>fade from the realised return</t>
         </is>
       </c>
-      <c r="C28" s="13" t="n">
+      <c r="C27" s="13" t="n">
         <v>0.25</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>Volume and price drivers</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr"/>
-      <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Volume and price drivers — built bottom-up</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Service-station network growth</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>network +11.3% y/y to June 2026</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G29" s="18" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Retail fuel volume growth</t>
+          <t>Growth in litres sold per station</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>network and mobility, less transition drag</t>
+          <t>realised MINUS 9.3% y/y to June 2026</t>
         </is>
       </c>
       <c r="C30" s="18" t="n">
-        <v>0.012</v>
+        <v>-0.01</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>0.02</v>
+        <v>-0.025</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>0.018</v>
+        <v>-0.02</v>
       </c>
       <c r="F30" s="18" t="n">
-        <v>0.015</v>
+        <v>-0.01</v>
       </c>
       <c r="G30" s="18" t="n">
-        <v>0.012</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Commercial fuel volume growth</t>
+          <t>Corporate fuel volume growth</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>aviation growth, corporate rationalisation</t>
+          <t>realised MINUS 2.6% in the first half</t>
         </is>
       </c>
       <c r="C31" s="18" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>0.025</v>
+        <v>0.005</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F31" s="18" t="n">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
       <c r="G31" s="18" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Realised retail price per litre (AED)</t>
+          <t>Aviation fuel volume growth</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>crude-linked price path</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="D32" s="16" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E32" s="16" t="n">
-        <v>2.363</v>
-      </c>
-      <c r="F32" s="16" t="n">
-        <v>2.387</v>
-      </c>
-      <c r="G32" s="16" t="n">
-        <v>2.411</v>
+          <t>realised PLUS 53.9% in the first half, faded</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G32" s="18" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Realised commercial price per litre (AED)</t>
+          <t>Realised retail price per litre (AED)</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -4368,528 +4384,586 @@
         </is>
       </c>
       <c r="C33" s="16" t="n">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="D33" s="16" t="n">
-        <v>2.95</v>
+        <v>2.34</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>2.98</v>
+        <v>2.363</v>
       </c>
       <c r="F33" s="16" t="n">
-        <v>3.01</v>
+        <v>2.387</v>
       </c>
       <c r="G33" s="16" t="n">
-        <v>3.04</v>
+        <v>2.411</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Retail margin per litre, escalation</t>
+          <t>Realised corporate price per litre (AED)</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>domestic escalator</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D34" s="18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E34" s="18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F34" s="18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G34" s="18" t="n">
-        <v>0.02</v>
+          <t>crude-linked price path</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="G34" s="16" t="n">
+        <v>3.04</v>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Commercial margin per litre, escalation</t>
+          <t>Realised aviation price per litre (AED)</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>realised step then domestic escalator</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F35" s="18" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G35" s="18" t="n">
-        <v>0.02</v>
+          <t>crude-linked; jet prices ~50% above</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>4.53</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Non-fuel retail revenue growth</t>
+          <t>Retail margin per litre, escalation</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>company's own doubling target to 2030</t>
+          <t>domestic escalator</t>
         </is>
       </c>
       <c r="C36" s="18" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="F36" s="18" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G36" s="18" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Non-fuel retail gross margin</t>
+          <t>Commercial margin per litre, escalation</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>realised first half 2026</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="D37" s="13" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E37" s="13" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F37" s="13" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="G37" s="13" t="n">
-        <v>0.5600000000000001</v>
+          <t>realised step then domestic escalator</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G37" s="18" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Inventory movement, normalised frame (AED m)</t>
+          <t>Fuel transaction growth</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>realised first half only, nil thereafter</t>
-        </is>
-      </c>
-      <c r="C38" s="20" t="n">
-        <v>762</v>
-      </c>
-      <c r="D38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="20" t="n">
-        <v>0</v>
+          <t>realised +4.9% in the first half</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G38" s="18" t="n">
+        <v>0.018</v>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Inventory movement, through-cycle frame (AED m)</t>
+          <t>Growth in the non-fuel conversion rate</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>FY2024-FY2025 average carried forward</t>
-        </is>
-      </c>
-      <c r="C39" s="20" t="n">
-        <v>950</v>
-      </c>
-      <c r="D39" s="20" t="n">
-        <v>295</v>
-      </c>
-      <c r="E39" s="20" t="n">
-        <v>295</v>
-      </c>
-      <c r="F39" s="20" t="n">
-        <v>295</v>
-      </c>
-      <c r="G39" s="20" t="n">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Cost, capital spending and working capital</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
+          <t>FELL from 27.0% to 26.2% y/y</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G39" s="18" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Growth in the average non-fuel basket</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>domestic escalator plus food service</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G40" s="18" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Cash operating cost growth</t>
+          <t>Non-fuel retail gross margin</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>domestic escalator plus network, less efficiency</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D41" s="18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F41" s="18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G41" s="18" t="n">
-        <v>0.04</v>
+          <t>realised first half 2026</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Other income growth</t>
+          <t>Inventory movement, normalised frame (AED m)</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>domestic escalator</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D42" s="18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E42" s="18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F42" s="18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G42" s="18" t="n">
-        <v>0.03</v>
+          <t>realised first half only, nil thereafter</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="n">
+        <v>762</v>
+      </c>
+      <c r="D42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Impairments and other operating expenses (AED m)</t>
+          <t>Inventory movement, through-cycle frame (AED m)</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>realised then normalised</t>
+          <t>FY2024-FY2025 average carried forward</t>
         </is>
       </c>
       <c r="C43" s="20" t="n">
-        <v>360</v>
+        <v>950</v>
       </c>
       <c r="D43" s="20" t="n">
-        <v>220</v>
+        <v>295</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>225</v>
+        <v>295</v>
       </c>
       <c r="F43" s="20" t="n">
-        <v>230</v>
+        <v>295</v>
       </c>
       <c r="G43" s="20" t="n">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Depreciation and amortisation (AED m)</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>grown on the asset base</t>
-        </is>
-      </c>
-      <c r="C44" s="20" t="n">
-        <v>800</v>
-      </c>
-      <c r="D44" s="20" t="n">
-        <v>830</v>
-      </c>
-      <c r="E44" s="20" t="n">
-        <v>862</v>
-      </c>
-      <c r="F44" s="20" t="n">
-        <v>894</v>
-      </c>
-      <c r="G44" s="20" t="n">
-        <v>926</v>
-      </c>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Cost, capital spending and working capital</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Capital expenditure (AED m)</t>
+          <t>Cash operating cost growth</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>company's own FY2026 guidance, then network</t>
-        </is>
-      </c>
-      <c r="C45" s="20" t="n">
-        <v>1010</v>
-      </c>
-      <c r="D45" s="20" t="n">
-        <v>1060</v>
-      </c>
-      <c r="E45" s="20" t="n">
-        <v>1100</v>
-      </c>
-      <c r="F45" s="20" t="n">
-        <v>1140</v>
-      </c>
-      <c r="G45" s="20" t="n">
-        <v>1180</v>
+          <t>domestic escalator plus network, less efficiency</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F45" s="18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G45" s="18" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Receivable days including parent balances</t>
+          <t>Other income growth</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>FY2025 statements</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="n">
-        <v>34.47981727637454</v>
+          <t>domestic escalator</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F46" s="18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G46" s="18" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Inventory days</t>
+          <t>Impairments and other operating expenses (AED m)</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>FY2025 statements</t>
-        </is>
-      </c>
-      <c r="C47" s="15" t="n">
-        <v>19.84754045195324</v>
+          <t>realised then normalised</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="n">
+        <v>360</v>
+      </c>
+      <c r="D47" s="20" t="n">
+        <v>220</v>
+      </c>
+      <c r="E47" s="20" t="n">
+        <v>225</v>
+      </c>
+      <c r="F47" s="20" t="n">
+        <v>230</v>
+      </c>
+      <c r="G47" s="20" t="n">
+        <v>235</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Payable days including parent balances</t>
+          <t>Depreciation and amortisation (AED m)</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>FY2025 statements</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="n">
-        <v>85.25432762248899</v>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="C48" s="22">
+        <f>Segments!C36</f>
+        <v/>
+      </c>
+      <c r="D48" s="22">
+        <f>Segments!D36</f>
+        <v/>
+      </c>
+      <c r="E48" s="22">
+        <f>Segments!E36</f>
+        <v/>
+      </c>
+      <c r="F48" s="22">
+        <f>Segments!F36</f>
+        <v/>
+      </c>
+      <c r="G48" s="22">
+        <f>Segments!G36</f>
+        <v/>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Dividend per share (AED)</t>
+          <t>Capital expenditure (AED m)</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>stated policy</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="n">
-        <v>0.2057</v>
+          <t>calculated</t>
+        </is>
+      </c>
+      <c r="C49" s="22">
+        <f>Segments!C40</f>
+        <v/>
+      </c>
+      <c r="D49" s="22">
+        <f>Segments!D40</f>
+        <v/>
+      </c>
+      <c r="E49" s="22">
+        <f>Segments!E40</f>
+        <v/>
+      </c>
+      <c r="F49" s="22">
+        <f>Segments!F40</f>
+        <v/>
+      </c>
+      <c r="G49" s="22">
+        <f>Segments!G40</f>
+        <v/>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Dividend payout ratio</t>
+          <t>Depreciation rate on the opening fixed and right-of-use base</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>paid against earnings since listing</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="n">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>Opening position, from the audited FY2025 balance sheet</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr"/>
-      <c r="C51" s="2" t="inlineStr"/>
-      <c r="D51" s="2" t="inlineStr"/>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
+          <t>measured off the audited FY2025 accounts</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>0.08359999999999999</v>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance capital spending, share of the opening base</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>set equal to the depreciation rate: a network replaces what it consumes</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="n">
+        <v>0.08359999999999999</v>
+      </c>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Retail fuel volume, FY2025 (million litres)</t>
+          <t>Capital cost per station added (AED m)</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>disclosure</t>
-        </is>
-      </c>
-      <c r="C52" s="20" t="n">
-        <v>11042</v>
+          <t>backed out of the company's own FY2026 guidance</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="n">
+        <v>3.5924</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Commercial fuel volume, FY2025 (million litres)</t>
+          <t>Receivable days including parent balances</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>disclosure</t>
-        </is>
-      </c>
-      <c r="C53" s="20" t="n">
-        <v>4668</v>
+          <t>FY2025 statements</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="n">
+        <v>34.47981727637454</v>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Retail margin per litre, FY2025 (AED)</t>
+          <t>Inventory days</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>unit build: segment gross profit less inventory movement, over volume</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="n">
-        <v>0.3542836442673429</v>
+          <t>FY2025 statements</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="n">
+        <v>19.84754045195324</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Commercial margin per litre, FY2025 (AED)</t>
+          <t>Payable days including parent balances</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>unit build: segment gross profit less inventory movement, over volume</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="n">
-        <v>0.367395029991431</v>
+          <t>FY2025 statements</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="n">
+        <v>85.25432762248899</v>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Non-fuel retail revenue, FY2025 (AED m)</t>
+          <t>Dividend per share (AED)</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>disclosure</t>
-        </is>
-      </c>
-      <c r="C56" s="20" t="n">
-        <v>1783.747</v>
+          <t>stated policy</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="n">
+        <v>0.2057</v>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Cash operating costs, FY2025 (AED m)</t>
+          <t>Dividend policy floor, share of net profit</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>disclosure</t>
-        </is>
-      </c>
-      <c r="C57" s="20" t="n">
-        <v>2547.6</v>
-      </c>
-    </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>Other income, FY2025 (AED m)</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>disclosure</t>
-        </is>
-      </c>
-      <c r="C58" s="20" t="n">
-        <v>167.665</v>
-      </c>
+          <t>the policy the company states: a minimum of 75%</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>Anchors — the annualised disclosed first half of 2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Fixed and right-of-use assets, FY2025 (AED m)</t>
+          <t>Service stations, June 2026</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
@@ -4897,14 +4971,14 @@
           <t>disclosure</t>
         </is>
       </c>
-      <c r="C59" s="20" t="n">
-        <v>9478.001</v>
+      <c r="C59" s="23" t="n">
+        <v>1045</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Goodwill, intangibles and other non-current, FY2025 (AED m)</t>
+          <t>Service stations, FY2025 year end</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
@@ -4912,29 +4986,29 @@
           <t>disclosure</t>
         </is>
       </c>
-      <c r="C60" s="20" t="n">
-        <v>671.2729999999999</v>
+      <c r="C60" s="23" t="n">
+        <v>1010</v>
       </c>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Equity attributable to owners, FY2025 (AED m)</t>
+          <t>Litres per station, first half annualised (million)</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>disclosure</t>
-        </is>
-      </c>
-      <c r="C61" s="20" t="n">
-        <v>3230.423</v>
+          <t>disclosed retail volume over the disclosed station count</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="n">
+        <v>10.288995215311</v>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Non-controlling interests, FY2025 (AED m)</t>
+          <t>Corporate fuel volume, first half annualised (million litres)</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
@@ -4942,14 +5016,14 @@
           <t>disclosure</t>
         </is>
       </c>
-      <c r="C62" s="20" t="n">
-        <v>230.374</v>
+      <c r="C62" s="16" t="n">
+        <v>4030</v>
       </c>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Borrowings, FY2025 (AED m)</t>
+          <t>Aviation fuel volume, first half annualised (million litres)</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -4957,14 +5031,14 @@
           <t>disclosure</t>
         </is>
       </c>
-      <c r="C63" s="20" t="n">
-        <v>5545.975</v>
+      <c r="C63" s="16" t="n">
+        <v>714</v>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Lease liabilities, FY2025 (AED m)</t>
+          <t>Fuel transactions, first half annualised (million)</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
@@ -4972,82 +5046,320 @@
           <t>disclosure</t>
         </is>
       </c>
-      <c r="C64" s="20" t="n">
-        <v>1446.327</v>
+      <c r="C64" s="23" t="n">
+        <v>201.8</v>
       </c>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Provisions and deferred tax, FY2025 (AED m)</t>
+          <t>Non-fuel conversion rate, first half 2026</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>disclosure</t>
-        </is>
-      </c>
-      <c r="C65" s="20" t="n">
-        <v>460.12</v>
+          <t>disclosed non-fuel transactions over disclosed fuel transactions</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="n">
+        <v>0.2616451932606541</v>
       </c>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Term deposits, FY2025 (AED m)</t>
+          <t>Average non-fuel basket, first half 2026 (AED)</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>disclosure</t>
-        </is>
-      </c>
-      <c r="C66" s="20" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="67" ht="24" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>Finance costs, held at the FY2025 level (AED m)</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>disclosure, held flat</t>
-        </is>
-      </c>
-      <c r="C67" s="20" t="n">
-        <v>402.945</v>
-      </c>
+          <t>disclosed non-fuel revenue over disclosed non-fuel transactions</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="n">
+        <v>35.12958333333334</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>Opening position, from the audited FY2025 balance sheet</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
     </row>
     <row r="68" ht="24" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Interest income, held at the FY2025 level (AED m)</t>
+          <t>Retail fuel volume, FY2025 (million litres)</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>disclosure, held flat</t>
+          <t>disclosure</t>
         </is>
       </c>
       <c r="C68" s="20" t="n">
-        <v>71.274</v>
+        <v>11042</v>
       </c>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
+          <t>Commercial fuel volume, FY2025 (million litres)</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>disclosure</t>
+        </is>
+      </c>
+      <c r="C69" s="20" t="n">
+        <v>4668</v>
+      </c>
+    </row>
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Retail margin per litre, first half 2026 (AED)</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>unit build: segment gross profit less inventory movement, over volume</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="n">
+        <v>0.3597470238095238</v>
+      </c>
+    </row>
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Commercial margin per litre, first half 2026 (AED)</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>unit build: segment gross profit less inventory movement, over volume</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="n">
+        <v>0.4363406408094435</v>
+      </c>
+    </row>
+    <row r="72" ht="24" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Non-fuel retail revenue, FY2025 (AED m)</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>disclosure</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="n">
+        <v>1783.747</v>
+      </c>
+    </row>
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Cash operating costs, FY2025 (AED m)</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>disclosure</t>
+        </is>
+      </c>
+      <c r="C73" s="20" t="n">
+        <v>2547.6</v>
+      </c>
+    </row>
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Other income, FY2025 (AED m)</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>disclosure</t>
+        </is>
+      </c>
+      <c r="C74" s="20" t="n">
+        <v>167.665</v>
+      </c>
+    </row>
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Fixed and right-of-use assets, FY2025 (AED m)</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>disclosure</t>
+        </is>
+      </c>
+      <c r="C75" s="20" t="n">
+        <v>9478.001</v>
+      </c>
+    </row>
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Goodwill, intangibles and other non-current, FY2025 (AED m)</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>disclosure</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="n">
+        <v>671.2729999999999</v>
+      </c>
+    </row>
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Equity attributable to owners, FY2025 (AED m)</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>disclosure</t>
+        </is>
+      </c>
+      <c r="C77" s="20" t="n">
+        <v>3230.423</v>
+      </c>
+    </row>
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Non-controlling interests, FY2025 (AED m)</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>disclosure</t>
+        </is>
+      </c>
+      <c r="C78" s="20" t="n">
+        <v>230.374</v>
+      </c>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Borrowings, FY2025 (AED m)</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>disclosure</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="n">
+        <v>5545.975</v>
+      </c>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Lease liabilities, FY2025 (AED m)</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>disclosure</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="n">
+        <v>1446.327</v>
+      </c>
+    </row>
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Provisions and deferred tax, FY2025 (AED m)</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>disclosure</t>
+        </is>
+      </c>
+      <c r="C81" s="20" t="n">
+        <v>460.12</v>
+      </c>
+    </row>
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Term deposits, FY2025 (AED m)</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>disclosure</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Finance costs, held at the FY2025 level (AED m)</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>disclosure, held flat</t>
+        </is>
+      </c>
+      <c r="C83" s="20" t="n">
+        <v>402.945</v>
+      </c>
+    </row>
+    <row r="84" ht="24" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Interest income, held at the FY2025 level (AED m)</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>disclosure, held flat</t>
+        </is>
+      </c>
+      <c r="C84" s="20" t="n">
+        <v>71.274</v>
+      </c>
+    </row>
+    <row r="85" ht="24" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
           <t>Non-controlling share of profit (AED m)</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>disclosure, held flat</t>
         </is>
       </c>
-      <c r="C69" s="20" t="n">
+      <c r="C85" s="20" t="n">
         <v>57.042</v>
       </c>
     </row>
@@ -5123,11 +5435,11 @@
           <t>ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B4" s="23">
+      <c r="B4" s="24">
         <f>B2+B3</f>
         <v/>
       </c>
-      <c r="C4" s="23">
+      <c r="C4" s="24">
         <f>C2+C3</f>
         <v/>
       </c>
@@ -5169,11 +5481,11 @@
         </is>
       </c>
       <c r="B7" s="22">
-        <f>-Assumptions!$C$64</f>
+        <f>-Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="C7" s="22">
-        <f>-Assumptions!$C$64</f>
+        <f>-Assumptions!$C$80</f>
         <v/>
       </c>
     </row>
@@ -5184,11 +5496,11 @@
         </is>
       </c>
       <c r="B8" s="22">
-        <f>-Assumptions!$C$62</f>
+        <f>-Assumptions!$C$78</f>
         <v/>
       </c>
       <c r="C8" s="22">
-        <f>-Assumptions!$C$62</f>
+        <f>-Assumptions!$C$78</f>
         <v/>
       </c>
     </row>
@@ -5198,11 +5510,11 @@
           <t>EQUITY VALUE</t>
         </is>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="24">
         <f>B4+B6+B7+B8</f>
         <v/>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="24">
         <f>C4+C6+C7+C8</f>
         <v/>
       </c>
@@ -5233,10 +5545,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -5248,12 +5560,12 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>The unit build — volume x price, and volume x margin per litre</t>
+          <t>The unit build — every forecast cell is a formula</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>Anchor</t>
         </is>
       </c>
       <c r="C1" s="6" t="inlineStr">
@@ -5277,586 +5589,1155 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Revenue is volume times realised price. Gross profit is volume times margin per litre. They are different questions: the price is a pass-through of crude and moves revenue and cost together, while the margin per litre is what the business earns.</t>
-        </is>
-      </c>
-      <c r="B2" s="24" t="n"/>
-      <c r="C2" s="24" t="n"/>
-      <c r="D2" s="24" t="n"/>
-      <c r="E2" s="24" t="n"/>
-      <c r="F2" s="24" t="n"/>
-      <c r="G2" s="25" t="n"/>
+          <t>The anchor column is the ANNUALISED DISCLOSED FIRST HALF of 2026, not FY2025: two quarters of the study year are already on the public record. The first forecast column therefore carries the second-half shape on that realised run rate, and growth proper begins in FY2027.</t>
+        </is>
+      </c>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="26" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Retail fuel volume (million litres)</t>
-        </is>
-      </c>
-      <c r="B3" s="20" t="n">
-        <v>11042</v>
-      </c>
-      <c r="C3" s="22">
-        <f>Assumptions!$C$52*(1+Assumptions!C$30)</f>
-        <v/>
-      </c>
-      <c r="D3" s="22">
-        <f>C3*(1+Assumptions!D$30)</f>
-        <v/>
-      </c>
-      <c r="E3" s="22">
-        <f>D3*(1+Assumptions!E$30)</f>
-        <v/>
-      </c>
-      <c r="F3" s="22">
-        <f>E3*(1+Assumptions!F$30)</f>
-        <v/>
-      </c>
-      <c r="G3" s="22">
-        <f>F3*(1+Assumptions!G$30)</f>
+          <t>Service stations</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="n">
+        <v>1045</v>
+      </c>
+      <c r="C3" s="27">
+        <f>Assumptions!$C$59*(1+Assumptions!C$29)</f>
+        <v/>
+      </c>
+      <c r="D3" s="27">
+        <f>C3*(1+Assumptions!D$29)</f>
+        <v/>
+      </c>
+      <c r="E3" s="27">
+        <f>D3*(1+Assumptions!E$29)</f>
+        <v/>
+      </c>
+      <c r="F3" s="27">
+        <f>E3*(1+Assumptions!F$29)</f>
+        <v/>
+      </c>
+      <c r="G3" s="27">
+        <f>F3*(1+Assumptions!G$29)</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Commercial fuel volume (million litres)</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="n">
-        <v>4668</v>
-      </c>
-      <c r="C4" s="22">
-        <f>Assumptions!$C$53*(1+Assumptions!C$31)</f>
-        <v/>
-      </c>
-      <c r="D4" s="22">
-        <f>C4*(1+Assumptions!D$31)</f>
-        <v/>
-      </c>
-      <c r="E4" s="22">
-        <f>D4*(1+Assumptions!E$31)</f>
-        <v/>
-      </c>
-      <c r="F4" s="22">
-        <f>E4*(1+Assumptions!F$31)</f>
-        <v/>
-      </c>
-      <c r="G4" s="22">
-        <f>F4*(1+Assumptions!G$31)</f>
+          <t>Litres sold per station (million)</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="n">
+        <v>10.288995215311</v>
+      </c>
+      <c r="C4" s="28">
+        <f>Assumptions!$C$61*(1+Assumptions!C$30)</f>
+        <v/>
+      </c>
+      <c r="D4" s="28">
+        <f>C4*(1+Assumptions!D$30)</f>
+        <v/>
+      </c>
+      <c r="E4" s="28">
+        <f>D4*(1+Assumptions!E$30)</f>
+        <v/>
+      </c>
+      <c r="F4" s="28">
+        <f>E4*(1+Assumptions!F$30)</f>
+        <v/>
+      </c>
+      <c r="G4" s="28">
+        <f>F4*(1+Assumptions!G$30)</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Total fuel volume (million litres)</t>
+          <t>RETAIL FUEL VOLUME = stations x litres per station</t>
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>15710</v>
+        <v>10752</v>
       </c>
       <c r="C5" s="17">
-        <f>C3+C4</f>
+        <f>C3*C4</f>
         <v/>
       </c>
       <c r="D5" s="17">
-        <f>D3+D4</f>
+        <f>D3*D4</f>
         <v/>
       </c>
       <c r="E5" s="17">
-        <f>E3+E4</f>
+        <f>E3*E4</f>
         <v/>
       </c>
       <c r="F5" s="17">
-        <f>F3+F4</f>
+        <f>F3*F4</f>
         <v/>
       </c>
       <c r="G5" s="17">
-        <f>G3+G4</f>
+        <f>G3*G4</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Realised retail price per litre (AED)</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n">
-        <v>2.064570458250317</v>
-      </c>
-      <c r="C6" s="26">
-        <f>Assumptions!C$32</f>
-        <v/>
-      </c>
-      <c r="D6" s="26">
-        <f>Assumptions!D$32</f>
-        <v/>
-      </c>
-      <c r="E6" s="26">
-        <f>Assumptions!E$32</f>
-        <v/>
-      </c>
-      <c r="F6" s="26">
-        <f>Assumptions!F$32</f>
-        <v/>
-      </c>
-      <c r="G6" s="26">
-        <f>Assumptions!G$32</f>
+          <t>Corporate fuel volume (million litres)</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="n">
+        <v>4030</v>
+      </c>
+      <c r="C6" s="22">
+        <f>Assumptions!$C$62*(1+Assumptions!C$31)</f>
+        <v/>
+      </c>
+      <c r="D6" s="22">
+        <f>C6*(1+Assumptions!D$31)</f>
+        <v/>
+      </c>
+      <c r="E6" s="22">
+        <f>D6*(1+Assumptions!E$31)</f>
+        <v/>
+      </c>
+      <c r="F6" s="22">
+        <f>E6*(1+Assumptions!F$31)</f>
+        <v/>
+      </c>
+      <c r="G6" s="22">
+        <f>F6*(1+Assumptions!G$31)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Realised commercial price per litre (AED)</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n">
-        <v>2.424139460154242</v>
-      </c>
-      <c r="C7" s="26">
-        <f>Assumptions!C$33</f>
-        <v/>
-      </c>
-      <c r="D7" s="26">
-        <f>Assumptions!D$33</f>
-        <v/>
-      </c>
-      <c r="E7" s="26">
-        <f>Assumptions!E$33</f>
-        <v/>
-      </c>
-      <c r="F7" s="26">
-        <f>Assumptions!F$33</f>
-        <v/>
-      </c>
-      <c r="G7" s="26">
-        <f>Assumptions!G$33</f>
+          <t>Aviation fuel volume (million litres)</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n">
+        <v>714</v>
+      </c>
+      <c r="C7" s="22">
+        <f>Assumptions!$C$63*(1+Assumptions!C$32)</f>
+        <v/>
+      </c>
+      <c r="D7" s="22">
+        <f>C7*(1+Assumptions!D$32)</f>
+        <v/>
+      </c>
+      <c r="E7" s="22">
+        <f>D7*(1+Assumptions!E$32)</f>
+        <v/>
+      </c>
+      <c r="F7" s="22">
+        <f>E7*(1+Assumptions!F$32)</f>
+        <v/>
+      </c>
+      <c r="G7" s="22">
+        <f>F7*(1+Assumptions!G$32)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Retail fuel revenue = volume x price</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Commercial fuel volume = corporate + aviation</t>
         </is>
       </c>
       <c r="B8" s="20" t="n">
-        <v>22796.987</v>
-      </c>
-      <c r="C8" s="22">
-        <f>C3*C6</f>
-        <v/>
-      </c>
-      <c r="D8" s="22">
-        <f>D3*D6</f>
-        <v/>
-      </c>
-      <c r="E8" s="22">
-        <f>E3*E6</f>
-        <v/>
-      </c>
-      <c r="F8" s="22">
-        <f>F3*F6</f>
-        <v/>
-      </c>
-      <c r="G8" s="22">
-        <f>G3*G6</f>
+        <v>4744</v>
+      </c>
+      <c r="C8" s="17">
+        <f>C6+C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="17">
+        <f>D6+D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="17">
+        <f>E6+E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="17">
+        <f>F6+F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="17">
+        <f>G6+G7</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Commercial revenue = volume x price</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>TOTAL FUEL VOLUME</t>
         </is>
       </c>
       <c r="B9" s="20" t="n">
-        <v>11315.883</v>
-      </c>
-      <c r="C9" s="22">
-        <f>C4*C7</f>
-        <v/>
-      </c>
-      <c r="D9" s="22">
-        <f>D4*D7</f>
-        <v/>
-      </c>
-      <c r="E9" s="22">
-        <f>E4*E7</f>
-        <v/>
-      </c>
-      <c r="F9" s="22">
-        <f>F4*F7</f>
-        <v/>
-      </c>
-      <c r="G9" s="22">
-        <f>G4*G7</f>
+        <v>15496</v>
+      </c>
+      <c r="C9" s="24">
+        <f>C5+C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="24">
+        <f>D5+D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="24">
+        <f>E5+E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="24">
+        <f>F5+F8</f>
+        <v/>
+      </c>
+      <c r="G9" s="24">
+        <f>G5+G8</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Non-fuel retail revenue</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="n">
-        <v>1783.747</v>
-      </c>
-      <c r="C10" s="22">
-        <f>Assumptions!$C$56*(1+Assumptions!C$36)</f>
-        <v/>
-      </c>
-      <c r="D10" s="22">
-        <f>C10*(1+Assumptions!D$36)</f>
-        <v/>
-      </c>
-      <c r="E10" s="22">
-        <f>D10*(1+Assumptions!E$36)</f>
-        <v/>
-      </c>
-      <c r="F10" s="22">
-        <f>E10*(1+Assumptions!F$36)</f>
-        <v/>
-      </c>
-      <c r="G10" s="22">
-        <f>F10*(1+Assumptions!G$36)</f>
+          <t>Realised retail price per litre (AED)</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>2.449770275297619</v>
+      </c>
+      <c r="C10" s="28">
+        <f>Assumptions!C$33</f>
+        <v/>
+      </c>
+      <c r="D10" s="28">
+        <f>Assumptions!D$33</f>
+        <v/>
+      </c>
+      <c r="E10" s="28">
+        <f>Assumptions!E$33</f>
+        <v/>
+      </c>
+      <c r="F10" s="28">
+        <f>Assumptions!F$33</f>
+        <v/>
+      </c>
+      <c r="G10" s="28">
+        <f>Assumptions!G$33</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>TOTAL REVENUE</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="n">
-        <v>35896.617</v>
-      </c>
-      <c r="C11" s="23">
-        <f>C8+C9+C10</f>
-        <v/>
-      </c>
-      <c r="D11" s="23">
-        <f>D8+D9+D10</f>
-        <v/>
-      </c>
-      <c r="E11" s="23">
-        <f>E8+E9+E10</f>
-        <v/>
-      </c>
-      <c r="F11" s="23">
-        <f>F8+F9+F10</f>
-        <v/>
-      </c>
-      <c r="G11" s="23">
-        <f>G8+G9+G10</f>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Realised corporate price per litre (AED)</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>3.117804466501241</v>
+      </c>
+      <c r="C11" s="28">
+        <f>Assumptions!C$34</f>
+        <v/>
+      </c>
+      <c r="D11" s="28">
+        <f>Assumptions!D$34</f>
+        <v/>
+      </c>
+      <c r="E11" s="28">
+        <f>Assumptions!E$34</f>
+        <v/>
+      </c>
+      <c r="F11" s="28">
+        <f>Assumptions!F$34</f>
+        <v/>
+      </c>
+      <c r="G11" s="28">
+        <f>Assumptions!G$34</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Retail margin per litre (AED)</t>
+          <t>Realised aviation price per litre (AED)</t>
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>0.3542836442673429</v>
-      </c>
-      <c r="C12" s="26">
-        <f>Assumptions!$C$54*(1+Assumptions!C$34)</f>
-        <v/>
-      </c>
-      <c r="D12" s="26">
-        <f>C12*(1+Assumptions!D$34)</f>
-        <v/>
-      </c>
-      <c r="E12" s="26">
-        <f>D12*(1+Assumptions!E$34)</f>
-        <v/>
-      </c>
-      <c r="F12" s="26">
-        <f>E12*(1+Assumptions!F$34)</f>
-        <v/>
-      </c>
-      <c r="G12" s="26">
-        <f>F12*(1+Assumptions!G$34)</f>
+        <v>4.636532212885154</v>
+      </c>
+      <c r="C12" s="28">
+        <f>Assumptions!C$35</f>
+        <v/>
+      </c>
+      <c r="D12" s="28">
+        <f>Assumptions!D$35</f>
+        <v/>
+      </c>
+      <c r="E12" s="28">
+        <f>Assumptions!E$35</f>
+        <v/>
+      </c>
+      <c r="F12" s="28">
+        <f>Assumptions!F$35</f>
+        <v/>
+      </c>
+      <c r="G12" s="28">
+        <f>Assumptions!G$35</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Commercial margin per litre (AED)</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>0.367395029991431</v>
-      </c>
-      <c r="C13" s="26">
-        <f>Assumptions!$C$55*(1+Assumptions!C$35)</f>
-        <v/>
-      </c>
-      <c r="D13" s="26">
-        <f>C13*(1+Assumptions!D$35)</f>
-        <v/>
-      </c>
-      <c r="E13" s="26">
-        <f>D13*(1+Assumptions!E$35)</f>
-        <v/>
-      </c>
-      <c r="F13" s="26">
-        <f>E13*(1+Assumptions!F$35)</f>
-        <v/>
-      </c>
-      <c r="G13" s="26">
-        <f>F13*(1+Assumptions!G$35)</f>
+          <t>Retail fuel revenue = volume x price</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="n">
+        <v>26339.93</v>
+      </c>
+      <c r="C13" s="22">
+        <f>C5*C10</f>
+        <v/>
+      </c>
+      <c r="D13" s="22">
+        <f>D5*D10</f>
+        <v/>
+      </c>
+      <c r="E13" s="22">
+        <f>E5*E10</f>
+        <v/>
+      </c>
+      <c r="F13" s="22">
+        <f>F5*F10</f>
+        <v/>
+      </c>
+      <c r="G13" s="22">
+        <f>G5*G10</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Retail fuel gross profit = volume x margin</t>
+          <t>Corporate revenue = volume x price</t>
         </is>
       </c>
       <c r="B14" s="20" t="n">
-        <v>3912</v>
+        <v>12564.752</v>
       </c>
       <c r="C14" s="22">
-        <f>C3*C12</f>
+        <f>C6*C11</f>
         <v/>
       </c>
       <c r="D14" s="22">
-        <f>D3*D12</f>
+        <f>D6*D11</f>
         <v/>
       </c>
       <c r="E14" s="22">
-        <f>E3*E12</f>
+        <f>E6*E11</f>
         <v/>
       </c>
       <c r="F14" s="22">
-        <f>F3*F12</f>
+        <f>F6*F11</f>
         <v/>
       </c>
       <c r="G14" s="22">
-        <f>G3*G12</f>
+        <f>G6*G11</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Commercial gross profit = volume x margin</t>
+          <t>Aviation revenue = volume x price</t>
         </is>
       </c>
       <c r="B15" s="20" t="n">
-        <v>1715</v>
+        <v>3310.484</v>
       </c>
       <c r="C15" s="22">
-        <f>C4*C13</f>
+        <f>C7*C12</f>
         <v/>
       </c>
       <c r="D15" s="22">
-        <f>D4*D13</f>
+        <f>D7*D12</f>
         <v/>
       </c>
       <c r="E15" s="22">
-        <f>E4*E13</f>
+        <f>E7*E12</f>
         <v/>
       </c>
       <c r="F15" s="22">
-        <f>F4*F13</f>
+        <f>F7*F12</f>
         <v/>
       </c>
       <c r="G15" s="22">
-        <f>G4*G13</f>
+        <f>G7*G12</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Non-fuel retail gross profit = revenue x margin</t>
+          <t>Commercial revenue = corporate + aviation</t>
         </is>
       </c>
       <c r="B16" s="20" t="n">
-        <v>984</v>
+        <v>15875.236</v>
       </c>
       <c r="C16" s="22">
-        <f>C10*Assumptions!C$37</f>
+        <f>C14+C15</f>
         <v/>
       </c>
       <c r="D16" s="22">
-        <f>D10*Assumptions!D$37</f>
+        <f>D14+D15</f>
         <v/>
       </c>
       <c r="E16" s="22">
-        <f>E10*Assumptions!E$37</f>
+        <f>E14+E15</f>
         <v/>
       </c>
       <c r="F16" s="22">
-        <f>F10*Assumptions!F$37</f>
+        <f>F14+F15</f>
         <v/>
       </c>
       <c r="G16" s="22">
-        <f>G10*Assumptions!G$37</f>
+        <f>G14+G15</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>STRUCTURAL GROSS PROFIT</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="n">
-        <v>6610.79</v>
-      </c>
-      <c r="C17" s="23">
-        <f>C14+C15+C16</f>
-        <v/>
-      </c>
-      <c r="D17" s="23">
-        <f>D14+D15+D16</f>
-        <v/>
-      </c>
-      <c r="E17" s="23">
-        <f>E14+E15+E16</f>
-        <v/>
-      </c>
-      <c r="F17" s="23">
-        <f>F14+F15+F16</f>
-        <v/>
-      </c>
-      <c r="G17" s="23">
-        <f>G14+G15+G16</f>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Blended commercial price per litre — AN OUTPUT of the mix</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="n">
+        <v>3.346381956155144</v>
+      </c>
+      <c r="C17" s="28">
+        <f>C16/C8</f>
+        <v/>
+      </c>
+      <c r="D17" s="28">
+        <f>D16/D8</f>
+        <v/>
+      </c>
+      <c r="E17" s="28">
+        <f>E16/E8</f>
+        <v/>
+      </c>
+      <c r="F17" s="28">
+        <f>F16/F8</f>
+        <v/>
+      </c>
+      <c r="G17" s="28">
+        <f>G16/G8</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Inventory movement — Frame A, normalised</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="n">
-        <v>335</v>
-      </c>
-      <c r="C18" s="22">
-        <f>Assumptions!C$38</f>
-        <v/>
-      </c>
-      <c r="D18" s="22">
-        <f>Assumptions!D$38</f>
-        <v/>
-      </c>
-      <c r="E18" s="22">
-        <f>Assumptions!E$38</f>
-        <v/>
-      </c>
-      <c r="F18" s="22">
-        <f>Assumptions!F$38</f>
-        <v/>
-      </c>
-      <c r="G18" s="22">
-        <f>Assumptions!G$38</f>
+          <t>Fuel transactions (million)</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="n">
+        <v>201.8</v>
+      </c>
+      <c r="C18" s="27">
+        <f>Assumptions!$C$64*(1+Assumptions!C$38)</f>
+        <v/>
+      </c>
+      <c r="D18" s="27">
+        <f>C18*(1+Assumptions!D$38)</f>
+        <v/>
+      </c>
+      <c r="E18" s="27">
+        <f>D18*(1+Assumptions!E$38)</f>
+        <v/>
+      </c>
+      <c r="F18" s="27">
+        <f>E18*(1+Assumptions!F$38)</f>
+        <v/>
+      </c>
+      <c r="G18" s="27">
+        <f>F18*(1+Assumptions!G$38)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>Non-fuel conversion rate</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="n">
+        <v>0.2616451932606541</v>
+      </c>
+      <c r="C19" s="29">
+        <f>Assumptions!$C$65*(1+Assumptions!C$39)</f>
+        <v/>
+      </c>
+      <c r="D19" s="29">
+        <f>C19*(1+Assumptions!D$39)</f>
+        <v/>
+      </c>
+      <c r="E19" s="29">
+        <f>D19*(1+Assumptions!E$39)</f>
+        <v/>
+      </c>
+      <c r="F19" s="29">
+        <f>E19*(1+Assumptions!F$39)</f>
+        <v/>
+      </c>
+      <c r="G19" s="29">
+        <f>F19*(1+Assumptions!G$39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Non-fuel transactions = fuel transactions x conversion</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="C20" s="27">
+        <f>C18*C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="27">
+        <f>D18*D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="27">
+        <f>E18*E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="27">
+        <f>F18*F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="27">
+        <f>G18*G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Average non-fuel basket (AED)</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="n">
+        <v>35.12958333333334</v>
+      </c>
+      <c r="C21" s="7">
+        <f>Assumptions!$C$66*(1+Assumptions!C$40)</f>
+        <v/>
+      </c>
+      <c r="D21" s="7">
+        <f>C21*(1+Assumptions!D$40)</f>
+        <v/>
+      </c>
+      <c r="E21" s="7">
+        <f>D21*(1+Assumptions!E$40)</f>
+        <v/>
+      </c>
+      <c r="F21" s="7">
+        <f>E21*(1+Assumptions!F$40)</f>
+        <v/>
+      </c>
+      <c r="G21" s="7">
+        <f>F21*(1+Assumptions!G$40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Non-fuel revenue = transactions x basket</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n">
+        <v>1854.842</v>
+      </c>
+      <c r="C22" s="22">
+        <f>C20*C21</f>
+        <v/>
+      </c>
+      <c r="D22" s="22">
+        <f>D20*D21</f>
+        <v/>
+      </c>
+      <c r="E22" s="22">
+        <f>E20*E21</f>
+        <v/>
+      </c>
+      <c r="F22" s="22">
+        <f>F20*F21</f>
+        <v/>
+      </c>
+      <c r="G22" s="22">
+        <f>G20*G21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n">
+        <v>44070.008</v>
+      </c>
+      <c r="C23" s="24">
+        <f>C13+C16+C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="24">
+        <f>D13+D16+D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="24">
+        <f>E13+E16+E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="24">
+        <f>F13+F16+F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="24">
+        <f>G13+G16+G22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Retail margin per litre (AED)</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>0.3597470238095238</v>
+      </c>
+      <c r="C24" s="28">
+        <f>Assumptions!$C$70*(1+Assumptions!C$36)</f>
+        <v/>
+      </c>
+      <c r="D24" s="28">
+        <f>C24*(1+Assumptions!D$36)</f>
+        <v/>
+      </c>
+      <c r="E24" s="28">
+        <f>D24*(1+Assumptions!E$36)</f>
+        <v/>
+      </c>
+      <c r="F24" s="28">
+        <f>E24*(1+Assumptions!F$36)</f>
+        <v/>
+      </c>
+      <c r="G24" s="28">
+        <f>F24*(1+Assumptions!G$36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Commercial margin per litre (AED) — blended, split NOT disclosed</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n">
+        <v>0.4363406408094435</v>
+      </c>
+      <c r="C25" s="28">
+        <f>Assumptions!$C$71*(1+Assumptions!C$37)</f>
+        <v/>
+      </c>
+      <c r="D25" s="28">
+        <f>C25*(1+Assumptions!D$37)</f>
+        <v/>
+      </c>
+      <c r="E25" s="28">
+        <f>D25*(1+Assumptions!E$37)</f>
+        <v/>
+      </c>
+      <c r="F25" s="28">
+        <f>E25*(1+Assumptions!F$37)</f>
+        <v/>
+      </c>
+      <c r="G25" s="28">
+        <f>F25*(1+Assumptions!G$37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Retail fuel gross profit = volume x margin</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="n">
+        <v>3868</v>
+      </c>
+      <c r="C26" s="22">
+        <f>C5*C24</f>
+        <v/>
+      </c>
+      <c r="D26" s="22">
+        <f>D5*D24</f>
+        <v/>
+      </c>
+      <c r="E26" s="22">
+        <f>E5*E24</f>
+        <v/>
+      </c>
+      <c r="F26" s="22">
+        <f>F5*F24</f>
+        <v/>
+      </c>
+      <c r="G26" s="22">
+        <f>G5*G24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Commercial gross profit = volume x margin</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n">
+        <v>2070</v>
+      </c>
+      <c r="C27" s="22">
+        <f>C8*C25</f>
+        <v/>
+      </c>
+      <c r="D27" s="22">
+        <f>D8*D25</f>
+        <v/>
+      </c>
+      <c r="E27" s="22">
+        <f>E8*E25</f>
+        <v/>
+      </c>
+      <c r="F27" s="22">
+        <f>F8*F25</f>
+        <v/>
+      </c>
+      <c r="G27" s="22">
+        <f>G8*G25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Non-fuel gross profit = revenue x margin</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n">
+        <v>1044</v>
+      </c>
+      <c r="C28" s="22">
+        <f>C22*Assumptions!C$41</f>
+        <v/>
+      </c>
+      <c r="D28" s="22">
+        <f>D22*Assumptions!D$41</f>
+        <v/>
+      </c>
+      <c r="E28" s="22">
+        <f>E22*Assumptions!E$41</f>
+        <v/>
+      </c>
+      <c r="F28" s="22">
+        <f>F22*Assumptions!F$41</f>
+        <v/>
+      </c>
+      <c r="G28" s="22">
+        <f>G22*Assumptions!G$41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>STRUCTURAL GROSS PROFIT</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n">
+        <v>6980.204</v>
+      </c>
+      <c r="C29" s="24">
+        <f>C26+C27+C28</f>
+        <v/>
+      </c>
+      <c r="D29" s="24">
+        <f>D26+D27+D28</f>
+        <v/>
+      </c>
+      <c r="E29" s="24">
+        <f>E26+E27+E28</f>
+        <v/>
+      </c>
+      <c r="F29" s="24">
+        <f>F26+F27+F28</f>
+        <v/>
+      </c>
+      <c r="G29" s="24">
+        <f>G26+G27+G28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Inventory movement — Frame A, normalised</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="n">
+        <v>762</v>
+      </c>
+      <c r="C30" s="22">
+        <f>Assumptions!C$42</f>
+        <v/>
+      </c>
+      <c r="D30" s="22">
+        <f>Assumptions!D$42</f>
+        <v/>
+      </c>
+      <c r="E30" s="22">
+        <f>Assumptions!E$42</f>
+        <v/>
+      </c>
+      <c r="F30" s="22">
+        <f>Assumptions!F$42</f>
+        <v/>
+      </c>
+      <c r="G30" s="22">
+        <f>Assumptions!G$42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
           <t>Inventory movement — Frame B, through-cycle</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n">
-        <v>335</v>
-      </c>
-      <c r="C19" s="22">
-        <f>Assumptions!C$39</f>
-        <v/>
-      </c>
-      <c r="D19" s="22">
-        <f>Assumptions!D$39</f>
-        <v/>
-      </c>
-      <c r="E19" s="22">
-        <f>Assumptions!E$39</f>
-        <v/>
-      </c>
-      <c r="F19" s="22">
-        <f>Assumptions!F$39</f>
-        <v/>
-      </c>
-      <c r="G19" s="22">
-        <f>Assumptions!G$39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="B31" s="20" t="n">
+        <v>762</v>
+      </c>
+      <c r="C31" s="22">
+        <f>Assumptions!C$43</f>
+        <v/>
+      </c>
+      <c r="D31" s="22">
+        <f>Assumptions!D$43</f>
+        <v/>
+      </c>
+      <c r="E31" s="22">
+        <f>Assumptions!E$43</f>
+        <v/>
+      </c>
+      <c r="F31" s="22">
+        <f>Assumptions!F$43</f>
+        <v/>
+      </c>
+      <c r="G31" s="22">
+        <f>Assumptions!G$43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>GROSS PROFIT — Frame A</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n">
-        <v>6945.79</v>
-      </c>
-      <c r="C20" s="23">
-        <f>C17+C18</f>
-        <v/>
-      </c>
-      <c r="D20" s="23">
-        <f>D17+D18</f>
-        <v/>
-      </c>
-      <c r="E20" s="23">
-        <f>E17+E18</f>
-        <v/>
-      </c>
-      <c r="F20" s="23">
-        <f>F17+F18</f>
-        <v/>
-      </c>
-      <c r="G20" s="23">
-        <f>G17+G18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="B32" s="20" t="n">
+        <v>8504.204</v>
+      </c>
+      <c r="C32" s="24">
+        <f>C29+C30</f>
+        <v/>
+      </c>
+      <c r="D32" s="24">
+        <f>D29+D30</f>
+        <v/>
+      </c>
+      <c r="E32" s="24">
+        <f>E29+E30</f>
+        <v/>
+      </c>
+      <c r="F32" s="24">
+        <f>F29+F30</f>
+        <v/>
+      </c>
+      <c r="G32" s="24">
+        <f>G29+G30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>GROSS PROFIT — Frame B</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n">
-        <v>6945.79</v>
-      </c>
-      <c r="C21" s="23">
-        <f>C17+C19</f>
-        <v/>
-      </c>
-      <c r="D21" s="23">
-        <f>D17+D19</f>
-        <v/>
-      </c>
-      <c r="E21" s="23">
-        <f>E17+E19</f>
-        <v/>
-      </c>
-      <c r="F21" s="23">
-        <f>F17+F19</f>
-        <v/>
-      </c>
-      <c r="G21" s="23">
-        <f>G17+G19</f>
+      <c r="B33" s="20" t="n">
+        <v>8504.204</v>
+      </c>
+      <c r="C33" s="24">
+        <f>C29+C31</f>
+        <v/>
+      </c>
+      <c r="D33" s="24">
+        <f>D29+D31</f>
+        <v/>
+      </c>
+      <c r="E33" s="24">
+        <f>E29+E31</f>
+        <v/>
+      </c>
+      <c r="F33" s="24">
+        <f>F29+F31</f>
+        <v/>
+      </c>
+      <c r="G33" s="24">
+        <f>G29+G31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>The asset base, rolled — depreciation and capital spending are outputs of it, not pasted arrays</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Opening fixed and right-of-use base</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr"/>
+      <c r="C35" s="22">
+        <f>Assumptions!$C$75</f>
+        <v/>
+      </c>
+      <c r="D35" s="22">
+        <f>C41</f>
+        <v/>
+      </c>
+      <c r="E35" s="22">
+        <f>D41</f>
+        <v/>
+      </c>
+      <c r="F35" s="22">
+        <f>E41</f>
+        <v/>
+      </c>
+      <c r="G35" s="22">
+        <f>F41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Depreciation = opening base x the measured rate</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="22">
+        <f>C35*Assumptions!$C$50</f>
+        <v/>
+      </c>
+      <c r="D36" s="22">
+        <f>D35*Assumptions!$C$50</f>
+        <v/>
+      </c>
+      <c r="E36" s="22">
+        <f>E35*Assumptions!$C$50</f>
+        <v/>
+      </c>
+      <c r="F36" s="22">
+        <f>F35*Assumptions!$C$50</f>
+        <v/>
+      </c>
+      <c r="G36" s="22">
+        <f>G35*Assumptions!$C$50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance capital spending = opening base x the maintenance rate</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr"/>
+      <c r="C37" s="22">
+        <f>C35*Assumptions!$C$51</f>
+        <v/>
+      </c>
+      <c r="D37" s="22">
+        <f>D35*Assumptions!$C$51</f>
+        <v/>
+      </c>
+      <c r="E37" s="22">
+        <f>E35*Assumptions!$C$51</f>
+        <v/>
+      </c>
+      <c r="F37" s="22">
+        <f>F35*Assumptions!$C$51</f>
+        <v/>
+      </c>
+      <c r="G37" s="22">
+        <f>G35*Assumptions!$C$51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Stations added</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr"/>
+      <c r="C38" s="27">
+        <f>C3-Assumptions!$C$60</f>
+        <v/>
+      </c>
+      <c r="D38" s="27">
+        <f>D3-C3</f>
+        <v/>
+      </c>
+      <c r="E38" s="27">
+        <f>E3-D3</f>
+        <v/>
+      </c>
+      <c r="F38" s="27">
+        <f>F3-E3</f>
+        <v/>
+      </c>
+      <c r="G38" s="27">
+        <f>G3-F3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Growth capital spending = stations added x cost per station</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr"/>
+      <c r="C39" s="22">
+        <f>C38*Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="D39" s="22">
+        <f>D38*Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="E39" s="22">
+        <f>E38*Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="F39" s="22">
+        <f>F38*Assumptions!$C$52</f>
+        <v/>
+      </c>
+      <c r="G39" s="22">
+        <f>G38*Assumptions!$C$52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>TOTAL CAPITAL SPENDING = maintenance + growth</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr"/>
+      <c r="C40" s="24">
+        <f>C37+C39</f>
+        <v/>
+      </c>
+      <c r="D40" s="24">
+        <f>D37+D39</f>
+        <v/>
+      </c>
+      <c r="E40" s="24">
+        <f>E37+E39</f>
+        <v/>
+      </c>
+      <c r="F40" s="24">
+        <f>F37+F39</f>
+        <v/>
+      </c>
+      <c r="G40" s="24">
+        <f>G37+G39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Closing base = opening + capital spending less depreciation</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr"/>
+      <c r="C41" s="22">
+        <f>C35+C40-C36</f>
+        <v/>
+      </c>
+      <c r="D41" s="22">
+        <f>D35+D40-D36</f>
+        <v/>
+      </c>
+      <c r="E41" s="22">
+        <f>E35+E40-E36</f>
+        <v/>
+      </c>
+      <c r="F41" s="22">
+        <f>F35+F40-F36</f>
+        <v/>
+      </c>
+      <c r="G41" s="22">
+        <f>G35+G40-G36</f>
         <v/>
       </c>
     </row>
@@ -5874,7 +6755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5911,9 +6792,9 @@
           <t>Triangulation: the reference multiple is the AVERAGE of three independently-derived readings, taken on the sheet rather than asserted.</t>
         </is>
       </c>
-      <c r="B2" s="24" t="n"/>
-      <c r="C2" s="24" t="n"/>
-      <c r="D2" s="25" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="26" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -5921,7 +6802,7 @@
           <t>Own trailing multiple today</t>
         </is>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="30">
         <f>Assumptions!$C$3/'Income Statement'!D19</f>
         <v/>
       </c>
@@ -5937,7 +6818,7 @@
           <t>Own three-year average multiple</t>
         </is>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="30">
         <f>(Assumptions!$C$3/'Income Statement'!B19+Assumptions!$C$3/'Income Statement'!C19+Assumptions!$C$3/'Income Statement'!D19)/3</f>
         <v/>
       </c>
@@ -5950,115 +6831,119 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Multiple the company’s own economics justify</t>
-        </is>
-      </c>
-      <c r="B5" s="27">
-        <f>Assumptions!$C$50*(1+Assumptions!$C$27)/(Assumptions!$C$12-Assumptions!$C$27)</f>
+          <t>Retention the growth rate requires = growth / return on equity</t>
+        </is>
+      </c>
+      <c r="B5" s="31">
+        <f>Assumptions!$C$26/0.8077013806</f>
         <v/>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>payout x (1 + growth) / (cost of equity less growth)</t>
+          <t>the sustainable-growth identity g = retention x ROE</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>REFERENCE MULTIPLE — the average of the three</t>
-        </is>
-      </c>
-      <c r="B6" s="28">
-        <f>(B3+B4+B5)/3</f>
-        <v/>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>triangulated on the sheet, not a peer median</t>
-        </is>
-      </c>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Payout consistent with that growth = 1 less the retention</t>
+        </is>
+      </c>
+      <c r="B6" s="29">
+        <f>1-B5</f>
+        <v/>
+      </c>
+      <c r="D6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>RELATIVE MULTIPLES READING (AED a share)</t>
-        </is>
-      </c>
-      <c r="B7" s="11">
-        <f>B6*'Income Statement'!E19</f>
+          <t>REFERENCE MULTIPLE — what the company’s own economics justify</t>
+        </is>
+      </c>
+      <c r="B7" s="32">
+        <f>B6*(1+Assumptions!$C$26)/(Assumptions!$C$12-Assumptions!$C$26)</f>
         <v/>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>reference multiple on the first forecast year</t>
+          <t>payout x (1 + growth) / (cost of equity less growth), on the payout the growth rate itself implies — NOT the realised payout and NOT the policy floor, either of which breaks the identity</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>First forecast year earnings per share — Frame B (AED)</t>
-        </is>
-      </c>
-      <c r="B8" s="26">
-        <f>(DCF!B18+Assumptions!$C$68-Assumptions!$C$67)*(1-Assumptions!$C$16)/Assumptions!$C$4-Assumptions!$C$69/Assumptions!$C$4</f>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Reference multiple carried into the lens</t>
+        </is>
+      </c>
+      <c r="B8" s="32">
+        <f>B7</f>
         <v/>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>the same construction as the income statement, on Frame B earnings</t>
+          <t>the fundamentals leg ALONE. The two traded multiples above are published as context and are deliberately NOT averaged in: both are the traded price divided by earnings, so averaging them would anchor the lens to the price it is being compared against</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>RELATIVE MULTIPLES READING — Frame B (AED a share)</t>
+          <t>RELATIVE MULTIPLES READING (AED a share)</t>
         </is>
       </c>
       <c r="B9" s="11">
-        <f>B6*B8</f>
+        <f>B8*'Income Statement'!E19</f>
         <v/>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>the same reference multiple on Frame B earnings</t>
+          <t>reference multiple on the first forecast year</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Normalised EBITDA — structural gross profit only, no inventory movement</t>
-        </is>
-      </c>
-      <c r="B10" s="22">
-        <f>Segments!C17+'Income Statement'!E5+'Income Statement'!E6+'Income Statement'!E7</f>
-        <v/>
-      </c>
-      <c r="D10" s="8" t="inlineStr"/>
+          <t>First forecast year earnings per share — Frame B (AED)</t>
+        </is>
+      </c>
+      <c r="B10" s="28">
+        <f>(DCF!B18+Assumptions!$C$84-Assumptions!$C$83)*(1-Assumptions!$C$16)/Assumptions!$C$4-Assumptions!$C$85/Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>the same construction as the income statement, on Frame B earnings</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Normalised EBIT</t>
-        </is>
-      </c>
-      <c r="B11" s="22">
-        <f>B10-Assumptions!C$44</f>
-        <v/>
-      </c>
-      <c r="D11" s="8" t="inlineStr"/>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>RELATIVE MULTIPLES READING — Frame B (AED a share)</t>
+        </is>
+      </c>
+      <c r="B11" s="11">
+        <f>B8*B10</f>
+        <v/>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>the same reference multiple on Frame B earnings</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Normalised NOPAT</t>
+          <t>Normalised EBITDA — structural gross profit only, no inventory movement</t>
         </is>
       </c>
       <c r="B12" s="22">
-        <f>B11*(1-Assumptions!$C$16)</f>
+        <f>Segments!C29+'Income Statement'!E5+'Income Statement'!E6+'Income Statement'!E7</f>
         <v/>
       </c>
       <c r="D12" s="8" t="inlineStr"/>
@@ -6066,11 +6951,11 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Normalised enterprise value = NOPAT / (cost of capital less growth)</t>
+          <t>Normalised EBIT</t>
         </is>
       </c>
       <c r="B13" s="22">
-        <f>B12/(Assumptions!$C$21-Assumptions!$C$27)</f>
+        <f>B12-Assumptions!C$48</f>
         <v/>
       </c>
       <c r="D13" s="8" t="inlineStr"/>
@@ -6078,23 +6963,23 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Normalised equity value</t>
+          <t>Normalised NOPAT</t>
         </is>
       </c>
       <c r="B14" s="22">
-        <f>B13-Assumptions!$C$18-Assumptions!$C$64-Assumptions!$C$62</f>
+        <f>B13*(1-Assumptions!$C$16)</f>
         <v/>
       </c>
       <c r="D14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>NORMALISED EARNINGS POWER READING (AED a share)</t>
-        </is>
-      </c>
-      <c r="B15" s="11">
-        <f>B14/Assumptions!$C$4</f>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Reinvestment this perpetuity must fund = growth / return on capital</t>
+        </is>
+      </c>
+      <c r="B15" s="29">
+        <f>Assumptions!$C$26/Assumptions!$C$27</f>
         <v/>
       </c>
       <c r="D15" s="8" t="inlineStr"/>
@@ -6102,64 +6987,104 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Book value per share (AED)</t>
-        </is>
-      </c>
-      <c r="B16" s="26">
-        <f>Assumptions!$C$61/Assumptions!$C$4</f>
-        <v/>
-      </c>
-      <c r="D16" s="8" t="inlineStr"/>
+          <t>Normalised enterprise value = NOPAT x (1 less reinvestment) / (cost of capital less growth)</t>
+        </is>
+      </c>
+      <c r="B16" s="22">
+        <f>B14*(1-B15)/(Assumptions!$C$21-Assumptions!$C$26)</f>
+        <v/>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>the identity g = ROIC x reinvestment governs EVERY perpetuity, not only the cash-flow model terminal block. This lens previously credited growth for free</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>Normalised equity value</t>
+        </is>
+      </c>
+      <c r="B17" s="22">
+        <f>B16-Assumptions!$C$18-Assumptions!$C$80-Assumptions!$C$78</f>
+        <v/>
+      </c>
+      <c r="D17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>NORMALISED EARNINGS POWER READING (AED a share)</t>
+        </is>
+      </c>
+      <c r="B18" s="11">
+        <f>B17/Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="D18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Book value per share (AED)</t>
+        </is>
+      </c>
+      <c r="B19" s="28">
+        <f>Assumptions!$C$77/Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="D19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>Sustainable return on equity — the three-year mean</t>
         </is>
       </c>
-      <c r="B17" s="29">
+      <c r="B20" s="29">
         <f>('Income Statement'!B18/3472.066+'Income Statement'!C18/2991.839+'Income Statement'!D18/3230.423)/3</f>
         <v/>
       </c>
-      <c r="D17" s="8" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Justified multiple of book = (return less growth) / (cost of equity less growth)</t>
         </is>
       </c>
-      <c r="B18" s="27">
-        <f>(B17-Assumptions!$C$27)/(Assumptions!$C$12-Assumptions!$C$27)</f>
-        <v/>
-      </c>
-      <c r="D18" s="8" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="B21" s="30">
+        <f>(B20-Assumptions!$C$26)/(Assumptions!$C$12-Assumptions!$C$26)</f>
+        <v/>
+      </c>
+      <c r="D21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>BOOK VALUE AND SUSTAINABLE RETURN READING (AED a share)</t>
         </is>
       </c>
-      <c r="B19" s="11">
-        <f>B16*B18</f>
-        <v/>
-      </c>
-      <c r="D19" s="8" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="B22" s="11">
+        <f>B19*B21</f>
+        <v/>
+      </c>
+      <c r="D22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>DIVIDEND CAPITALISATION READING (AED a share, unweighted)</t>
         </is>
       </c>
-      <c r="B20" s="12">
-        <f>Assumptions!$C$49*(1+Assumptions!$C$27)/(Assumptions!$C$12-Assumptions!$C$27)</f>
-        <v/>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>a claim on cash paid, not cash earned</t>
+      <c r="B23" s="12">
+        <f>Assumptions!$C$56/Assumptions!$C$12</f>
+        <v/>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>the dividend is a FIXED commitment held flat from 2024 through 2030, so it is valued flat. Growing it credited growth the policy does not promise</t>
         </is>
       </c>
     </row>
@@ -6259,24 +7184,24 @@
           <t>Discount rate = first-year rate + glide x (terminal less first-year)</t>
         </is>
       </c>
-      <c r="B3" s="30">
-        <f>Assumptions!$C$21+B2*(Assumptions!$C$26-Assumptions!$C$21)</f>
-        <v/>
-      </c>
-      <c r="C3" s="30">
-        <f>Assumptions!$C$21+C2*(Assumptions!$C$26-Assumptions!$C$21)</f>
-        <v/>
-      </c>
-      <c r="D3" s="30">
-        <f>Assumptions!$C$21+D2*(Assumptions!$C$26-Assumptions!$C$21)</f>
-        <v/>
-      </c>
-      <c r="E3" s="30">
-        <f>Assumptions!$C$21+E2*(Assumptions!$C$26-Assumptions!$C$21)</f>
-        <v/>
-      </c>
-      <c r="F3" s="30">
-        <f>Assumptions!$C$21+F2*(Assumptions!$C$26-Assumptions!$C$21)</f>
+      <c r="B3" s="31">
+        <f>Assumptions!$C$21+B2*(Assumptions!$C$25-Assumptions!$C$21)</f>
+        <v/>
+      </c>
+      <c r="C3" s="31">
+        <f>Assumptions!$C$21+C2*(Assumptions!$C$25-Assumptions!$C$21)</f>
+        <v/>
+      </c>
+      <c r="D3" s="31">
+        <f>Assumptions!$C$21+D2*(Assumptions!$C$25-Assumptions!$C$21)</f>
+        <v/>
+      </c>
+      <c r="E3" s="31">
+        <f>Assumptions!$C$21+E2*(Assumptions!$C$25-Assumptions!$C$21)</f>
+        <v/>
+      </c>
+      <c r="F3" s="31">
+        <f>Assumptions!$C$21+F2*(Assumptions!$C$25-Assumptions!$C$21)</f>
         <v/>
       </c>
     </row>
@@ -6286,23 +7211,23 @@
           <t>Discount factor (compounding)</t>
         </is>
       </c>
-      <c r="B4" s="31">
+      <c r="B4" s="33">
         <f>1/(1+B3)</f>
         <v/>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="33">
         <f>B4/(1+C3)</f>
         <v/>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="33">
         <f>C4/(1+D3)</f>
         <v/>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="33">
         <f>D4/(1+E3)</f>
         <v/>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="33">
         <f>E4/(1+F3)</f>
         <v/>
       </c>
@@ -6327,23 +7252,23 @@
         </is>
       </c>
       <c r="B6" s="22">
-        <f>Segments!C20-Assumptions!$C$57*0+'Income Statement'!E5+'Income Statement'!E6+'Income Statement'!E7</f>
+        <f>Segments!C32-Assumptions!$C$73*0+'Income Statement'!E5+'Income Statement'!E6+'Income Statement'!E7</f>
         <v/>
       </c>
       <c r="C6" s="22">
-        <f>Segments!D20-Assumptions!$C$57*0+'Income Statement'!F5+'Income Statement'!F6+'Income Statement'!F7</f>
+        <f>Segments!D32-Assumptions!$C$73*0+'Income Statement'!F5+'Income Statement'!F6+'Income Statement'!F7</f>
         <v/>
       </c>
       <c r="D6" s="22">
-        <f>Segments!E20-Assumptions!$C$57*0+'Income Statement'!G5+'Income Statement'!G6+'Income Statement'!G7</f>
+        <f>Segments!E32-Assumptions!$C$73*0+'Income Statement'!G5+'Income Statement'!G6+'Income Statement'!G7</f>
         <v/>
       </c>
       <c r="E6" s="22">
-        <f>Segments!F20-Assumptions!$C$57*0+'Income Statement'!H5+'Income Statement'!H6+'Income Statement'!H7</f>
+        <f>Segments!F32-Assumptions!$C$73*0+'Income Statement'!H5+'Income Statement'!H6+'Income Statement'!H7</f>
         <v/>
       </c>
       <c r="F6" s="22">
-        <f>Segments!G20-Assumptions!$C$57*0+'Income Statement'!I5+'Income Statement'!I6+'Income Statement'!I7</f>
+        <f>Segments!G32-Assumptions!$C$73*0+'Income Statement'!I5+'Income Statement'!I6+'Income Statement'!I7</f>
         <v/>
       </c>
     </row>
@@ -6354,23 +7279,23 @@
         </is>
       </c>
       <c r="B7" s="22">
-        <f>-Assumptions!C$44</f>
+        <f>-Assumptions!C$48</f>
         <v/>
       </c>
       <c r="C7" s="22">
-        <f>-Assumptions!D$44</f>
+        <f>-Assumptions!D$48</f>
         <v/>
       </c>
       <c r="D7" s="22">
-        <f>-Assumptions!E$44</f>
+        <f>-Assumptions!E$48</f>
         <v/>
       </c>
       <c r="E7" s="22">
-        <f>-Assumptions!F$44</f>
+        <f>-Assumptions!F$48</f>
         <v/>
       </c>
       <c r="F7" s="22">
-        <f>-Assumptions!G$44</f>
+        <f>-Assumptions!G$48</f>
         <v/>
       </c>
     </row>
@@ -6435,23 +7360,23 @@
         </is>
       </c>
       <c r="B10" s="22">
-        <f>Assumptions!C$44</f>
+        <f>Assumptions!C$48</f>
         <v/>
       </c>
       <c r="C10" s="22">
-        <f>Assumptions!D$44</f>
+        <f>Assumptions!D$48</f>
         <v/>
       </c>
       <c r="D10" s="22">
-        <f>Assumptions!E$44</f>
+        <f>Assumptions!E$48</f>
         <v/>
       </c>
       <c r="E10" s="22">
-        <f>Assumptions!F$44</f>
+        <f>Assumptions!F$48</f>
         <v/>
       </c>
       <c r="F10" s="22">
-        <f>Assumptions!G$44</f>
+        <f>Assumptions!G$48</f>
         <v/>
       </c>
     </row>
@@ -6462,23 +7387,23 @@
         </is>
       </c>
       <c r="B11" s="22">
-        <f>-Assumptions!C$45</f>
+        <f>-Assumptions!C$49</f>
         <v/>
       </c>
       <c r="C11" s="22">
-        <f>-Assumptions!D$45</f>
+        <f>-Assumptions!D$49</f>
         <v/>
       </c>
       <c r="D11" s="22">
-        <f>-Assumptions!E$45</f>
+        <f>-Assumptions!E$49</f>
         <v/>
       </c>
       <c r="E11" s="22">
-        <f>-Assumptions!F$45</f>
+        <f>-Assumptions!F$49</f>
         <v/>
       </c>
       <c r="F11" s="22">
-        <f>-Assumptions!G$45</f>
+        <f>-Assumptions!G$49</f>
         <v/>
       </c>
     </row>
@@ -6515,23 +7440,23 @@
           <t>FREE CASH FLOW TO THE FIRM — Frame A</t>
         </is>
       </c>
-      <c r="B13" s="23">
+      <c r="B13" s="24">
         <f>B9+B10+B11+B12</f>
         <v/>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="24">
         <f>C9+C10+C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="24">
         <f>D9+D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="24">
         <f>E9+E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="24">
         <f>F9+F10+F11+F12</f>
         <v/>
       </c>
@@ -6542,27 +7467,27 @@
           <t>PRESENT VALUE of free cash flow</t>
         </is>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="24">
         <f>B13*B4</f>
         <v/>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="24">
         <f>C13*C4</f>
         <v/>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="24">
         <f>D13*D4</f>
         <v/>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="24">
         <f>E13*E4</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="24">
         <f>F13*F4</f>
         <v/>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="24">
         <f>SUM(B14:F14)</f>
         <v/>
       </c>
@@ -6587,23 +7512,23 @@
         </is>
       </c>
       <c r="B16" s="22">
-        <f>Segments!C21-Assumptions!$C$57*0+'Income Statement'!E5+'Income Statement'!E6+'Income Statement'!E7</f>
+        <f>Segments!C33-Assumptions!$C$73*0+'Income Statement'!E5+'Income Statement'!E6+'Income Statement'!E7</f>
         <v/>
       </c>
       <c r="C16" s="22">
-        <f>Segments!D21-Assumptions!$C$57*0+'Income Statement'!F5+'Income Statement'!F6+'Income Statement'!F7</f>
+        <f>Segments!D33-Assumptions!$C$73*0+'Income Statement'!F5+'Income Statement'!F6+'Income Statement'!F7</f>
         <v/>
       </c>
       <c r="D16" s="22">
-        <f>Segments!E21-Assumptions!$C$57*0+'Income Statement'!G5+'Income Statement'!G6+'Income Statement'!G7</f>
+        <f>Segments!E33-Assumptions!$C$73*0+'Income Statement'!G5+'Income Statement'!G6+'Income Statement'!G7</f>
         <v/>
       </c>
       <c r="E16" s="22">
-        <f>Segments!F21-Assumptions!$C$57*0+'Income Statement'!H5+'Income Statement'!H6+'Income Statement'!H7</f>
+        <f>Segments!F33-Assumptions!$C$73*0+'Income Statement'!H5+'Income Statement'!H6+'Income Statement'!H7</f>
         <v/>
       </c>
       <c r="F16" s="22">
-        <f>Segments!G21-Assumptions!$C$57*0+'Income Statement'!I5+'Income Statement'!I6+'Income Statement'!I7</f>
+        <f>Segments!G33-Assumptions!$C$73*0+'Income Statement'!I5+'Income Statement'!I6+'Income Statement'!I7</f>
         <v/>
       </c>
     </row>
@@ -6614,23 +7539,23 @@
         </is>
       </c>
       <c r="B17" s="22">
-        <f>-Assumptions!C$44</f>
+        <f>-Assumptions!C$48</f>
         <v/>
       </c>
       <c r="C17" s="22">
-        <f>-Assumptions!D$44</f>
+        <f>-Assumptions!D$48</f>
         <v/>
       </c>
       <c r="D17" s="22">
-        <f>-Assumptions!E$44</f>
+        <f>-Assumptions!E$48</f>
         <v/>
       </c>
       <c r="E17" s="22">
-        <f>-Assumptions!F$44</f>
+        <f>-Assumptions!F$48</f>
         <v/>
       </c>
       <c r="F17" s="22">
-        <f>-Assumptions!G$44</f>
+        <f>-Assumptions!G$48</f>
         <v/>
       </c>
     </row>
@@ -6695,23 +7620,23 @@
         </is>
       </c>
       <c r="B20" s="22">
-        <f>Assumptions!C$44</f>
+        <f>Assumptions!C$48</f>
         <v/>
       </c>
       <c r="C20" s="22">
-        <f>Assumptions!D$44</f>
+        <f>Assumptions!D$48</f>
         <v/>
       </c>
       <c r="D20" s="22">
-        <f>Assumptions!E$44</f>
+        <f>Assumptions!E$48</f>
         <v/>
       </c>
       <c r="E20" s="22">
-        <f>Assumptions!F$44</f>
+        <f>Assumptions!F$48</f>
         <v/>
       </c>
       <c r="F20" s="22">
-        <f>Assumptions!G$44</f>
+        <f>Assumptions!G$48</f>
         <v/>
       </c>
     </row>
@@ -6722,23 +7647,23 @@
         </is>
       </c>
       <c r="B21" s="22">
-        <f>-Assumptions!C$45</f>
+        <f>-Assumptions!C$49</f>
         <v/>
       </c>
       <c r="C21" s="22">
-        <f>-Assumptions!D$45</f>
+        <f>-Assumptions!D$49</f>
         <v/>
       </c>
       <c r="D21" s="22">
-        <f>-Assumptions!E$45</f>
+        <f>-Assumptions!E$49</f>
         <v/>
       </c>
       <c r="E21" s="22">
-        <f>-Assumptions!F$45</f>
+        <f>-Assumptions!F$49</f>
         <v/>
       </c>
       <c r="F21" s="22">
-        <f>-Assumptions!G$45</f>
+        <f>-Assumptions!G$49</f>
         <v/>
       </c>
     </row>
@@ -6775,23 +7700,23 @@
           <t>FREE CASH FLOW TO THE FIRM — Frame B</t>
         </is>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="24">
         <f>B19+B20+B21+B22</f>
         <v/>
       </c>
-      <c r="C23" s="23">
+      <c r="C23" s="24">
         <f>C19+C20+C21+C22</f>
         <v/>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="24">
         <f>D19+D20+D21+D22</f>
         <v/>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="24">
         <f>E19+E20+E21+E22</f>
         <v/>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="24">
         <f>F19+F20+F21+F22</f>
         <v/>
       </c>
@@ -6802,27 +7727,27 @@
           <t>PRESENT VALUE of free cash flow</t>
         </is>
       </c>
-      <c r="B24" s="23">
+      <c r="B24" s="24">
         <f>B23*B4</f>
         <v/>
       </c>
-      <c r="C24" s="23">
+      <c r="C24" s="24">
         <f>C23*C4</f>
         <v/>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="24">
         <f>D23*D4</f>
         <v/>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="24">
         <f>E23*E4</f>
         <v/>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="24">
         <f>F23*F4</f>
         <v/>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="24">
         <f>SUM(B24:F24)</f>
         <v/>
       </c>
@@ -6847,7 +7772,7 @@
         </is>
       </c>
       <c r="B26" s="29">
-        <f>Assumptions!$C$27/Assumptions!$C$28</f>
+        <f>Assumptions!$C$26/Assumptions!$C$27</f>
         <v/>
       </c>
     </row>
@@ -6858,7 +7783,7 @@
         </is>
       </c>
       <c r="B27" s="22">
-        <f>F9*(1+Assumptions!$C$27)</f>
+        <f>F9*(1+Assumptions!$C$26)</f>
         <v/>
       </c>
     </row>
@@ -6880,7 +7805,7 @@
         </is>
       </c>
       <c r="B29" s="17">
-        <f>B28/(Assumptions!$C$26-Assumptions!$C$27)</f>
+        <f>B28/(Assumptions!$C$25-Assumptions!$C$26)</f>
         <v/>
       </c>
     </row>
@@ -6890,7 +7815,7 @@
           <t>Present value of the terminal value</t>
         </is>
       </c>
-      <c r="B30" s="23">
+      <c r="B30" s="24">
         <f>B29*F4</f>
         <v/>
       </c>
@@ -6901,7 +7826,7 @@
           <t>ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B31" s="23">
+      <c r="B31" s="24">
         <f>G14+B30</f>
         <v/>
       </c>
@@ -6937,7 +7862,7 @@
         </is>
       </c>
       <c r="B34" s="29">
-        <f>Assumptions!$C$27/Assumptions!$C$28</f>
+        <f>Assumptions!$C$26/Assumptions!$C$27</f>
         <v/>
       </c>
     </row>
@@ -6948,7 +7873,7 @@
         </is>
       </c>
       <c r="B35" s="22">
-        <f>F19*(1+Assumptions!$C$27)</f>
+        <f>F19*(1+Assumptions!$C$26)</f>
         <v/>
       </c>
     </row>
@@ -6970,7 +7895,7 @@
         </is>
       </c>
       <c r="B37" s="17">
-        <f>B36/(Assumptions!$C$26-Assumptions!$C$27)</f>
+        <f>B36/(Assumptions!$C$25-Assumptions!$C$26)</f>
         <v/>
       </c>
     </row>
@@ -6980,7 +7905,7 @@
           <t>Present value of the terminal value</t>
         </is>
       </c>
-      <c r="B38" s="23">
+      <c r="B38" s="24">
         <f>B37*F4</f>
         <v/>
       </c>
@@ -6991,7 +7916,7 @@
           <t>ENTERPRISE VALUE</t>
         </is>
       </c>
-      <c r="B39" s="23">
+      <c r="B39" s="24">
         <f>G24+B38</f>
         <v/>
       </c>
@@ -7018,7 +7943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7095,23 +8020,23 @@
         <v>35896.617</v>
       </c>
       <c r="E2" s="22">
-        <f>Segments!C11</f>
+        <f>Segments!C23</f>
         <v/>
       </c>
       <c r="F2" s="22">
-        <f>Segments!D11</f>
+        <f>Segments!D23</f>
         <v/>
       </c>
       <c r="G2" s="22">
-        <f>Segments!E11</f>
+        <f>Segments!E23</f>
         <v/>
       </c>
       <c r="H2" s="22">
-        <f>Segments!F11</f>
+        <f>Segments!F23</f>
         <v/>
       </c>
       <c r="I2" s="22">
-        <f>Segments!G11</f>
+        <f>Segments!G23</f>
         <v/>
       </c>
     </row>
@@ -7131,23 +8056,23 @@
         <v>6945.79</v>
       </c>
       <c r="E3" s="22">
-        <f>Segments!C20</f>
+        <f>Segments!C32</f>
         <v/>
       </c>
       <c r="F3" s="22">
-        <f>Segments!D20</f>
+        <f>Segments!D32</f>
         <v/>
       </c>
       <c r="G3" s="22">
-        <f>Segments!E20</f>
+        <f>Segments!E32</f>
         <v/>
       </c>
       <c r="H3" s="22">
-        <f>Segments!F20</f>
+        <f>Segments!F32</f>
         <v/>
       </c>
       <c r="I3" s="22">
-        <f>Segments!G20</f>
+        <f>Segments!G32</f>
         <v/>
       </c>
     </row>
@@ -7203,23 +8128,23 @@
         <v>-2547.6</v>
       </c>
       <c r="E5" s="22">
-        <f>-Assumptions!$C$57*(1+Assumptions!C$41)</f>
+        <f>-Assumptions!$C$73*(1+Assumptions!C$45)</f>
         <v/>
       </c>
       <c r="F5" s="22">
-        <f>E5*(1+Assumptions!D$41)</f>
+        <f>E5*(1+Assumptions!D$45)</f>
         <v/>
       </c>
       <c r="G5" s="22">
-        <f>F5*(1+Assumptions!E$41)</f>
+        <f>F5*(1+Assumptions!E$45)</f>
         <v/>
       </c>
       <c r="H5" s="22">
-        <f>G5*(1+Assumptions!F$41)</f>
+        <f>G5*(1+Assumptions!F$45)</f>
         <v/>
       </c>
       <c r="I5" s="22">
-        <f>H5*(1+Assumptions!G$41)</f>
+        <f>H5*(1+Assumptions!G$45)</f>
         <v/>
       </c>
     </row>
@@ -7239,23 +8164,23 @@
         <v>167.665</v>
       </c>
       <c r="E6" s="22">
-        <f>Assumptions!$C$58*(1+Assumptions!C$42)</f>
+        <f>Assumptions!$C$74*(1+Assumptions!C$46)</f>
         <v/>
       </c>
       <c r="F6" s="22">
-        <f>E6*(1+Assumptions!D$42)</f>
+        <f>E6*(1+Assumptions!D$46)</f>
         <v/>
       </c>
       <c r="G6" s="22">
-        <f>F6*(1+Assumptions!E$42)</f>
+        <f>F6*(1+Assumptions!E$46)</f>
         <v/>
       </c>
       <c r="H6" s="22">
-        <f>G6*(1+Assumptions!F$42)</f>
+        <f>G6*(1+Assumptions!F$46)</f>
         <v/>
       </c>
       <c r="I6" s="22">
-        <f>H6*(1+Assumptions!G$42)</f>
+        <f>H6*(1+Assumptions!G$46)</f>
         <v/>
       </c>
     </row>
@@ -7275,23 +8200,23 @@
         <v>-284.305</v>
       </c>
       <c r="E7" s="22">
-        <f>-Assumptions!C$43</f>
+        <f>-Assumptions!C$47</f>
         <v/>
       </c>
       <c r="F7" s="22">
-        <f>-Assumptions!D$43</f>
+        <f>-Assumptions!D$47</f>
         <v/>
       </c>
       <c r="G7" s="22">
-        <f>-Assumptions!E$43</f>
+        <f>-Assumptions!E$47</f>
         <v/>
       </c>
       <c r="H7" s="22">
-        <f>-Assumptions!F$43</f>
+        <f>-Assumptions!F$47</f>
         <v/>
       </c>
       <c r="I7" s="22">
-        <f>-Assumptions!G$43</f>
+        <f>-Assumptions!G$47</f>
         <v/>
       </c>
     </row>
@@ -7301,32 +8226,32 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n">
+      <c r="B8" s="34" t="n">
         <v>3679.814</v>
       </c>
-      <c r="C8" s="32" t="n">
+      <c r="C8" s="34" t="n">
         <v>3854.702</v>
       </c>
-      <c r="D8" s="32" t="n">
+      <c r="D8" s="34" t="n">
         <v>4281.55</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="24">
         <f>E3+E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="24">
         <f>F3+F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="24">
         <f>G3+G5+G6+G7</f>
         <v/>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="24">
         <f>H3+H5+H6+H7</f>
         <v/>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="24">
         <f>I3+I5+I6+I7</f>
         <v/>
       </c>
@@ -7383,23 +8308,23 @@
         <v>-775.946</v>
       </c>
       <c r="E10" s="22">
-        <f>-Assumptions!C$44</f>
+        <f>-Assumptions!C$48</f>
         <v/>
       </c>
       <c r="F10" s="22">
-        <f>-Assumptions!D$44</f>
+        <f>-Assumptions!D$48</f>
         <v/>
       </c>
       <c r="G10" s="22">
-        <f>-Assumptions!E$44</f>
+        <f>-Assumptions!E$48</f>
         <v/>
       </c>
       <c r="H10" s="22">
-        <f>-Assumptions!F$44</f>
+        <f>-Assumptions!F$48</f>
         <v/>
       </c>
       <c r="I10" s="22">
-        <f>-Assumptions!G$44</f>
+        <f>-Assumptions!G$48</f>
         <v/>
       </c>
     </row>
@@ -7409,32 +8334,32 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B11" s="32" t="n">
+      <c r="B11" s="34" t="n">
         <v>2983.249</v>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="34" t="n">
         <v>3068.895</v>
       </c>
-      <c r="D11" s="32" t="n">
+      <c r="D11" s="34" t="n">
         <v>3505.604</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="24">
         <f>E8+E10</f>
         <v/>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="24">
         <f>F8+F10</f>
         <v/>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="24">
         <f>G8+G10</f>
         <v/>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="24">
         <f>H8+H10</f>
         <v/>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="24">
         <f>I8+I10</f>
         <v/>
       </c>
@@ -7455,23 +8380,23 @@
         <v>71.274</v>
       </c>
       <c r="E12" s="22">
-        <f>Assumptions!$C$68</f>
+        <f>Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="F12" s="22">
-        <f>Assumptions!$C$68</f>
+        <f>Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="G12" s="22">
-        <f>Assumptions!$C$68</f>
+        <f>Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="H12" s="22">
-        <f>Assumptions!$C$68</f>
+        <f>Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="I12" s="22">
-        <f>Assumptions!$C$68</f>
+        <f>Assumptions!$C$84</f>
         <v/>
       </c>
     </row>
@@ -7491,23 +8416,23 @@
         <v>-402.945</v>
       </c>
       <c r="E13" s="22">
-        <f>-Assumptions!$C$67</f>
+        <f>-Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="F13" s="22">
-        <f>-Assumptions!$C$67</f>
+        <f>-Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="G13" s="22">
-        <f>-Assumptions!$C$67</f>
+        <f>-Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="H13" s="22">
-        <f>-Assumptions!$C$67</f>
+        <f>-Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="I13" s="22">
-        <f>-Assumptions!$C$67</f>
+        <f>-Assumptions!$C$83</f>
         <v/>
       </c>
     </row>
@@ -7589,13 +8514,13 @@
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B16" s="33" t="n">
+      <c r="B16" s="35" t="n">
         <v>2630.489</v>
       </c>
-      <c r="C16" s="33" t="n">
+      <c r="C16" s="35" t="n">
         <v>2472.283</v>
       </c>
-      <c r="D16" s="33" t="n">
+      <c r="D16" s="35" t="n">
         <v>2851.042</v>
       </c>
       <c r="E16" s="17">
@@ -7635,23 +8560,23 @@
         <v>-57.042</v>
       </c>
       <c r="E17" s="22">
-        <f>-Assumptions!$C$69</f>
+        <f>-Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="F17" s="22">
-        <f>-Assumptions!$C$69</f>
+        <f>-Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="G17" s="22">
-        <f>-Assumptions!$C$69</f>
+        <f>-Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="H17" s="22">
-        <f>-Assumptions!$C$69</f>
+        <f>-Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="I17" s="22">
-        <f>-Assumptions!$C$69</f>
+        <f>-Assumptions!$C$85</f>
         <v/>
       </c>
     </row>
@@ -7661,32 +8586,32 @@
           <t>Profit attributable to owners</t>
         </is>
       </c>
-      <c r="B18" s="32" t="n">
+      <c r="B18" s="34" t="n">
         <v>2601.421</v>
       </c>
-      <c r="C18" s="32" t="n">
+      <c r="C18" s="34" t="n">
         <v>2420.275</v>
       </c>
-      <c r="D18" s="32" t="n">
+      <c r="D18" s="34" t="n">
         <v>2794</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="24">
         <f>E16+E17</f>
         <v/>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="24">
         <f>F16+F17</f>
         <v/>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="24">
         <f>G16+G17</f>
         <v/>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="24">
         <f>H16+H17</f>
         <v/>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="24">
         <f>I16+I17</f>
         <v/>
       </c>
@@ -7706,24 +8631,114 @@
       <c r="D19" s="16" t="n">
         <v>0.224</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="28">
         <f>E18/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="28">
         <f>F18/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="28">
         <f>G18/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="H19" s="26">
+      <c r="H19" s="28">
         <f>H18/Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="I19" s="26">
+      <c r="I19" s="28">
         <f>I18/Assumptions!$C$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Dividend — the fixed policy commitment</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="22">
+        <f>Assumptions!$C$56*Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="F20" s="22">
+        <f>Assumptions!$C$56*Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="G20" s="22">
+        <f>Assumptions!$C$56*Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="H20" s="22">
+        <f>Assumptions!$C$56*Assumptions!$C$4</f>
+        <v/>
+      </c>
+      <c r="I20" s="22">
+        <f>Assumptions!$C$56*Assumptions!$C$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Dividend — the 75% of profit minimum</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="22">
+        <f>Assumptions!$C$57*E18</f>
+        <v/>
+      </c>
+      <c r="F21" s="22">
+        <f>Assumptions!$C$57*F18</f>
+        <v/>
+      </c>
+      <c r="G21" s="22">
+        <f>Assumptions!$C$57*G18</f>
+        <v/>
+      </c>
+      <c r="H21" s="22">
+        <f>Assumptions!$C$57*H18</f>
+        <v/>
+      </c>
+      <c r="I21" s="22">
+        <f>Assumptions!$C$57*I18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>DIVIDEND PAID = the higher of the two</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="n"/>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="35" t="n"/>
+      <c r="E22" s="17">
+        <f>MAX(E20,E21)</f>
+        <v/>
+      </c>
+      <c r="F22" s="17">
+        <f>MAX(F20,F21)</f>
+        <v/>
+      </c>
+      <c r="G22" s="17">
+        <f>MAX(G20,G21)</f>
+        <v/>
+      </c>
+      <c r="H22" s="17">
+        <f>MAX(H20,H21)</f>
+        <v/>
+      </c>
+      <c r="I22" s="17">
+        <f>MAX(I20,I21)</f>
         <v/>
       </c>
     </row>

--- a/engine/adnocdist_study/ADNOCDIST_Valuation_Model_09082026.xlsx
+++ b/engine/adnocdist_study/ADNOCDIST_Valuation_Model_09082026.xlsx
@@ -2230,19 +2230,19 @@
         </is>
       </c>
       <c r="B3" s="15" t="n">
-        <v>5.037845630037896</v>
+        <v>5.039624840025958</v>
       </c>
       <c r="C3" s="15" t="n">
-        <v>5.345214853859902</v>
+        <v>5.347254783976864</v>
       </c>
       <c r="D3" s="15" t="n">
-        <v>5.713836104953238</v>
+        <v>5.716213552971893</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>6.16441462979946</v>
+        <v>6.167241416127026</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>6.728172817732825</v>
+        <v>6.731618765321264</v>
       </c>
     </row>
     <row r="4">
@@ -2252,19 +2252,19 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>4.658763041404357</v>
+        <v>4.660291078202476</v>
       </c>
       <c r="C4" s="15" t="n">
-        <v>4.909890610408024</v>
+        <v>4.911618031216516</v>
       </c>
       <c r="D4" s="15" t="n">
-        <v>5.206306997169102</v>
+        <v>5.208286557962923</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>5.561771030445217</v>
+        <v>5.56407692605848</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>5.996242801840086</v>
+        <v>5.998983043740145</v>
       </c>
     </row>
     <row r="5">
@@ -2274,19 +2274,19 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>4.334107990736483</v>
+        <v>4.335436272321719</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>4.541936057842556</v>
+        <v>4.543419809706135</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>4.783957863288807</v>
+        <v>4.785634375641991</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>5.069606287348343</v>
+        <v>5.071526506015136</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>5.412135179525237</v>
+        <v>5.41437074066283</v>
       </c>
     </row>
     <row r="6">
@@ -2296,19 +2296,19 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>4.052905511891289</v>
+        <v>4.054072221721011</v>
       </c>
       <c r="C6" s="15" t="n">
-        <v>4.226787299827193</v>
+        <v>4.228077263095823</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>4.426944036409902</v>
+        <v>4.428384255273475</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>4.660013683874013</v>
+        <v>4.66164015279281</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>4.935075786102526</v>
+        <v>4.936937671528304</v>
       </c>
     </row>
     <row r="7">
@@ -2318,19 +2318,19 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>3.806945979527142</v>
+        <v>3.807980077733704</v>
       </c>
       <c r="C7" s="15" t="n">
-        <v>3.953796778929035</v>
+        <v>3.954929995051433</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>4.121141840732053</v>
+        <v>4.122394135194883</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>4.31375658044441</v>
+        <v>4.315154004863403</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>4.538024994088219</v>
+        <v>4.5396022692034</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>0.06437428020423498</v>
+        <v>0.06435489098612174</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>5.713836104953238</v>
+        <v>5.716213552971893</v>
       </c>
     </row>
     <row r="11">
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>0.06937428020423497</v>
+        <v>0.06935489098612173</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>5.206306997169102</v>
+        <v>5.208286557962923</v>
       </c>
     </row>
     <row r="12">
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>0.07437428020423498</v>
+        <v>0.07435489098612173</v>
       </c>
       <c r="C12" s="15" t="n">
-        <v>4.783957863288807</v>
+        <v>4.785634375641991</v>
       </c>
     </row>
     <row r="13">
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>0.07937428020423498</v>
+        <v>0.07935489098612174</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>4.426944036409902</v>
+        <v>4.428384255273475</v>
       </c>
     </row>
     <row r="14">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>0.08437428020423497</v>
+        <v>0.08435489098612173</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>4.121141840732053</v>
+        <v>4.122394135194883</v>
       </c>
     </row>
     <row r="15">
@@ -2428,7 +2428,7 @@
         <v>0.005</v>
       </c>
       <c r="C15" s="15" t="n">
-        <v>4.334107990736483</v>
+        <v>4.335436272321719</v>
       </c>
     </row>
     <row r="16">
@@ -2441,7 +2441,7 @@
         <v>0.01</v>
       </c>
       <c r="C16" s="15" t="n">
-        <v>4.541936057842556</v>
+        <v>4.543419809706135</v>
       </c>
     </row>
     <row r="17">
@@ -2454,7 +2454,7 @@
         <v>0.015</v>
       </c>
       <c r="C17" s="15" t="n">
-        <v>4.783957863288807</v>
+        <v>4.785634375641991</v>
       </c>
     </row>
     <row r="18">
@@ -2467,7 +2467,7 @@
         <v>0.02</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>5.069606287348343</v>
+        <v>5.071526506015136</v>
       </c>
     </row>
     <row r="19">
@@ -2480,7 +2480,7 @@
         <v>0.025</v>
       </c>
       <c r="C19" s="15" t="n">
-        <v>5.412135179525237</v>
+        <v>5.41437074066283</v>
       </c>
     </row>
     <row r="20">
@@ -2493,7 +2493,7 @@
         <v>0.45</v>
       </c>
       <c r="C20" s="15" t="n">
-        <v>5.721632266901376</v>
+        <v>5.72321287684248</v>
       </c>
     </row>
     <row r="21">
@@ -2506,7 +2506,7 @@
         <v>0.55</v>
       </c>
       <c r="C21" s="15" t="n">
-        <v>5.212160196485639</v>
+        <v>5.21380830844749</v>
       </c>
     </row>
     <row r="22">
@@ -2519,7 +2519,7 @@
         <v>0.6494</v>
       </c>
       <c r="C22" s="15" t="n">
-        <v>4.783957863288807</v>
+        <v>4.785634375641991</v>
       </c>
     </row>
     <row r="23">
@@ -2532,7 +2532,7 @@
         <v>0.8</v>
       </c>
       <c r="C23" s="15" t="n">
-        <v>4.247686654673135</v>
+        <v>4.249362241125167</v>
       </c>
     </row>
     <row r="24">
@@ -2545,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="15" t="n">
-        <v>3.687579642884075</v>
+        <v>3.689210943290246</v>
       </c>
     </row>
     <row r="25">
@@ -2558,7 +2558,7 @@
         <v>-0.01</v>
       </c>
       <c r="C25" s="15" t="n">
-        <v>4.503551144301958</v>
+        <v>4.505124152371323</v>
       </c>
     </row>
     <row r="26">
@@ -2571,7 +2571,7 @@
         <v>-0.005</v>
       </c>
       <c r="C26" s="15" t="n">
-        <v>4.681463152860606</v>
+        <v>4.683100005271345</v>
       </c>
     </row>
     <row r="27">
@@ -2584,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="15" t="n">
-        <v>4.862800051117585</v>
+        <v>4.864502043009441</v>
       </c>
     </row>
     <row r="28">
@@ -2597,7 +2597,7 @@
         <v>0.005</v>
       </c>
       <c r="C28" s="15" t="n">
-        <v>5.047612510089233</v>
+        <v>5.049380956261225</v>
       </c>
     </row>
     <row r="29">
@@ -2610,7 +2610,7 @@
         <v>0.01</v>
       </c>
       <c r="C29" s="15" t="n">
-        <v>5.235951704116874</v>
+        <v>5.237787939225549</v>
       </c>
     </row>
     <row r="30">
@@ -2623,7 +2623,7 @@
         <v>-0.1</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>3.980351258054539</v>
+        <v>3.981765775764861</v>
       </c>
     </row>
     <row r="31">
@@ -2636,7 +2636,7 @@
         <v>-0.05</v>
       </c>
       <c r="C31" s="15" t="n">
-        <v>4.382154560671673</v>
+        <v>4.383700075703425</v>
       </c>
     </row>
     <row r="32">
@@ -2649,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>4.783957863288807</v>
+        <v>4.785634375641991</v>
       </c>
     </row>
     <row r="33">
@@ -2662,7 +2662,7 @@
         <v>0.05</v>
       </c>
       <c r="C33" s="15" t="n">
-        <v>5.185761165905943</v>
+        <v>5.187568675580559</v>
       </c>
     </row>
     <row r="34">
@@ -2675,7 +2675,7 @@
         <v>0.1</v>
       </c>
       <c r="C34" s="15" t="n">
-        <v>5.587564468523079</v>
+        <v>5.589502975519126</v>
       </c>
     </row>
     <row r="35">
@@ -2688,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="C35" s="15" t="n">
-        <v>4.783957863288807</v>
+        <v>4.785634375641991</v>
       </c>
     </row>
     <row r="36">
@@ -2701,7 +2701,7 @@
         <v>150</v>
       </c>
       <c r="C36" s="15" t="n">
-        <v>4.938619794286794</v>
+        <v>4.940348831172789</v>
       </c>
     </row>
     <row r="37">
@@ -2714,7 +2714,7 @@
         <v>295</v>
       </c>
       <c r="C37" s="15" t="n">
-        <v>5.088126327584848</v>
+        <v>5.089906138185894</v>
       </c>
     </row>
     <row r="38">
@@ -2727,7 +2727,7 @@
         <v>450</v>
       </c>
       <c r="C38" s="15" t="n">
-        <v>5.247943656282771</v>
+        <v>5.249777742234385</v>
       </c>
     </row>
     <row r="39">
@@ -2740,7 +2740,7 @@
         <v>600</v>
       </c>
       <c r="C39" s="15" t="n">
-        <v>5.402605587280759</v>
+        <v>5.404492197765181</v>
       </c>
     </row>
     <row r="40">
@@ -2753,7 +2753,7 @@
         <v>0.09</v>
       </c>
       <c r="C40" s="15" t="n">
-        <v>4.851251222861921</v>
+        <v>4.852949586505804</v>
       </c>
     </row>
     <row r="41">
@@ -2766,7 +2766,7 @@
         <v>0.1017</v>
       </c>
       <c r="C41" s="15" t="n">
-        <v>4.783957863288807</v>
+        <v>4.785634375641991</v>
       </c>
     </row>
     <row r="42">
@@ -2779,7 +2779,7 @@
         <v>0.12</v>
       </c>
       <c r="C42" s="15" t="n">
-        <v>4.678704147033425</v>
+        <v>4.680346481726801</v>
       </c>
     </row>
     <row r="43">
@@ -2792,7 +2792,7 @@
         <v>0.15</v>
       </c>
       <c r="C43" s="15" t="n">
-        <v>4.506157071204932</v>
+        <v>4.507743376947799</v>
       </c>
     </row>
     <row r="44">
@@ -2805,7 +2805,7 @@
         <v>0.18</v>
       </c>
       <c r="C44" s="15" t="n">
-        <v>4.333609995376437</v>
+        <v>4.335140272168797</v>
       </c>
     </row>
     <row r="45">
@@ -2818,7 +2818,7 @@
         <v>-0.2</v>
       </c>
       <c r="C45" s="15" t="n">
-        <v>4.848178505227209</v>
+        <v>4.849858313746314</v>
       </c>
     </row>
     <row r="46">
@@ -2831,7 +2831,7 @@
         <v>-0.1</v>
       </c>
       <c r="C46" s="15" t="n">
-        <v>4.816068184258008</v>
+        <v>4.817746344694153</v>
       </c>
     </row>
     <row r="47">
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="C47" s="15" t="n">
-        <v>4.783957863288807</v>
+        <v>4.785634375641991</v>
       </c>
     </row>
     <row r="48">
@@ -2857,7 +2857,7 @@
         <v>0.1</v>
       </c>
       <c r="C48" s="15" t="n">
-        <v>4.751847542319606</v>
+        <v>4.75352240658983</v>
       </c>
     </row>
     <row r="49">
@@ -2870,7 +2870,7 @@
         <v>0.2</v>
       </c>
       <c r="C49" s="15" t="n">
-        <v>4.719737221350404</v>
+        <v>4.721410437537669</v>
       </c>
     </row>
   </sheetData>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="C3" s="15" t="n">
-        <v>4.07</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
